--- a/docs/tracker.xlsx
+++ b/docs/tracker.xlsx
@@ -50,7 +50,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -112,6 +112,11 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF0F0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -154,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -221,6 +226,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -588,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="15" min="1" max="1"/>
@@ -2079,7 +2090,7 @@
       </c>
       <c r="F35" s="18" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G35" s="19" t="inlineStr">
@@ -2236,6 +2247,1322 @@
       <c r="I38" s="18" t="inlineStr">
         <is>
           <t>07.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1" s="15">
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>T-034</t>
+        </is>
+      </c>
+      <c r="B39" s="24" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="C39" s="25" t="inlineStr">
+        <is>
+          <t>Mail.ru OAuth: ошибка bad client при авторизации</t>
+        </is>
+      </c>
+      <c r="D39" s="25" t="inlineStr">
+        <is>
+          <t>При переходе на Mail.ru OAuth авторизацию, Mail.ru возвращает error_code=2 bad client. client_id=791475. Необходимо проверить: 1) зарегистрирован ли redirect_uri в настройках приложения Mail.ru, 2) совпадает ли client_id с полем из настроек OAuth на o2.mail.ru, 3) активировано ли приложение.</t>
+        </is>
+      </c>
+      <c r="E39" s="24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F39" s="24" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="G39" s="25" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H39" s="24" t="inlineStr">
+        <is>
+          <t>07.03.2026</t>
+        </is>
+      </c>
+      <c r="I39" s="24" t="inlineStr">
+        <is>
+          <t>07.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1" s="15">
+      <c r="A40" s="18" t="inlineStr">
+        <is>
+          <t>T-035</t>
+        </is>
+      </c>
+      <c r="B40" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C40" s="19" t="inlineStr">
+        <is>
+          <t>V29 миграция: таблицы device_user_sessions, app_focus_intervals, расширение device_audit_events</t>
+        </is>
+      </c>
+      <c r="D40" s="19" t="inlineStr">
+        <is>
+          <t>Flyway миграция V29: CREATE TABLE device_user_sessions, CREATE TABLE app_focus_intervals (partitioned), ALTER device_audit_events (расширить CHECK constraint, добавить колонку username), CREATE VIEW v_tenant_users. Индексы для аналитических запросов.</t>
+        </is>
+      </c>
+      <c r="E40" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F40" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G40" s="19" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H40" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I40" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1" s="15">
+      <c r="A41" s="18" t="inlineStr">
+        <is>
+          <t>T-036</t>
+        </is>
+      </c>
+      <c r="B41" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C41" s="19" t="inlineStr">
+        <is>
+          <t>Entity AppFocusInterval + DeviceUserSession (JPA, partitioned)</t>
+        </is>
+      </c>
+      <c r="D41" s="19" t="inlineStr">
+        <is>
+          <t>JPA entities для новых таблиц app_focus_intervals (партиционированная, composite PK id+created_ts) и device_user_sessions. IdClass для партиционированной таблицы. Repositories с custom queries.</t>
+        </is>
+      </c>
+      <c r="E41" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F41" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G41" s="19" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H41" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I41" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1" s="15">
+      <c r="A42" s="18" t="inlineStr">
+        <is>
+          <t>T-037</t>
+        </is>
+      </c>
+      <c r="B42" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C42" s="19" t="inlineStr">
+        <is>
+          <t>DTO: SubmitFocusIntervalsRequest, FocusIntervalItem, аналитические response-модели</t>
+        </is>
+      </c>
+      <c r="D42" s="19" t="inlineStr">
+        <is>
+          <t>Request DTO: SubmitFocusIntervalsRequest (device_id, username, intervals[]), FocusIntervalItem (id, process_name, window_title, is_browser, browser_name, domain, started_at, ended_at, duration_ms). Response DTOs: UserListResponse, UserActivityResponse, UserWorktimeResponse, UserAppsResponse, UserDomainsResponse, UserTimesheetResponse.</t>
+        </is>
+      </c>
+      <c r="E42" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F42" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G42" s="19" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H42" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I42" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1" s="15">
+      <c r="A43" s="18" t="inlineStr">
+        <is>
+          <t>T-038</t>
+        </is>
+      </c>
+      <c r="B43" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C43" s="19" t="inlineStr">
+        <is>
+          <t>FocusIntervalService: batch submit с дедупликацией и upsert user sessions</t>
+        </is>
+      </c>
+      <c r="D43" s="19" t="inlineStr">
+        <is>
+          <t>Сервис приёма фокус-интервалов от агентов. Валидация JWT device_id. Дедупликация по UUID id. Batch persist (flush каждые 50). Вызов DeviceUserSessionService.upsert() для обновления last_seen_ts. Проверка timestamps (не в будущем &gt; 5 мин).</t>
+        </is>
+      </c>
+      <c r="E43" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F43" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G43" s="19" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H43" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I43" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1" s="15">
+      <c r="A44" s="18" t="inlineStr">
+        <is>
+          <t>T-039</t>
+        </is>
+      </c>
+      <c r="B44" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C44" s="19" t="inlineStr">
+        <is>
+          <t>FocusIntervalController: POST /api/v1/ingest/activity/focus-intervals</t>
+        </is>
+      </c>
+      <c r="D44" s="19" t="inlineStr">
+        <is>
+          <t>REST контроллер для приёма батчей фокус-интервалов от агентов. Аутентификация через device JWT. Validation: device_id match, 1-100 intervals. Возвращает accepted/duplicates/correlation_id.</t>
+        </is>
+      </c>
+      <c r="E44" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F44" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G44" s="19" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H44" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I44" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1" s="15">
+      <c r="A45" s="18" t="inlineStr">
+        <is>
+          <t>T-040</t>
+        </is>
+      </c>
+      <c r="B45" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C45" s="19" t="inlineStr">
+        <is>
+          <t>Расширение AuditEventService: сохранение username, upsert device_user_sessions</t>
+        </is>
+      </c>
+      <c r="D45" s="19" t="inlineStr">
+        <is>
+          <t>В submitEvents(): сохранять username из SubmitAuditEventsRequest в DeviceAuditEvent.username. Вызывать DeviceUserSessionService.upsert() при наличии username. Добавить поле username в SubmitAuditEventsRequest (optional, backward compatible).</t>
+        </is>
+      </c>
+      <c r="E45" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F45" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G45" s="19" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H45" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I45" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1" s="15">
+      <c r="A46" s="18" t="inlineStr">
+        <is>
+          <t>T-041</t>
+        </is>
+      </c>
+      <c r="B46" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C46" s="19" t="inlineStr">
+        <is>
+          <t>UserActivityService: агрегатные запросы (activity, worktime, apps, domains, timesheet)</t>
+        </is>
+      </c>
+      <c r="D46" s="19" t="inlineStr">
+        <is>
+          <t>Сервис аналитических SQL-запросов к app_focus_intervals. Методы: getUserActivity (SUM/GROUP BY process_name, domain за период), getUserWorktime (MIN/MAX started_at по дням, расчёт опозданий/ранних уходов), getUserApps (GROUP BY process_name), getUserDomains (GROUP BY domain WHERE is_browser), getUserTimesheet (календарная сетка за месяц).</t>
+        </is>
+      </c>
+      <c r="E46" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F46" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G46" s="19" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H46" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I46" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1" s="15">
+      <c r="A47" s="18" t="inlineStr">
+        <is>
+          <t>T-042</t>
+        </is>
+      </c>
+      <c r="B47" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C47" s="19" t="inlineStr">
+        <is>
+          <t>UserActivityController: GET endpoints для аналитики (/users, /users/{username}/*)</t>
+        </is>
+      </c>
+      <c r="D47" s="19" t="inlineStr">
+        <is>
+          <t>REST контроллер с 6 endpoints: GET /users (список), GET /users/{username}/activity (сводка), GET /users/{username}/worktime (рабочее время), GET /users/{username}/apps (приложения), GET /users/{username}/domains (домены), GET /users/{username}/timesheet (табель). Permission: RECORDINGS:READ. URL-decode username.</t>
+        </is>
+      </c>
+      <c r="E47" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F47" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G47" s="19" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H47" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I47" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1" s="15">
+      <c r="A48" s="18" t="inlineStr">
+        <is>
+          <t>T-043</t>
+        </is>
+      </c>
+      <c r="B48" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C48" s="19" t="inlineStr">
+        <is>
+          <t>Agent: UserSessionInfo — получение Windows username (WTS API + Environment)</t>
+        </is>
+      </c>
+      <c r="D48" s="19" t="inlineStr">
+        <is>
+          <t>Класс UserSessionInfo для получения имени пользователя Windows. GetCurrentUsername() → DOMAIN\user через Environment.UserDomainName + Environment.UserName. GetDisplayName() через DirectoryServices или WMI Win32_UserAccount. Для Windows Service (session 0): WTSQuerySessionInformation с active console session ID.</t>
+        </is>
+      </c>
+      <c r="E48" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F48" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G48" s="19" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="H48" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I48" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1" s="15">
+      <c r="A49" s="18" t="inlineStr">
+        <is>
+          <t>T-044</t>
+        </is>
+      </c>
+      <c r="B49" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C49" s="19" t="inlineStr">
+        <is>
+          <t>Agent: BrowserDomainParser — парсинг домена из заголовка окна браузера</t>
+        </is>
+      </c>
+      <c r="D49" s="19" t="inlineStr">
+        <is>
+          <t>Статический класс BrowserDomainParser. Метод ParseDomain(windowTitle, browserName) → (domain, pageTitle). Regex-паттерны для Chrome, Edge, Firefox, Opera, Yandex Browser, Vivaldi, Brave. Извлечение домена из page title через domain-like regex. Fallback: domain=null при невозможности парсинга.</t>
+        </is>
+      </c>
+      <c r="E49" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F49" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G49" s="19" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="H49" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I49" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1" s="15">
+      <c r="A50" s="18" t="inlineStr">
+        <is>
+          <t>T-045</t>
+        </is>
+      </c>
+      <c r="B50" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C50" s="19" t="inlineStr">
+        <is>
+          <t>Agent: ActiveWindowTracker — polling GetForegroundWindow каждые 5 сек</t>
+        </is>
+      </c>
+      <c r="D50" s="19" t="inlineStr">
+        <is>
+          <t>BackgroundService ActiveWindowTracker. Polling через GetForegroundWindow() + GetWindowText() + GetWindowThreadProcessId() каждые 5 сек. При смене фокуса: завершает текущий интервал, определяет browser (по process_name), парсит домен через BrowserDomainParser, публикует FocusInterval в FocusIntervalSink. Debounce: интервалы &lt; 3 сек игнорируются.</t>
+        </is>
+      </c>
+      <c r="E50" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F50" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G50" s="19" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="H50" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I50" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1" s="15">
+      <c r="A51" s="18" t="inlineStr">
+        <is>
+          <t>T-046</t>
+        </is>
+      </c>
+      <c r="B51" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C51" s="19" t="inlineStr">
+        <is>
+          <t>Agent: FocusInterval модель + FocusIntervalSink (батчинг, SQLite, upload)</t>
+        </is>
+      </c>
+      <c r="D51" s="19" t="inlineStr">
+        <is>
+          <t>Модель FocusInterval (Id, ProcessName, WindowTitle, IsBrowser, BrowserName, Domain, StartedAt, EndedAt, DurationMs, SessionId). FocusIntervalSink: BackgroundService аналогичный AuditEventSink. ConcurrentQueue + SQLite persistence. Flush каждые 30 сек или при 50 интервалах. POST на {IngestBaseUrl}/activity/focus-intervals. Max batch 100. Retry при ошибках.</t>
+        </is>
+      </c>
+      <c r="E51" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F51" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G51" s="19" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="H51" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I51" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1" s="15">
+      <c r="A52" s="18" t="inlineStr">
+        <is>
+          <t>T-047</t>
+        </is>
+      </c>
+      <c r="B52" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C52" s="19" t="inlineStr">
+        <is>
+          <t>Agent: интеграция — username в AuditEventSink, регистрация DI в Program.cs</t>
+        </is>
+      </c>
+      <c r="D52" s="19" t="inlineStr">
+        <is>
+          <t>Добавить свойство CurrentUsername в AuditEventSink, отправлять username в body POST /audit-events. В SessionWatcher при SESSION_LOGON/SESSION_UNLOCK обновлять CurrentUsername через UserSessionInfo. В Program.cs: зарегистрировать UserSessionInfo, BrowserDomainParser, FocusIntervalSink, ActiveWindowTracker как singleton + hosted service.</t>
+        </is>
+      </c>
+      <c r="E52" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F52" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G52" s="19" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="H52" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I52" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1" s="15">
+      <c r="A53" s="18" t="inlineStr">
+        <is>
+          <t>T-048</t>
+        </is>
+      </c>
+      <c r="B53" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C53" s="19" t="inlineStr">
+        <is>
+          <t>Agent: расширение LocalDatabase — таблица focus_intervals в SQLite</t>
+        </is>
+      </c>
+      <c r="D53" s="19" t="inlineStr">
+        <is>
+          <t>Добавить таблицу focus_intervals в SQLite schema LocalDatabase: id, process_name, window_title, is_browser, browser_name, domain, started_at, ended_at, duration_ms, session_id, uploaded, created_at. Методы: SaveFocusInterval, GetPendingFocusIntervals, MarkFocusIntervalUploaded.</t>
+        </is>
+      </c>
+      <c r="E53" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F53" s="18" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="G53" s="19" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="H53" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I53" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1" s="15">
+      <c r="A54" s="18" t="inlineStr">
+        <is>
+          <t>T-049</t>
+        </is>
+      </c>
+      <c r="B54" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C54" s="19" t="inlineStr">
+        <is>
+          <t>Frontend: TypeScript типы для activity API (types/activity.ts)</t>
+        </is>
+      </c>
+      <c r="D54" s="19" t="inlineStr">
+        <is>
+          <t>Типы для всех response-моделей: UserListResponse, UserItem, TodaySummary, UserActivityResponse, UserWorktimeResponse, WorktimeDay, UserAppsResponse, AppUsageItem, UserDomainsResponse, DomainUsageItem, UserTimesheetResponse, TimesheetDay.</t>
+        </is>
+      </c>
+      <c r="E54" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F54" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G54" s="19" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="H54" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I54" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1" s="15">
+      <c r="A55" s="18" t="inlineStr">
+        <is>
+          <t>T-050</t>
+        </is>
+      </c>
+      <c r="B55" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C55" s="19" t="inlineStr">
+        <is>
+          <t>Frontend: API клиент activity.ts</t>
+        </is>
+      </c>
+      <c r="D55" s="19" t="inlineStr">
+        <is>
+          <t>API клиент для аналитики пользователей: getActivityUsers, getUserActivity, getUserWorktime, getUserApps, getUserDomains, getUserTimesheet. Используется ingestApiClient. URL-encode username в path.</t>
+        </is>
+      </c>
+      <c r="E55" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F55" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G55" s="19" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="H55" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I55" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1" s="15">
+      <c r="A56" s="18" t="inlineStr">
+        <is>
+          <t>T-051</t>
+        </is>
+      </c>
+      <c r="B56" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C56" s="19" t="inlineStr">
+        <is>
+          <t>Frontend: Sidebar — Архив с подменю Устройства и Пользователи</t>
+        </is>
+      </c>
+      <c r="D56" s="19" t="inlineStr">
+        <is>
+          <t>Переделать пункт Архив записей в раскрывающуюся группу Архив. Подпункты: Устройства → /recordings (существующий DeviceGridPage), Пользователи → /activity/users (новый UserActivityListPage). Для обоих навигаций (superAdmin и tenantScoped).</t>
+        </is>
+      </c>
+      <c r="E56" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F56" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G56" s="19" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="H56" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I56" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1" s="15">
+      <c r="A57" s="18" t="inlineStr">
+        <is>
+          <t>T-052</t>
+        </is>
+      </c>
+      <c r="B57" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C57" s="19" t="inlineStr">
+        <is>
+          <t>Frontend: UserActivityListPage — список пользователей устройств</t>
+        </is>
+      </c>
+      <c r="D57" s="19" t="inlineStr">
+        <is>
+          <t>Страница /activity/users. Таблица с колонками: username, display_name, device_count, last_seen_ts, today active time. Поиск по username/display_name. Пагинация. Клик → переход на /activity/users/:username. Permission: RECORDINGS:READ.</t>
+        </is>
+      </c>
+      <c r="E57" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F57" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G57" s="19" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="H57" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I57" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1" s="15">
+      <c r="A58" s="18" t="inlineStr">
+        <is>
+          <t>T-053</t>
+        </is>
+      </c>
+      <c r="B58" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C58" s="19" t="inlineStr">
+        <is>
+          <t>Frontend: UserActivityDetailPage — страница с табами отчетов</t>
+        </is>
+      </c>
+      <c r="D58" s="19" t="inlineStr">
+        <is>
+          <t>Страница /activity/users/:username. 5 табов: Обзор (сводка, top apps, top domains), Рабочее время (приход/уход, опоздания), Приложения (таблица с временем по процессам), Веб-сайты (таблица с временем по доменам), Табель (календарная сетка за месяц). DateRangePicker для выбора периода. Ссылка на видеозапись по timestamp.</t>
+        </is>
+      </c>
+      <c r="E58" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F58" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G58" s="19" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="H58" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I58" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1" s="15">
+      <c r="A59" s="18" t="inlineStr">
+        <is>
+          <t>T-054</t>
+        </is>
+      </c>
+      <c r="B59" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C59" s="19" t="inlineStr">
+        <is>
+          <t>Frontend: компонент TimesheetReport — табель за месяц</t>
+        </is>
+      </c>
+      <c r="D59" s="19" t="inlineStr">
+        <is>
+          <t>Компонент TimesheetReport.tsx. Календарная сетка: дата, день недели, приход, уход, часы, сверхурочные, статус. Цветовая индикация: зеленый (норма), желтый (опоздание), красный (отсутствие). Итоговая строка с суммой часов.</t>
+        </is>
+      </c>
+      <c r="E59" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F59" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G59" s="19" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="H59" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I59" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1" s="15">
+      <c r="A60" s="18" t="inlineStr">
+        <is>
+          <t>T-055</t>
+        </is>
+      </c>
+      <c r="B60" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C60" s="19" t="inlineStr">
+        <is>
+          <t>Frontend: компоненты AppUsageChart, DomainUsageChart</t>
+        </is>
+      </c>
+      <c r="D60" s="19" t="inlineStr">
+        <is>
+          <t>Визуальные компоненты для отображения времени по приложениям и доменам. Горизонтальные bar charts с процентами. AppUsageChart: process_name, duration, %. DomainUsageChart: domain, browser, duration, %. Tailwind CSS, без внешних библиотек для графиков.</t>
+        </is>
+      </c>
+      <c r="E60" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F60" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G60" s="19" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="H60" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I60" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1" s="15">
+      <c r="A61" s="18" t="inlineStr">
+        <is>
+          <t>T-056</t>
+        </is>
+      </c>
+      <c r="B61" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C61" s="19" t="inlineStr">
+        <is>
+          <t>Frontend: маршруты в App.tsx для /activity/users</t>
+        </is>
+      </c>
+      <c r="D61" s="19" t="inlineStr">
+        <is>
+          <t>Добавить в App.tsx: Route /activity/users → UserActivityListPage (ProtectedRoute RECORDINGS:READ), Route /activity/users/:username → UserActivityDetailPage (ProtectedRoute RECORDINGS:READ). Import новых страниц.</t>
+        </is>
+      </c>
+      <c r="E61" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F61" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G61" s="19" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="H61" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I61" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1" s="15">
+      <c r="A62" s="18" t="inlineStr">
+        <is>
+          <t>T-057</t>
+        </is>
+      </c>
+      <c r="B62" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C62" s="19" t="inlineStr">
+        <is>
+          <t>Unit-тесты FocusIntervalService</t>
+        </is>
+      </c>
+      <c r="D62" s="19" t="inlineStr">
+        <is>
+          <t>JUnit тесты: batch submit с дедупликацией, валидация timestamps, device_id mismatch, batch size &gt; 100, upsert device_user_sessions.</t>
+        </is>
+      </c>
+      <c r="E62" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F62" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G62" s="19" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H62" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I62" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1" s="15">
+      <c r="A63" s="18" t="inlineStr">
+        <is>
+          <t>T-058</t>
+        </is>
+      </c>
+      <c r="B63" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C63" s="19" t="inlineStr">
+        <is>
+          <t>Unit-тесты UserActivityService</t>
+        </is>
+      </c>
+      <c r="D63" s="19" t="inlineStr">
+        <is>
+          <t>JUnit тесты: агрегатные запросы activity/worktime/apps/domains/timesheet. Проверка tenant isolation. Проверка расчетов рабочего времени (опоздания, ранние уходы, overtime).</t>
+        </is>
+      </c>
+      <c r="E63" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F63" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G63" s="19" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H63" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I63" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1" s="15">
+      <c r="A64" s="18" t="inlineStr">
+        <is>
+          <t>T-059</t>
+        </is>
+      </c>
+      <c r="B64" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C64" s="19" t="inlineStr">
+        <is>
+          <t>Unit-тесты BrowserDomainParser (все браузеры, edge cases)</t>
+        </is>
+      </c>
+      <c r="D64" s="19" t="inlineStr">
+        <is>
+          <t>NUnit/xUnit тесты: парсинг заголовков Chrome, Edge, Firefox, Opera, Yandex Browser. Edge cases: пустой заголовок, инкогнито, отсутствие домена в title, кириллица, Unicode символы в разделителях.</t>
+        </is>
+      </c>
+      <c r="E64" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F64" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G64" s="19" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="H64" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I64" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1" s="15">
+      <c r="A65" s="18" t="inlineStr">
+        <is>
+          <t>T-060</t>
+        </is>
+      </c>
+      <c r="B65" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C65" s="19" t="inlineStr">
+        <is>
+          <t>E2E тест: agent → focus intervals → server → UI отчеты</t>
+        </is>
+      </c>
+      <c r="D65" s="19" t="inlineStr">
+        <is>
+          <t>E2E сценарий: агент отправляет фокус-интервалы и audit events с username → ingest-gateway сохраняет → UI отображает пользователя в списке → детальные отчеты по приложениям/доменам/рабочему времени корректны. Проверка tenant isolation.</t>
+        </is>
+      </c>
+      <c r="E65" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F65" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G65" s="19" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="H65" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I65" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1" s="15">
+      <c r="A66" s="18" t="inlineStr">
+        <is>
+          <t>T-061</t>
+        </is>
+      </c>
+      <c r="B66" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C66" s="19" t="inlineStr">
+        <is>
+          <t>Деплой User Activity Tracking на test стейджинг</t>
+        </is>
+      </c>
+      <c r="D66" s="19" t="inlineStr">
+        <is>
+          <t>Полный деплой фичи user-activity-tracking: V29 миграция на PostgreSQL, пересборка ingest-gateway, пересборка web-dashboard, пересборка windows-agent. Smoke test на test стейджинге.</t>
+        </is>
+      </c>
+      <c r="E66" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F66" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G66" s="19" t="inlineStr">
+        <is>
+          <t>DevOps</t>
+        </is>
+      </c>
+      <c r="H66" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I66" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
         </is>
       </c>
     </row>
@@ -2253,7 +3580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="15" min="1" max="1"/>
@@ -3194,48 +4521,52 @@
       </c>
     </row>
     <row r="22" ht="50" customHeight="1" s="15">
-      <c r="A22" s="20" t="inlineStr">
+      <c r="A22" s="22" t="inlineStr">
         <is>
           <t>TC-017</t>
         </is>
       </c>
-      <c r="B22" s="20" t="inlineStr">
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>Mail.ru OAuth</t>
         </is>
       </c>
-      <c r="C22" s="21" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>Redirect на Mail.ru при нажатии кнопки</t>
         </is>
       </c>
-      <c r="D22" s="21" t="inlineStr">
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>auth-service запущен, Mail.ru client_id настроен</t>
         </is>
       </c>
-      <c r="E22" s="20" t="inlineStr">
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>1. Открыть /login\n2. Нажать кнопку Войти через Mail.ru\n3. Проверить что browser redirect на https://oauth.mail.ru/login с правильными params</t>
         </is>
       </c>
-      <c r="F22" s="20" t="inlineStr">
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>302 redirect на oauth.mail.ru с response_type=code, client_id, redirect_uri, scope=userinfo, state</t>
         </is>
       </c>
-      <c r="G22" s="21" t="inlineStr"/>
-      <c r="H22" s="20" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="I22" s="20" t="inlineStr">
+      <c r="G22" s="23" t="inlineStr">
+        <is>
+          <t>302 redirect на https://oauth.mail.ru/login?response_type=code&amp;client_id=791475&amp;redirect_uri=...&amp;scope=userinfo&amp;state=&lt;UUID&gt;. Все параметры корректны.</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
         <is>
           <t>T-026</t>
         </is>
       </c>
-      <c r="J22" s="21" t="inlineStr">
+      <c r="J22" s="23" t="inlineStr">
         <is>
           <t>07.03.2026</t>
         </is>
@@ -3272,7 +4603,11 @@
           <t>Создан новый tenant, user с auth_provider=oauth, user_oauth_links с provider=mailru. Redirect на главную страницу.</t>
         </is>
       </c>
-      <c r="G23" s="21" t="inlineStr"/>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>Требует ручного прохождения полного OAuth flow через браузер (real Mail.ru аккаунт). Инфраструктура готова: redirect, state validation, callback endpoint работают.</t>
+        </is>
+      </c>
       <c r="H23" s="20" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -3320,7 +4655,11 @@
           <t>Автоматический вход в систему, redirect на главную страницу. access_token и refresh_token установлены.</t>
         </is>
       </c>
-      <c r="G24" s="21" t="inlineStr"/>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>Требует ручного повторного логина через Mail.ru OAuth. Инфраструктура готова.</t>
+        </is>
+      </c>
       <c r="H24" s="20" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -3338,48 +4677,52 @@
       </c>
     </row>
     <row r="25" ht="50" customHeight="1" s="15">
-      <c r="A25" s="20" t="inlineStr">
+      <c r="A25" s="22" t="inlineStr">
         <is>
           <t>TC-020</t>
         </is>
       </c>
-      <c r="B25" s="20" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>Mail.ru OAuth</t>
         </is>
       </c>
-      <c r="C25" s="21" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>OAuth callback: ошибка авторизации -&gt; redirect to login</t>
         </is>
       </c>
-      <c r="D25" s="21" t="inlineStr">
+      <c r="D25" s="23" t="inlineStr">
         <is>
           <t>auth-service запущен</t>
         </is>
       </c>
-      <c r="E25" s="20" t="inlineStr">
+      <c r="E25" s="22" t="inlineStr">
         <is>
           <t>1. Вызвать GET /api/v1/auth/oauth/mailru/callback?error=access_denied\n2. Проверить redirect</t>
         </is>
       </c>
-      <c r="F25" s="20" t="inlineStr">
+      <c r="F25" s="22" t="inlineStr">
         <is>
           <t>Redirect на /login?error=OAuth+authorization+denied</t>
         </is>
       </c>
-      <c r="G25" s="21" t="inlineStr"/>
-      <c r="H25" s="20" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="I25" s="20" t="inlineStr">
+      <c r="G25" s="23" t="inlineStr">
+        <is>
+          <t>302 redirect на /login?error=Authentication+failed. State validation отклоняет невалидный state. Логи: InvalidCredentialsException: Invalid or expired OAuth state parameter. Сервер НЕ обращается к Mail.ru API.</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I25" s="22" t="inlineStr">
         <is>
           <t>T-026</t>
         </is>
       </c>
-      <c r="J25" s="21" t="inlineStr">
+      <c r="J25" s="23" t="inlineStr">
         <is>
           <t>07.03.2026</t>
         </is>
@@ -3416,7 +4759,11 @@
           <t>Две разные записи в oauth_identities: одна с provider=yandex, вторая с provider=mailru. Разные user_oauth_links, потенциально разные tenants.</t>
         </is>
       </c>
-      <c r="G26" s="21" t="inlineStr"/>
+      <c r="G26" s="21" t="inlineStr">
+        <is>
+          <t>Требует два OAuth-аккаунта (Yandex + Mail.ru) с одинаковым email. Ручное тестирование.</t>
+        </is>
+      </c>
       <c r="H26" s="20" t="inlineStr">
         <is>
           <t>Pending</t>
@@ -3434,48 +4781,572 @@
       </c>
     </row>
     <row r="27" ht="50" customHeight="1" s="15">
-      <c r="A27" s="20" t="inlineStr">
+      <c r="A27" s="22" t="inlineStr">
         <is>
           <t>TC-022</t>
         </is>
       </c>
-      <c r="B27" s="20" t="inlineStr">
+      <c r="B27" s="22" t="inlineStr">
         <is>
           <t>Mail.ru OAuth</t>
         </is>
       </c>
-      <c r="C27" s="21" t="inlineStr">
+      <c r="C27" s="23" t="inlineStr">
         <is>
           <t>Frontend: кнопка Mail.ru отображается на LoginPage</t>
         </is>
       </c>
-      <c r="D27" s="21" t="inlineStr">
+      <c r="D27" s="23" t="inlineStr">
         <is>
           <t>web-dashboard запущен</t>
         </is>
       </c>
-      <c r="E27" s="20" t="inlineStr">
+      <c r="E27" s="22" t="inlineStr">
         <is>
           <t>1. Открыть /login\n2. Проверить наличие кнопки Войти через Mail.ru\n3. Проверить цвет кнопки (#005FF9)\n4. Проверить наличие иконки Mail.ru</t>
         </is>
       </c>
-      <c r="F27" s="20" t="inlineStr">
+      <c r="F27" s="22" t="inlineStr">
         <is>
           <t>Кнопка Войти через Mail.ru отображается под кнопкой Яндекс, синего цвета, с иконкой.</t>
         </is>
       </c>
-      <c r="G27" s="21" t="inlineStr"/>
-      <c r="H27" s="20" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="I27" s="20" t="inlineStr">
+      <c r="G27" s="23" t="inlineStr">
+        <is>
+          <t>JS-бандл содержит: Mail.ru (1), #005FF9 (2), oauth/mailru (1). Кнопка присутствует.</t>
+        </is>
+      </c>
+      <c r="H27" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I27" s="22" t="inlineStr">
         <is>
           <t>T-028</t>
         </is>
       </c>
-      <c r="J27" s="21" t="inlineStr">
+      <c r="J27" s="23" t="inlineStr">
+        <is>
+          <t>07.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="50" customHeight="1" s="15">
+      <c r="A28" s="22" t="inlineStr">
+        <is>
+          <t>TC-023</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>Mail.ru OAuth</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>Mail.ru callback с невалидным code и state</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="inlineStr">
+        <is>
+          <t>Mail.ru OAuth задеплоен на test</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>1. Отправить GET /api/v1/auth/oauth/mailru/callback?code=invalid_code&amp;state=invalid_state</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>Redirect на frontend с ошибкой (302) или 400. НЕ 500. State validation должен отклонить запрос.</t>
+        </is>
+      </c>
+      <c r="G28" s="23" t="inlineStr">
+        <is>
+          <t>302 redirect на /login?error=Authentication+failed. State validation корректно отклоняет invalid_state. x-correlation-id присутствует. НЕ 500.</t>
+        </is>
+      </c>
+      <c r="H28" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I28" s="22" t="inlineStr">
+        <is>
+          <t>T-026</t>
+        </is>
+      </c>
+      <c r="J28" s="23" t="inlineStr">
+        <is>
+          <t>07.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="50" customHeight="1" s="15">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>TC-024</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>Mail.ru OAuth</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>Mail.ru callback без state parameter</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="inlineStr">
+        <is>
+          <t>Mail.ru OAuth задеплоен на test</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>1. Отправить GET /api/v1/auth/oauth/mailru/callback?code=test_code (без state)</t>
+        </is>
+      </c>
+      <c r="F29" s="22" t="inlineStr">
+        <is>
+          <t>400 или redirect с ошибкой (invalid state)</t>
+        </is>
+      </c>
+      <c r="G29" s="23" t="inlineStr">
+        <is>
+          <t>302 redirect на /login?error=Authentication+failed. Без state parameter сервер корректно отклоняет запрос. НЕ 500.</t>
+        </is>
+      </c>
+      <c r="H29" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I29" s="22" t="inlineStr">
+        <is>
+          <t>T-026</t>
+        </is>
+      </c>
+      <c r="J29" s="23" t="inlineStr">
+        <is>
+          <t>07.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="50" customHeight="1" s="15">
+      <c r="A30" s="22" t="inlineStr">
+        <is>
+          <t>TC-025</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>Mail.ru OAuth</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>Yandex callback с невалидным state (CSRF protection)</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="inlineStr">
+        <is>
+          <t>Yandex OAuth работает на test</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>1. Отправить GET /api/v1/auth/oauth/yandex/callback?code=test_code&amp;state=fake_state_12345</t>
+        </is>
+      </c>
+      <c r="F30" s="22" t="inlineStr">
+        <is>
+          <t>400 или redirect с ошибкой state validation. НЕ должен пытаться обменять code на token.</t>
+        </is>
+      </c>
+      <c r="G30" s="23" t="inlineStr">
+        <is>
+          <t>302 redirect на /login?error=Authentication+failed. Yandex callback тоже проходит state validation (OAuthService.validateState). CSRF protection работает для обоих провайдеров.</t>
+        </is>
+      </c>
+      <c r="H30" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I30" s="22" t="inlineStr">
+        <is>
+          <t>T-026</t>
+        </is>
+      </c>
+      <c r="J30" s="23" t="inlineStr">
+        <is>
+          <t>07.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="50" customHeight="1" s="15">
+      <c r="A31" s="22" t="inlineStr">
+        <is>
+          <t>TC-026</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>Mail.ru OAuth</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="inlineStr">
+        <is>
+          <t>Rate limiting на callback endpoint</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="inlineStr">
+        <is>
+          <t>Mail.ru OAuth задеплоен на test</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>1. Отправить 15 запросов подряд на /api/v1/auth/oauth/mailru/callback с разными code/state</t>
+        </is>
+      </c>
+      <c r="F31" s="22" t="inlineStr">
+        <is>
+          <t>Первые ~10 запросов: 302/400 (state invalid), после 10-го: 429 (rate limited)</t>
+        </is>
+      </c>
+      <c r="G31" s="23" t="inlineStr">
+        <is>
+          <t>Первые 7 запросов: 302 (state invalid redirect), запросы 8-15: 429 (rate limit). OAuthRateLimiter: key=oauth-callback:IP, лимит ~7 за окно.</t>
+        </is>
+      </c>
+      <c r="H31" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I31" s="22" t="inlineStr">
+        <is>
+          <t>T-026</t>
+        </is>
+      </c>
+      <c r="J31" s="23" t="inlineStr">
+        <is>
+          <t>07.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="50" customHeight="1" s="15">
+      <c r="A32" s="22" t="inlineStr">
+        <is>
+          <t>TC-027</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>Mail.ru OAuth</t>
+        </is>
+      </c>
+      <c r="C32" s="23" t="inlineStr">
+        <is>
+          <t>Rate limiting на onboarding endpoint</t>
+        </is>
+      </c>
+      <c r="D32" s="23" t="inlineStr">
+        <is>
+          <t>Mail.ru OAuth задеплоен на test</t>
+        </is>
+      </c>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>1. Отправить 8 запросов подряд POST на /api/v1/auth/oauth/onboarding</t>
+        </is>
+      </c>
+      <c r="F32" s="22" t="inlineStr">
+        <is>
+          <t>Первые ~5: 401 (no token), после 5-го: 429 (rate limited)</t>
+        </is>
+      </c>
+      <c r="G32" s="23" t="inlineStr">
+        <is>
+          <t>С полным payload: первые 5 запросов - 401 (OAUTH_TOKEN_MISSING), запросы 6-8: 429 (TOO_MANY_REQUESTS). Rate limit работает. Примечание: без company_name (400 VALIDATION_ERROR) rate limit не срабатывает - валидация body раньше rate limiter.</t>
+        </is>
+      </c>
+      <c r="H32" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I32" s="22" t="inlineStr">
+        <is>
+          <t>T-026</t>
+        </is>
+      </c>
+      <c r="J32" s="23" t="inlineStr">
+        <is>
+          <t>07.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="50" customHeight="1" s="15">
+      <c r="A33" s="22" t="inlineStr">
+        <is>
+          <t>TC-028</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>Mail.ru OAuth</t>
+        </is>
+      </c>
+      <c r="C33" s="23" t="inlineStr">
+        <is>
+          <t>receiver.html доступен и содержит connect.mail.ru</t>
+        </is>
+      </c>
+      <c r="D33" s="23" t="inlineStr">
+        <is>
+          <t>web-dashboard задеплоен на test</t>
+        </is>
+      </c>
+      <c r="E33" s="22" t="inlineStr">
+        <is>
+          <t>1. GET https://services-test.shepaland.ru/receiver.html\n2. Проверить наличие connect.mail.ru в теле</t>
+        </is>
+      </c>
+      <c r="F33" s="22" t="inlineStr">
+        <is>
+          <t>200, содержит connect.mail.ru</t>
+        </is>
+      </c>
+      <c r="G33" s="23" t="inlineStr">
+        <is>
+          <t>200 OK. receiver.html содержит connect.mail.ru/js/loader.js и mailru.receiver.init(). Файл доступен по корневому пути (не под /screenrecorder).</t>
+        </is>
+      </c>
+      <c r="H33" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I33" s="22" t="inlineStr">
+        <is>
+          <t>T-028</t>
+        </is>
+      </c>
+      <c r="J33" s="23" t="inlineStr">
+        <is>
+          <t>07.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="50" customHeight="1" s="15">
+      <c r="A34" s="22" t="inlineStr">
+        <is>
+          <t>TC-029</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>Mail.ru OAuth</t>
+        </is>
+      </c>
+      <c r="C34" s="23" t="inlineStr">
+        <is>
+          <t>Health check auth-service после тестов</t>
+        </is>
+      </c>
+      <c r="D34" s="23" t="inlineStr">
+        <is>
+          <t>auth-service задеплоен на test</t>
+        </is>
+      </c>
+      <c r="E34" s="22" t="inlineStr">
+        <is>
+          <t>1. GET /api/actuator/health или /api/v1/auth/health</t>
+        </is>
+      </c>
+      <c r="F34" s="22" t="inlineStr">
+        <is>
+          <t>200, {"status":"UP"}</t>
+        </is>
+      </c>
+      <c r="G34" s="23" t="inlineStr">
+        <is>
+          <t>ClusterIP: {status:UP, groups:[liveness,readiness]}. Через внешний URL /api/actuator/health возвращает 401 (требует auth) - это by design, actuator защищен.</t>
+        </is>
+      </c>
+      <c r="H34" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I34" s="22" t="inlineStr">
+        <is>
+          <t>T-030</t>
+        </is>
+      </c>
+      <c r="J34" s="23" t="inlineStr">
+        <is>
+          <t>07.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="50" customHeight="1" s="15">
+      <c r="A35" s="22" t="inlineStr">
+        <is>
+          <t>TC-030</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>Mail.ru OAuth</t>
+        </is>
+      </c>
+      <c r="C35" s="23" t="inlineStr">
+        <is>
+          <t>Логин superadmin по-прежнему работает (регрессия)</t>
+        </is>
+      </c>
+      <c r="D35" s="23" t="inlineStr">
+        <is>
+          <t>auth-service задеплоен на test</t>
+        </is>
+      </c>
+      <c r="E35" s="22" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/auth/login с superadmin/Admin@12345</t>
+        </is>
+      </c>
+      <c r="F35" s="22" t="inlineStr">
+        <is>
+          <t>200, JSON с access_token</t>
+        </is>
+      </c>
+      <c r="G35" s="23" t="inlineStr">
+        <is>
+          <t>200, access_token получен, user=superadmin, role=SUPER_ADMIN, 33 permissions. Логин superadmin работает корректно после деплоя Mail.ru OAuth.</t>
+        </is>
+      </c>
+      <c r="H35" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I35" s="22" t="inlineStr">
+        <is>
+          <t>T-030</t>
+        </is>
+      </c>
+      <c r="J35" s="23" t="inlineStr">
+        <is>
+          <t>07.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="50" customHeight="1" s="15">
+      <c r="A36" s="22" t="inlineStr">
+        <is>
+          <t>TC-031</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>Mail.ru OAuth</t>
+        </is>
+      </c>
+      <c r="C36" s="23" t="inlineStr">
+        <is>
+          <t>Yandex OAuth redirect по-прежнему работает (регрессия)</t>
+        </is>
+      </c>
+      <c r="D36" s="23" t="inlineStr">
+        <is>
+          <t>auth-service задеплоен на test</t>
+        </is>
+      </c>
+      <c r="E36" s="22" t="inlineStr">
+        <is>
+          <t>1. GET /api/v1/auth/oauth/yandex\n2. Проверить 302 redirect на oauth.yandex.ru</t>
+        </is>
+      </c>
+      <c r="F36" s="22" t="inlineStr">
+        <is>
+          <t>302, redirect на https://oauth.yandex.ru/authorize?...</t>
+        </is>
+      </c>
+      <c r="G36" s="23" t="inlineStr">
+        <is>
+          <t>302 redirect на https://oauth.yandex.ru/authorize?response_type=code&amp;client_id=a655b3c89f49442abaa119309c6fe04c&amp;redirect_uri=...&amp;state=&lt;UUID&gt;. Yandex OAuth не сломан.</t>
+        </is>
+      </c>
+      <c r="H36" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I36" s="22" t="inlineStr">
+        <is>
+          <t>T-030</t>
+        </is>
+      </c>
+      <c r="J36" s="23" t="inlineStr">
+        <is>
+          <t>07.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="50" customHeight="1" s="15">
+      <c r="A37" s="22" t="inlineStr">
+        <is>
+          <t>TC-032</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="inlineStr">
+        <is>
+          <t>Mail.ru OAuth</t>
+        </is>
+      </c>
+      <c r="C37" s="23" t="inlineStr">
+        <is>
+          <t>Логи auth-service: нет неожиданных ошибок после тестов</t>
+        </is>
+      </c>
+      <c r="D37" s="23" t="inlineStr">
+        <is>
+          <t>auth-service задеплоен на test, тесты прогнаны</t>
+        </is>
+      </c>
+      <c r="E37" s="22" t="inlineStr">
+        <is>
+          <t>1. Проверить kubectl logs auth-service --tail=100\n2. grep error/exception/fail\n3. Отфильтровать ожидаемые ошибки (state validation, rate limit)</t>
+        </is>
+      </c>
+      <c r="F37" s="22" t="inlineStr">
+        <is>
+          <t>Нет неожиданных ошибок</t>
+        </is>
+      </c>
+      <c r="G37" s="23" t="inlineStr">
+        <is>
+          <t>Логи содержат только ожидаемые ошибки от тестов: Invalid or expired OAuth state (наши тесты), Rate limit exceeded (наши тесты), Validation error: Company name required (наши тесты), OAuth token is required (наши тесты). Нет неожиданных исключений.</t>
+        </is>
+      </c>
+      <c r="H37" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I37" s="22" t="inlineStr">
+        <is>
+          <t>T-030</t>
+        </is>
+      </c>
+      <c r="J37" s="23" t="inlineStr">
         <is>
           <t>07.03.2026</t>
         </is>

--- a/docs/tracker.xlsx
+++ b/docs/tracker.xlsx
@@ -50,7 +50,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -117,6 +117,11 @@
         <fgColor rgb="00FFF0F0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0E0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -159,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -232,6 +237,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -599,7 +610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I113"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="15" min="1" max="1"/>
@@ -3566,6 +3577,2215 @@
         </is>
       </c>
     </row>
+    <row r="67" ht="20" customHeight="1" s="15">
+      <c r="A67" s="24" t="inlineStr">
+        <is>
+          <t>T-062</t>
+        </is>
+      </c>
+      <c r="B67" s="24" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="C67" s="25" t="inlineStr">
+        <is>
+          <t>GET /users/{username}/*: Tomcat блокирует backslash в URL path для DOMAIN\user</t>
+        </is>
+      </c>
+      <c r="D67" s="25" t="inlineStr">
+        <is>
+          <t>Описание: Все GET endpoints UserActivityController используют {username} как path variable. Для Windows domain usernames формата DOMAIN\user (например TESTCORP\ivanov.a) backslash кодируется как %5C в URL. Tomcat по умолчанию блокирует encoded backslash в URL path и возвращает 400 Bad Request. Double-encoding (%255C) проходит, но сервер получает literal '%5Civanov.a' вместо '\ivanov.a', и данные не находятся. Это делает невозможным получение activity/apps/domains/worktime/timesheet для пользователей с Windows domain prefix.\n\nШаги воспроизведения:\n1. POST focus-intervals с username='TESTCORP\ivanov.a' — успешно (200)\n2. GET /users — возвращает username='TESTCORP\ivanov.a' — OK\n3. GET /users/TESTCORP%5Civanov.a/activity — Tomcat 400 Bad Request\n4. GET /users/TESTCORP%255Civanov.a/activity — 200, но данные пустые (username не совпадает)\n\nОжидаемый результат: Возможность получения данных для username с backslash.\n\nВарианты решения:\n1. Добавить server.tomcat.relaxed-path-chars=\,| в application.yml\n2. Передавать username через query parameter вместо path variable\n3. Использовать base64 encoding для username в URL</t>
+        </is>
+      </c>
+      <c r="E67" s="24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F67" s="24" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G67" s="25" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H67" s="24" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I67" s="24" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1" s="15">
+      <c r="A68" s="24" t="inlineStr">
+        <is>
+          <t>T-063</t>
+        </is>
+      </c>
+      <c r="B68" s="24" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="C68" s="25" t="inlineStr">
+        <is>
+          <t>GET /users/activity без username возвращает 500 вместо 400</t>
+        </is>
+      </c>
+      <c r="D68" s="25" t="inlineStr">
+        <is>
+          <t>Среда: test (services-test.shepaland.ru)\nEndpoint: GET /api/ingest/v1/ingest/users/activity\nШаги: 1) Авторизоваться как superadmin 2) Отправить GET запрос без параметра username, но с from и to\nВходные данные: GET /api/ingest/v1/ingest/users/activity?from=2026-03-01T00:00:00Z&amp;to=2026-03-08T23:59:59Z\nОжидаемый результат: HTTP 400 с сообщением 'Required parameter username is missing'\nФактический результат: HTTP 500 {"error":"Internal server error","code":"INTERNAL_ERROR"}\nПричина: Spring не обрабатывает MissingServletRequestParameterException — вероятно, параметр username объявлен как @RequestParam(required=true) но глобальный обработчик исключений не перехватывает MissingServletRequestParameterException, либо username не помечен как required и передается как null, что вызывает NullPointerException.</t>
+        </is>
+      </c>
+      <c r="E68" s="24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F68" s="24" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G68" s="25" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H68" s="24" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I68" s="24" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1" s="15">
+      <c r="A69" s="18" t="inlineStr">
+        <is>
+          <t>T-064</t>
+        </is>
+      </c>
+      <c r="B69" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C69" s="19" t="inlineStr">
+        <is>
+          <t>Повторный просмотр токена: backend endpoint GET /api/v1/device-tokens/{id}/reveal</t>
+        </is>
+      </c>
+      <c r="D69" s="19" t="inlineStr">
+        <is>
+          <t>Добавить endpoint для повторного просмотра raw-значения токена. Доступен только ролям OWNER, TENANT_ADMIN, SUPER_ADMIN. Требует пересмотра архитектуры хранения токенов (сейчас хранится только hash). Варианты: 1) хранить encrypted raw token, 2) regenerate token. Аудит операции обязателен.</t>
+        </is>
+      </c>
+      <c r="E69" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F69" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G69" s="19" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H69" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I69" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1" s="15">
+      <c r="A70" s="18" t="inlineStr">
+        <is>
+          <t>T-065</t>
+        </is>
+      </c>
+      <c r="B70" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C70" s="19" t="inlineStr">
+        <is>
+          <t>V29 миграция: добавить encrypted_token в device_registration_tokens</t>
+        </is>
+      </c>
+      <c r="D70" s="19" t="inlineStr">
+        <is>
+          <t>Flyway миграция V29: ALTER TABLE device_registration_tokens ADD COLUMN encrypted_token TEXT. Для поддержки повторного просмотра токена. Шифрование AES-256-GCM с ключом из конфигурации. Бэкфил для существующих записей невозможен (raw token утрачен).</t>
+        </is>
+      </c>
+      <c r="E70" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F70" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G70" s="19" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H70" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I70" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1" s="15">
+      <c r="A71" s="18" t="inlineStr">
+        <is>
+          <t>T-066</t>
+        </is>
+      </c>
+      <c r="B71" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C71" s="19" t="inlineStr">
+        <is>
+          <t>Повторный просмотр токена: frontend UI кнопка 'Показать токен'</t>
+        </is>
+      </c>
+      <c r="D71" s="19" t="inlineStr">
+        <is>
+          <t>Добавить кнопку 'Показать токен' на странице DeviceTokensListPage в колонке 'Действия'. Видима только для ролей OWNER/TENANT_ADMIN/SUPER_ADMIN. При клике — вызов API reveal, показ в модальном окне с возможностью копирования. Ограничить видимость по роли, а не по пермишену.</t>
+        </is>
+      </c>
+      <c r="E71" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F71" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G71" s="19" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="H71" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I71" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1" s="15">
+      <c r="A72" s="18" t="inlineStr">
+        <is>
+          <t>T-067</t>
+        </is>
+      </c>
+      <c r="B72" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C72" s="19" t="inlineStr">
+        <is>
+          <t>Удаление токена: физическое удаление (hard delete) device_registration_token</t>
+        </is>
+      </c>
+      <c r="D72" s="19" t="inlineStr">
+        <is>
+          <t>Расширить DeviceTokenService: метод hardDeleteToken(). DELETE /api/v1/device-tokens/{id} с query param ?hard=true. Проверка: нет связанных активных устройств. Доступно только OWNER/TENANT_ADMIN/SUPER_ADMIN. Аудит DEVICE_TOKEN_DELETED. Каскадное обнуление registration_token_id у привязанных devices.</t>
+        </is>
+      </c>
+      <c r="E72" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F72" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G72" s="19" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H72" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I72" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1" s="15">
+      <c r="A73" s="18" t="inlineStr">
+        <is>
+          <t>T-068</t>
+        </is>
+      </c>
+      <c r="B73" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C73" s="19" t="inlineStr">
+        <is>
+          <t>Удаление токена: frontend UI кнопка 'Удалить' с подтверждением</t>
+        </is>
+      </c>
+      <c r="D73" s="19" t="inlineStr">
+        <is>
+          <t>Добавить кнопку 'Удалить' рядом с 'Деактивировать' на DeviceTokensListPage. Видима только OWNER/TENANT_ADMIN/SUPER_ADMIN. ConfirmDialog с предупреждением о необратимости. Показывать количество привязанных устройств в диалоге подтверждения.</t>
+        </is>
+      </c>
+      <c r="E73" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F73" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G73" s="19" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="H73" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I73" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1" s="15">
+      <c r="A74" s="18" t="inlineStr">
+        <is>
+          <t>T-069</t>
+        </is>
+      </c>
+      <c r="B74" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C74" s="19" t="inlineStr">
+        <is>
+          <t>Удаление пользователей: физическое удаление (hard delete) user</t>
+        </is>
+      </c>
+      <c r="D74" s="19" t="inlineStr">
+        <is>
+          <t>Расширить UserService: метод hardDeleteUser(). DELETE /api/v1/users/{id}?hard=true. Каскадная очистка: user_roles, refresh_tokens, oauth_identities, device_registration_tokens.created_by (SET NULL). Запрет удаления самого себя и последнего OWNER. Доступно только OWNER/TENANT_ADMIN/SUPER_ADMIN. Аудит USER_DELETED.</t>
+        </is>
+      </c>
+      <c r="E74" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F74" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G74" s="19" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H74" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I74" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1" s="15">
+      <c r="A75" s="18" t="inlineStr">
+        <is>
+          <t>T-070</t>
+        </is>
+      </c>
+      <c r="B75" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C75" s="19" t="inlineStr">
+        <is>
+          <t>Удаление пользователей: frontend UI кнопка 'Удалить' в UserDetailPage</t>
+        </is>
+      </c>
+      <c r="D75" s="19" t="inlineStr">
+        <is>
+          <t>Добавить кнопку 'Удалить' (красная, с иконкой TrashIcon) рядом с 'Deactivate' на UserDetailPage. Видима только OWNER/TENANT_ADMIN/SUPER_ADMIN. ConfirmDialog с вводом username для подтверждения. Запрет удаления самого себя (кнопка скрыта/disabled).</t>
+        </is>
+      </c>
+      <c r="E75" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F75" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G75" s="19" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="H75" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I75" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1" s="15">
+      <c r="A76" s="18" t="inlineStr">
+        <is>
+          <t>T-071</t>
+        </is>
+      </c>
+      <c r="B76" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C76" s="19" t="inlineStr">
+        <is>
+          <t>Реорганизация sidebar: новая структура меню тенанта</t>
+        </is>
+      </c>
+      <c r="D76" s="19" t="inlineStr">
+        <is>
+          <t>Переделать Sidebar.tsx: структура меню тенанта: 1) Контрольная панель (/), 2) Аналитика (переименовать из 'Архив', подменю: Устройства, Пользователи), 3) Настройки (подменю: Устройства, Пользователи, Токены, Настройки записи). Убрать Скачать клиент из основного меню (перенести в Настройки или отдельный раздел).</t>
+        </is>
+      </c>
+      <c r="E76" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F76" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G76" s="19" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="H76" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I76" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1" s="15">
+      <c r="A77" s="18" t="inlineStr">
+        <is>
+          <t>T-072</t>
+        </is>
+      </c>
+      <c r="B77" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C77" s="19" t="inlineStr">
+        <is>
+          <t>Реорганизация sidebar: обновление superadmin меню</t>
+        </is>
+      </c>
+      <c r="D77" s="19" t="inlineStr">
+        <is>
+          <t>Обновить superAdminNavigation в Sidebar.tsx аналогично тенантному меню. Добавить раздел Настройки с подменю. Переименовать Архив в Аналитика. Сохранить доступ к Tenants и Audit в глобальном разделе.</t>
+        </is>
+      </c>
+      <c r="E77" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F77" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G77" s="19" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="H77" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I77" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1" s="15">
+      <c r="A78" s="18" t="inlineStr">
+        <is>
+          <t>T-073</t>
+        </is>
+      </c>
+      <c r="B78" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C78" s="19" t="inlineStr">
+        <is>
+          <t>Обновление маршрутов App.tsx под новую структуру меню</t>
+        </is>
+      </c>
+      <c r="D78" s="19" t="inlineStr">
+        <is>
+          <t>Обновить App.tsx: 1) /archive/* -&gt; /analytics/* с redirect /archive/* -&gt; /analytics/*, 2) /settings/devices -&gt; DevicesListPage, /settings/users -&gt; UsersListPage, /settings/tokens -&gt; DeviceTokensListPage, /settings/recording -&gt; RecordingSettingsPage. Добавить redirect для старых путей для обратной совместимости.</t>
+        </is>
+      </c>
+      <c r="E78" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F78" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G78" s="19" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="H78" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I78" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1" s="15">
+      <c r="A79" s="18" t="inlineStr">
+        <is>
+          <t>T-074</t>
+        </is>
+      </c>
+      <c r="B79" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C79" s="19" t="inlineStr">
+        <is>
+          <t>Добавить проверку роли (не пермишена) для admin-only операций</t>
+        </is>
+      </c>
+      <c r="D79" s="19" t="inlineStr">
+        <is>
+          <t>Создать backend-утилиту requireAdminRole(principal) проверяющую роль OWNER/TENANT_ADMIN/SUPER_ADMIN. Использовать в: reveal token, hard delete token, hard delete user. На frontend: создать хук useHasAdminRole() и компонент AdminRoleGate для проверки роли, а не пермишена.</t>
+        </is>
+      </c>
+      <c r="E79" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F79" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G79" s="19" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H79" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I79" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1" s="15">
+      <c r="A80" s="24" t="inlineStr">
+        <is>
+          <t>T-075</t>
+        </is>
+      </c>
+      <c r="B80" s="24" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="C80" s="25" t="inlineStr">
+        <is>
+          <t>SessionLogon не стартует запись после перелогина (Windows Agent)</t>
+        </is>
+      </c>
+      <c r="D80" s="25" t="inlineStr">
+        <is>
+          <t>SessionWatcher обрабатывает SessionLogon только как аудит-событие (break без вызова StartRecording). После логофа пользователя A и логона пользователя B агент остается в состоянии _isPausedByLock=true, запись не возобновляется. Необходимо: 1) Добавить HandleSessionLogonAsync в CommandHandler (сброс _isPausedByLock, вызов AutoStartRecordingAsync). 2) Вызвать его из SessionWatcher.OnSessionSwitch(SessionLogon).</t>
+        </is>
+      </c>
+      <c r="E80" s="24" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F80" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G80" s="25" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="H80" s="24" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I80" s="24" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1" s="15">
+      <c r="A81" s="24" t="inlineStr">
+        <is>
+          <t>T-076</t>
+        </is>
+      </c>
+      <c r="B81" s="24" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="C81" s="25" t="inlineStr">
+        <is>
+          <t>UserSessionInfo.cachedUsername не инвалидируется при SessionLogon</t>
+        </is>
+      </c>
+      <c r="D81" s="25" t="inlineStr">
+        <is>
+          <t>При перелогине под другим пользователем UserSessionInfo._cachedUsername остается от предыдущего пользователя. Аудит-события и focus-intervals отправляются с неверным username. Необходимо вызвать _userSessionInfo.InvalidateCache() при SessionLogon и обновить FocusIntervalSink.SetUsername().</t>
+        </is>
+      </c>
+      <c r="E81" s="24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F81" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G81" s="25" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="H81" s="24" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I81" s="24" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1" s="15">
+      <c r="A82" s="24" t="inlineStr">
+        <is>
+          <t>T-077</t>
+        </is>
+      </c>
+      <c r="B82" s="24" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="C82" s="25" t="inlineStr">
+        <is>
+          <t>ApiClient не делает auto-refresh JWT при 401 ответе</t>
+        </is>
+      </c>
+      <c r="D82" s="25" t="inlineStr">
+        <is>
+          <t>ApiClient.SendWithRetry ретраит только 503/504 и HttpRequestException. При получении 401 (token expired) -- вызывает EnsureSuccessStatusCode и бросает исключение, без попытки refresh. Необходимо: при 401 вызвать AuthManager.RefreshTokenAsync(), обновить заголовок Authorization и повторить запрос.</t>
+        </is>
+      </c>
+      <c r="E82" s="24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F82" s="24" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="G82" s="25" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="H82" s="24" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I82" s="24" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1" s="15">
+      <c r="A83" s="24" t="inlineStr">
+        <is>
+          <t>T-078</t>
+        </is>
+      </c>
+      <c r="B83" s="24" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="C83" s="25" t="inlineStr">
+        <is>
+          <t>ApiClient теряет response body при HTTP-ошибках</t>
+        </is>
+      </c>
+      <c r="D83" s="25" t="inlineStr">
+        <is>
+          <t>EnsureSuccessStatusCode() вызывается без предварительного чтения тела ответа. В логах видно только 'Response status code does not indicate success: 401', но JSON с error/code теряется. Необходимо: при не-2xx -- прочитать и залогировать body перед throw.</t>
+        </is>
+      </c>
+      <c r="E83" s="24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F83" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G83" s="25" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="H83" s="24" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I83" s="24" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1" s="15">
+      <c r="A84" s="18" t="inlineStr">
+        <is>
+          <t>T-079</t>
+        </is>
+      </c>
+      <c r="B84" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C84" s="19" t="inlineStr">
+        <is>
+          <t>SegmentUploader: обработка 404 как session expired (не ретраить)</t>
+        </is>
+      </c>
+      <c r="D84" s="19" t="inlineStr">
+        <is>
+          <t>При получении 404 на presign запрос (session закрыта или не найдена) -- SegmentUploader должен дискардить сегмент, а не ставить его в pending для бесконечного retry. Добавить catch (HttpRequestException ex) when (ex.StatusCode == 404) -&gt; return true.</t>
+        </is>
+      </c>
+      <c r="E84" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F84" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G84" s="19" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="H84" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I84" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1" s="15">
+      <c r="A85" s="18" t="inlineStr">
+        <is>
+          <t>T-080</t>
+        </is>
+      </c>
+      <c r="B85" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C85" s="19" t="inlineStr">
+        <is>
+          <t>SessionWatcher: добавить зависимость UserSessionInfo + FocusIntervalSink</t>
+        </is>
+      </c>
+      <c r="D85" s="19" t="inlineStr">
+        <is>
+          <t>Для корректной работы при SessionLogon необходимо инжектировать UserSessionInfo и FocusIntervalSink в SessionWatcher. Обновить конструктор SessionWatcher, DI регистрацию в Program.cs.</t>
+        </is>
+      </c>
+      <c r="E85" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F85" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G85" s="19" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="H85" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I85" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1" s="15">
+      <c r="A86" s="24" t="inlineStr">
+        <is>
+          <t>T-081</t>
+        </is>
+      </c>
+      <c r="B86" s="24" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="C86" s="25" t="inlineStr">
+        <is>
+          <t>Не отображается статистика посещения сайтов: BrowserDomainParser не извлекает домен из title</t>
+        </is>
+      </c>
+      <c r="D86" s="25" t="inlineStr">
+        <is>
+          <t>BrowserDomainParser.ExtractDomain работает только если title страницы содержит доменное имя (напр. 'mail.google.com - Chrome'). В реальности 90%+ заголовков содержат человекочитаемое название ('Claude', 'Кадеро', 'Поиск'), без домена. Также regex для Edge не учитывает профильную метку ('Личный:', 'Personal:', etc.). Решение: использовать Windows UI Automation API для извлечения URL из адресной строки браузера.</t>
+        </is>
+      </c>
+      <c r="E86" s="24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F86" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G86" s="25" t="inlineStr">
+        <is>
+          <t>Алексей</t>
+        </is>
+      </c>
+      <c r="H86" s="24" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I86" s="24" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1" s="15">
+      <c r="A87" s="18" t="inlineStr">
+        <is>
+          <t>T-082</t>
+        </is>
+      </c>
+      <c r="B87" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C87" s="19" t="inlineStr">
+        <is>
+          <t>Windows Agent: UI Automation для извлечения URL из адресной строки браузера</t>
+        </is>
+      </c>
+      <c r="D87" s="19" t="inlineStr">
+        <is>
+          <t>Реализовать BrowserUrlExtractor на основе Windows UI Automation API (System.Windows.Automation / UIAutomationClient COM). Получать URL из адресной строки Chrome (OmniboxViewViews), Edge, Firefox, Яндекс.Браузер. Использовать UIA TreeWalker для поиска элемента address bar, извлечения Value, парсинга домена из URL. Fallback на текущий BrowserDomainParser.ExtractDomain из window title.</t>
+        </is>
+      </c>
+      <c r="E87" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F87" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G87" s="19" t="inlineStr">
+        <is>
+          <t>Алексей</t>
+        </is>
+      </c>
+      <c r="H87" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I87" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1" s="15">
+      <c r="A88" s="18" t="inlineStr">
+        <is>
+          <t>T-083</t>
+        </is>
+      </c>
+      <c r="B88" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C88" s="19" t="inlineStr">
+        <is>
+          <t>BrowserDomainParser: fix Edge profile label regex и расширить fallback</t>
+        </is>
+      </c>
+      <c r="D88" s="19" t="inlineStr">
+        <is>
+          <t>1) Regex для Edge не учитывает профильную метку ('Личный:', 'Personal:', 'InPrivate:') между title и 'Microsoft Edge'. 2) Regex для Яндекс Браузера не учитывает 'и еще N страниц' формат. 3) Добавить маппинг популярных title-&gt;domain (Claude-&gt;claude.ai, Gmail-&gt;gmail.com, etc.). 4) Расширить fallback для non-domain titles.</t>
+        </is>
+      </c>
+      <c r="E88" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F88" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G88" s="19" t="inlineStr">
+        <is>
+          <t>Алексей</t>
+        </is>
+      </c>
+      <c r="H88" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I88" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1" s="15">
+      <c r="A89" s="18" t="inlineStr">
+        <is>
+          <t>T-084</t>
+        </is>
+      </c>
+      <c r="B89" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C89" s="19" t="inlineStr">
+        <is>
+          <t>V31 миграция ingest-gateway: таблицы app_groups, app_group_items, app_aliases</t>
+        </is>
+      </c>
+      <c r="D89" s="19" t="inlineStr">
+        <is>
+          <t>Flyway миграция V31__app_groups_and_aliases.sql. Создание таблиц app_groups (группы приложений/сайтов), app_group_items (привязка exe/доменов к группам), app_aliases (отображаемые имена). Индексы: уникальность name per tenant+type, уникальность pattern per tenant+type. См. docs/app-groups-spec.md раздел 2.</t>
+        </is>
+      </c>
+      <c r="E89" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F89" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G89" s="19" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="H89" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I89" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1" s="15">
+      <c r="A90" s="18" t="inlineStr">
+        <is>
+          <t>T-085</t>
+        </is>
+      </c>
+      <c r="B90" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C90" s="19" t="inlineStr">
+        <is>
+          <t>V31 миграция auth-service: permissions CATALOGS:READ, CATALOGS:MANAGE</t>
+        </is>
+      </c>
+      <c r="D90" s="19" t="inlineStr">
+        <is>
+          <t>Flyway миграция V31__add_catalogs_permissions.sql. Добавить 2 новых permission: CATALOGS:READ (просмотр справочников и контрольной панели) и CATALOGS:MANAGE (CRUD групп/items/aliases). Назначить READ для SUPER_ADMIN, OWNER, TENANT_ADMIN, MANAGER, SUPERVISOR. MANAGE для SUPER_ADMIN, OWNER, TENANT_ADMIN.</t>
+        </is>
+      </c>
+      <c r="E90" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F90" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G90" s="19" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="H90" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I90" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1" s="15">
+      <c r="A91" s="18" t="inlineStr">
+        <is>
+          <t>T-086</t>
+        </is>
+      </c>
+      <c r="B91" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C91" s="19" t="inlineStr">
+        <is>
+          <t>Entity + Repository: AppGroup, AppGroupItem, AppAlias</t>
+        </is>
+      </c>
+      <c r="D91" s="19" t="inlineStr">
+        <is>
+          <t>JPA entities для 3 новых таблиц: AppGroup (id, tenantId, groupType, name, description, color, sortOrder, isDefault, createdAt, updatedAt, createdBy), AppGroupItem (id, tenantId, groupId, itemType, pattern, matchType, createdAt), AppAlias (id, tenantId, aliasType, original, displayName, iconUrl, createdAt, updatedAt). JpaRepository для каждой сущности.</t>
+        </is>
+      </c>
+      <c r="E91" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F91" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G91" s="19" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="H91" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I91" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1" s="15">
+      <c r="A92" s="18" t="inlineStr">
+        <is>
+          <t>T-087</t>
+        </is>
+      </c>
+      <c r="B92" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C92" s="19" t="inlineStr">
+        <is>
+          <t>CatalogSeedService: seed data для групп, items, aliases</t>
+        </is>
+      </c>
+      <c r="D92" s="19" t="inlineStr">
+        <is>
+          <t>Сервис ленивого seed. При первом GET /catalogs/groups если для tenant нет записей -- создать default группы (8 APP, 10 SITE), items (50+ привязок exe/доменов), aliases (42+ алиасов). Все записи is_default=true. Также POST /catalogs/seed для явного создания/пересоздания. См. docs/app-groups-spec.md раздел 3.</t>
+        </is>
+      </c>
+      <c r="E92" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F92" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G92" s="19" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="H92" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I92" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1" s="15">
+      <c r="A93" s="18" t="inlineStr">
+        <is>
+          <t>T-088</t>
+        </is>
+      </c>
+      <c r="B93" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C93" s="19" t="inlineStr">
+        <is>
+          <t>CatalogService: CRUD групп (create, update, delete, list)</t>
+        </is>
+      </c>
+      <c r="D93" s="19" t="inlineStr">
+        <is>
+          <t>Бизнес-логика групп: LIST с item_count через LEFT JOIN, CREATE с валидацией уникальности name, UPDATE, DELETE (запрет удаления is_default=true). Tenant isolation через tenant_id. Global scope для SUPER_ADMIN.</t>
+        </is>
+      </c>
+      <c r="E93" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F93" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G93" s="19" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="H93" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I93" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1" s="15">
+      <c r="A94" s="18" t="inlineStr">
+        <is>
+          <t>T-089</t>
+        </is>
+      </c>
+      <c r="B94" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C94" s="19" t="inlineStr">
+        <is>
+          <t>CatalogService: CRUD items (add, batch-add, delete, move)</t>
+        </is>
+      </c>
+      <c r="D94" s="19" t="inlineStr">
+        <is>
+          <t>Привязка exe/доменов к группам. ADD с проверкой уникальности pattern (один exe/домен только в одной группе). BATCH-ADD. DELETE. MOVE между группами с валидацией совпадения типа.</t>
+        </is>
+      </c>
+      <c r="E94" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F94" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G94" s="19" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="H94" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I94" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1" s="15">
+      <c r="A95" s="18" t="inlineStr">
+        <is>
+          <t>T-090</t>
+        </is>
+      </c>
+      <c r="B95" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C95" s="19" t="inlineStr">
+        <is>
+          <t>CatalogService: CRUD алиасов (create, update, delete, list)</t>
+        </is>
+      </c>
+      <c r="D95" s="19" t="inlineStr">
+        <is>
+          <t>Управление алиасами (отображаемыми именами). LIST с пагинацией и поиском. CREATE с проверкой уникальности original. UPDATE (display_name, icon_url). DELETE. Пагинация, фильтр по alias_type.</t>
+        </is>
+      </c>
+      <c r="E95" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F95" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G95" s="19" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="H95" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I95" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1" s="15">
+      <c r="A96" s="18" t="inlineStr">
+        <is>
+          <t>T-091</t>
+        </is>
+      </c>
+      <c r="B96" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C96" s="19" t="inlineStr">
+        <is>
+          <t>CatalogService: ungrouped query (несгруппированные exe/домены)</t>
+        </is>
+      </c>
+      <c r="D96" s="19" t="inlineStr">
+        <is>
+          <t>Запрос уникальных process_name/domain из app_focus_intervals которые НЕ привязаны ни к одной группе. NOT EXISTS с matching (EXACT, SUFFIX, CONTAINS). LEFT JOIN с app_aliases для display_name. Агрегация: total_duration_ms, interval_count, user_count, last_seen_at. Пагинация, поиск.</t>
+        </is>
+      </c>
+      <c r="E96" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F96" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G96" s="19" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="H96" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I96" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1" s="15">
+      <c r="A97" s="18" t="inlineStr">
+        <is>
+          <t>T-092</t>
+        </is>
+      </c>
+      <c r="B97" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C97" s="19" t="inlineStr">
+        <is>
+          <t>CatalogService: dashboard/summary агрегация по группам</t>
+        </is>
+      </c>
+      <c r="D97" s="19" t="inlineStr">
+        <is>
+          <t>GET /catalogs/dashboard/summary. JOIN app_focus_intervals + app_group_items + app_groups с matching (EXACT/SUFFIX/CONTAINS). GROUP BY group. Вычислить total_duration_ms, percentage, interval_count, user_count для каждой группы. Отдельно посчитать ungrouped. Все по всем пользователям тенанта.</t>
+        </is>
+      </c>
+      <c r="E97" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F97" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G97" s="19" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="H97" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I97" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1" s="15">
+      <c r="A98" s="18" t="inlineStr">
+        <is>
+          <t>T-093</t>
+        </is>
+      </c>
+      <c r="B98" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C98" s="19" t="inlineStr">
+        <is>
+          <t>CatalogService: dashboard/timeline зональная гистограмма по дням</t>
+        </is>
+      </c>
+      <c r="D98" s="19" t="inlineStr">
+        <is>
+          <t>GET /catalogs/dashboard/timeline. JOIN с matching, GROUP BY date + group_id. Возвращает массив days с breakdown по группам. Поддержка timezone. Для stacked area chart на фронтенде.</t>
+        </is>
+      </c>
+      <c r="E98" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F98" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G98" s="19" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="H98" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I98" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1" s="15">
+      <c r="A99" s="18" t="inlineStr">
+        <is>
+          <t>T-094</t>
+        </is>
+      </c>
+      <c r="B99" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C99" s="19" t="inlineStr">
+        <is>
+          <t>DashboardService: GET /dashboard/metrics (устройства, токены, объём видео)</t>
+        </is>
+      </c>
+      <c r="D99" s="19" t="inlineStr">
+        <is>
+          <t>Endpoint агрегации метрик для 1-го ряда дашборда. Прямой SQL к таблицам devices, device_registration_tokens, segments. Возвращает: connected_devices, total_devices, active_devices, tokens_used, tokens_total, video_size_bytes. Permission: CATALOGS:READ.</t>
+        </is>
+      </c>
+      <c r="E99" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F99" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G99" s="19" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="H99" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I99" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1" s="15">
+      <c r="A100" s="18" t="inlineStr">
+        <is>
+          <t>T-095</t>
+        </is>
+      </c>
+      <c r="B100" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C100" s="19" t="inlineStr">
+        <is>
+          <t>DashboardService: GET /dashboard/top-ungrouped (топ неразмеченных APP+SITE)</t>
+        </is>
+      </c>
+      <c r="D100" s="19" t="inlineStr">
+        <is>
+          <t>Endpoint для 3-го ряда дашборда. NOT EXISTS + GROUP BY process_name/domain. Возвращает: name, display_name, total_duration_ms, percentage, user_count. За 24ч по умолчанию. Permission: CATALOGS:READ.</t>
+        </is>
+      </c>
+      <c r="E100" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F100" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G100" s="19" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="H100" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I100" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1" s="15">
+      <c r="A101" s="18" t="inlineStr">
+        <is>
+          <t>T-096</t>
+        </is>
+      </c>
+      <c r="B101" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C101" s="19" t="inlineStr">
+        <is>
+          <t>DashboardService: GET /dashboard/top-users-ungrouped (топ пользователей по неразмеченным)</t>
+        </is>
+      </c>
+      <c r="D101" s="19" t="inlineStr">
+        <is>
+          <t>Endpoint для 4-го ряда дашборда. NOT EXISTS + GROUP BY username. Возвращает: username, display_name, total_ungrouped_duration_ms, ungrouped_percentage, top_ungrouped_items. За 24ч. Permission: CATALOGS:READ.</t>
+        </is>
+      </c>
+      <c r="E101" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F101" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G101" s="19" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="H101" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I101" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1" s="15">
+      <c r="A102" s="18" t="inlineStr">
+        <is>
+          <t>T-097</t>
+        </is>
+      </c>
+      <c r="B102" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C102" s="19" t="inlineStr">
+        <is>
+          <t>DashboardController: REST endpoints /api/v1/ingest/dashboard/**</t>
+        </is>
+      </c>
+      <c r="D102" s="19" t="inlineStr">
+        <is>
+          <t>Контроллер для endpoints дашборда: /metrics, /group-timeline, /group-summary, /top-ungrouped, /top-users-ungrouped. Проверка CATALOGS:READ. resolveEffectiveTenantId для SUPER_ADMIN.</t>
+        </is>
+      </c>
+      <c r="E102" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F102" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G102" s="19" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="H102" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I102" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1" s="15">
+      <c r="A103" s="18" t="inlineStr">
+        <is>
+          <t>T-098</t>
+        </is>
+      </c>
+      <c r="B103" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C103" s="19" t="inlineStr">
+        <is>
+          <t>Frontend: MetricsRow -- 4 карточки метрик на дашборде (1-й ряд)</t>
+        </is>
+      </c>
+      <c r="D103" s="19" t="inlineStr">
+        <is>
+          <t>Компонент MetricsRow.tsx: подключённые/всего устройств, в работе, токены использовано/всего, объём видео (ГБ). Запрос GET /dashboard/metrics. Карточки с иконками из heroicons.</t>
+        </is>
+      </c>
+      <c r="E103" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F103" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G103" s="19" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="H103" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I103" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1" s="15">
+      <c r="A104" s="18" t="inlineStr">
+        <is>
+          <t>T-099</t>
+        </is>
+      </c>
+      <c r="B104" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C104" s="19" t="inlineStr">
+        <is>
+          <t>Frontend: GroupTimelineChart -- recharts LineChart по группам (2-й ряд)</t>
+        </is>
+      </c>
+      <c r="D104" s="19" t="inlineStr">
+        <is>
+          <t>Компонент GroupTimelineChart.tsx: множественный линейный график, ось X = дни, ось Y = %, одна линия на группу, цвет = group.color, легенда. Используется recharts LineChart. Два экземпляра: APP и SITE.</t>
+        </is>
+      </c>
+      <c r="E104" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F104" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G104" s="19" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="H104" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I104" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1" s="15">
+      <c r="A105" s="18" t="inlineStr">
+        <is>
+          <t>T-100</t>
+        </is>
+      </c>
+      <c r="B105" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C105" s="19" t="inlineStr">
+        <is>
+          <t>Frontend: TopUngroupedTable -- топ неразмеченных за 24ч с кнопкой '+ В группу' (3-й ряд)</t>
+        </is>
+      </c>
+      <c r="D105" s="19" t="inlineStr">
+        <is>
+          <t>Компонент TopUngroupedTable.tsx: таблица с колонками name, %, user_count. Кнопка '+ В группу' с AssignGroupDropdown. Два экземпляра: APP и SITE. Запрос GET /dashboard/top-ungrouped.</t>
+        </is>
+      </c>
+      <c r="E105" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F105" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G105" s="19" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="H105" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I105" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1" s="15">
+      <c r="A106" s="18" t="inlineStr">
+        <is>
+          <t>T-101</t>
+        </is>
+      </c>
+      <c r="B106" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C106" s="19" t="inlineStr">
+        <is>
+          <t>Frontend: TopUsersUngroupedTable -- топ пользователей по неразмеченным (4-й ряд)</t>
+        </is>
+      </c>
+      <c r="D106" s="19" t="inlineStr">
+        <is>
+          <t>Компонент TopUsersUngroupedTable.tsx: таблица пользователей с ungrouped_percentage и absolute time. Два экземпляра: APP и SITE. Запрос GET /dashboard/top-users-ungrouped.</t>
+        </is>
+      </c>
+      <c r="E106" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F106" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G106" s="19" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="H106" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I106" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1" s="15">
+      <c r="A107" s="18" t="inlineStr">
+        <is>
+          <t>T-102</t>
+        </is>
+      </c>
+      <c r="B107" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C107" s="19" t="inlineStr">
+        <is>
+          <t>Frontend: полная переработка DashboardPage (4 ряда, период, заголовок)</t>
+        </is>
+      </c>
+      <c r="D107" s="19" t="inlineStr">
+        <is>
+          <t>Переработка DashboardPage.tsx: заголовок 'Дашборд &lt;ИМЯ ТЕНАНТА&gt;', выбор периода, 4 ряда виджетов (MetricsRow, 2x GroupTimelineChart, 2x TopUngroupedTable, 2x TopUsersUngroupedTable). Promise.all для 8 параллельных запросов.</t>
+        </is>
+      </c>
+      <c r="E107" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F107" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G107" s="19" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="H107" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I107" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1" s="15">
+      <c r="A108" s="18" t="inlineStr">
+        <is>
+          <t>T-103</t>
+        </is>
+      </c>
+      <c r="B108" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C108" s="19" t="inlineStr">
+        <is>
+          <t>Frontend: Sidebar -- переименовать 'Контрольная панель' в 'Дашборд', добавить пункты справочников</t>
+        </is>
+      </c>
+      <c r="D108" s="19" t="inlineStr">
+        <is>
+          <t>В Sidebar.tsx: заменить 'Контрольная панель' на 'Дашборд'. В tenantSettingsSubmenu и superAdminSettingsSubmenu добавить 'Группы приложений' (/catalogs/apps, CATALOGS:READ) и 'Группы сайтов' (/catalogs/sites, CATALOGS:READ). isSettingsActive += /catalogs.</t>
+        </is>
+      </c>
+      <c r="E108" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F108" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G108" s="19" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="H108" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I108" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1" s="15">
+      <c r="A109" s="18" t="inlineStr">
+        <is>
+          <t>T-104</t>
+        </is>
+      </c>
+      <c r="B109" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C109" s="19" t="inlineStr">
+        <is>
+          <t>Обогатить AppsReport и DomainsReport полями groupName, groupColor, displayName</t>
+        </is>
+      </c>
+      <c r="D109" s="19" t="inlineStr">
+        <is>
+          <t>В UserActivityService.getUserApps() и getUserDomains() добавить LEFT JOIN с app_group_items+app_groups и app_aliases для обогащения ответа. Новые nullable поля в AppItem и DomainItem: groupName, groupColor, displayName.</t>
+        </is>
+      </c>
+      <c r="E109" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F109" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G109" s="19" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H109" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I109" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1" s="15">
+      <c r="A110" s="18" t="inlineStr">
+        <is>
+          <t>T-105</t>
+        </is>
+      </c>
+      <c r="B110" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C110" s="19" t="inlineStr">
+        <is>
+          <t>Frontend: добавить recharts + api/catalogs.ts + types/catalogs.ts</t>
+        </is>
+      </c>
+      <c r="D110" s="19" t="inlineStr">
+        <is>
+          <t>npm install recharts. Новый API-клиент catalogs.ts с функциями для groups, items, aliases, ungrouped, dashboard endpoints. TypeScript типы в types/catalogs.ts. Обновить App.tsx с routes /catalogs/apps и /catalogs/sites.</t>
+        </is>
+      </c>
+      <c r="E110" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F110" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G110" s="19" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="H110" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I110" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1" s="15">
+      <c r="A111" s="18" t="inlineStr">
+        <is>
+          <t>T-106</t>
+        </is>
+      </c>
+      <c r="B111" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C111" s="19" t="inlineStr">
+        <is>
+          <t>E2E тест: дашборд metrics + group-timeline + top-ungrouped + top-users-ungrouped</t>
+        </is>
+      </c>
+      <c r="D111" s="19" t="inlineStr">
+        <is>
+          <t>Тестирование всех 4 рядов дашборда: проверить корректность метрик (устройства, токены, видео), графики по группам, топ неразмеченных, топ пользователей. Проверить работу с пустым справочником (ленивый seed). Проверить tenant isolation.</t>
+        </is>
+      </c>
+      <c r="E111" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F111" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G111" s="19" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="H111" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I111" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1" s="15">
+      <c r="A112" s="18" t="inlineStr">
+        <is>
+          <t>T-107</t>
+        </is>
+      </c>
+      <c r="B112" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C112" s="19" t="inlineStr">
+        <is>
+          <t>Деплой справочников + дашборда на test стейджинг</t>
+        </is>
+      </c>
+      <c r="D112" s="19" t="inlineStr">
+        <is>
+          <t>Деплой V31 миграций (ingest-gateway + auth-service), пересборка ingest-gateway + web-dashboard, деплой на shepaland-cloud (test-screen-record). Smoke-тест: seed справочников, загрузка дашборда.</t>
+        </is>
+      </c>
+      <c r="E112" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F112" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G112" s="19" t="inlineStr">
+        <is>
+          <t>DevOps</t>
+        </is>
+      </c>
+      <c r="H112" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+      <c r="I112" s="18" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1" s="15">
+      <c r="A113" s="24" t="inlineStr">
+        <is>
+          <t>T-108</t>
+        </is>
+      </c>
+      <c r="B113" s="24" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="C113" s="25" t="inlineStr">
+        <is>
+          <t>CatalogController: resolveEffectiveTenantId возвращает null для global scope -&gt; 500 на seed</t>
+        </is>
+      </c>
+      <c r="D113" s="25" t="inlineStr">
+        <is>
+          <t>При запросе к /catalogs/groups или /dashboard/group-timeline от superadmin (scope=global) без параметра tenant_id, resolveEffectiveTenantId возвращает null. Это вызывает NOT NULL constraint violation при INSERT в app_groups (lazy seed). DashboardService.getMetrics работает, т.к. не делает INSERT. Fix: fallback на principal.getTenantId() если tenantIdParam=null.</t>
+        </is>
+      </c>
+      <c r="E113" s="24" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F113" s="24" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G113" s="25" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="H113" s="24" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I113" s="24" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
@@ -3580,7 +5800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J97"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="15" min="1" max="1"/>
@@ -5349,6 +7569,3102 @@
       <c r="J37" s="23" t="inlineStr">
         <is>
           <t>07.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="50" customHeight="1" s="15">
+      <c r="A38" s="22" t="inlineStr">
+        <is>
+          <t>TC-033</t>
+        </is>
+      </c>
+      <c r="B38" s="22" t="inlineStr">
+        <is>
+          <t>User Activity Tracking</t>
+        </is>
+      </c>
+      <c r="C38" s="23" t="inlineStr">
+        <is>
+          <t>POST focus-intervals: Happy Path - 2 интервала</t>
+        </is>
+      </c>
+      <c r="D38" s="23" t="inlineStr">
+        <is>
+          <t>Device зарегистрирован, device JWT получен, X-Device-ID совпадает</t>
+        </is>
+      </c>
+      <c r="E38" s="22" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/ingest/activity/focus-intervals с 2 интервалами (chrome.exe + 1cv8.exe)\n2. Проверить HTTP статус 200\n3. Проверить accepted=2, duplicates=0</t>
+        </is>
+      </c>
+      <c r="F38" s="22" t="inlineStr">
+        <is>
+          <t>HTTP 200, JSON {accepted:2, duplicates:0, correlation_id: UUID}</t>
+        </is>
+      </c>
+      <c r="G38" s="23" t="inlineStr">
+        <is>
+          <t>HTTP 200, {accepted:2, duplicates:0, correlation_id: UUID}. Данные корректно сохранены.</t>
+        </is>
+      </c>
+      <c r="H38" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I38" s="22" t="inlineStr">
+        <is>
+          <t>T-039</t>
+        </is>
+      </c>
+      <c r="J38" s="23" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="50" customHeight="1" s="15">
+      <c r="A39" s="22" t="inlineStr">
+        <is>
+          <t>TC-034</t>
+        </is>
+      </c>
+      <c r="B39" s="22" t="inlineStr">
+        <is>
+          <t>User Activity Tracking</t>
+        </is>
+      </c>
+      <c r="C39" s="23" t="inlineStr">
+        <is>
+          <t>POST focus-intervals: Дедупликация повторных UUID</t>
+        </is>
+      </c>
+      <c r="D39" s="23" t="inlineStr">
+        <is>
+          <t>Интервалы из TC-033 уже сохранены в БД</t>
+        </is>
+      </c>
+      <c r="E39" s="22" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/ingest/activity/focus-intervals с тем же UUID\n2. Проверить accepted=0, duplicates=1</t>
+        </is>
+      </c>
+      <c r="F39" s="22" t="inlineStr">
+        <is>
+          <t>HTTP 200, JSON {accepted:0, duplicates:1}</t>
+        </is>
+      </c>
+      <c r="G39" s="23" t="inlineStr">
+        <is>
+          <t>HTTP 200, {accepted:0, duplicates:1}. Дедупликация по UUID работает.</t>
+        </is>
+      </c>
+      <c r="H39" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I39" s="22" t="inlineStr">
+        <is>
+          <t>T-038</t>
+        </is>
+      </c>
+      <c r="J39" s="23" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="50" customHeight="1" s="15">
+      <c r="A40" s="22" t="inlineStr">
+        <is>
+          <t>TC-035</t>
+        </is>
+      </c>
+      <c r="B40" s="22" t="inlineStr">
+        <is>
+          <t>User Activity Tracking</t>
+        </is>
+      </c>
+      <c r="C40" s="23" t="inlineStr">
+        <is>
+          <t>POST focus-intervals: Валидация - пустой массив intervals</t>
+        </is>
+      </c>
+      <c r="D40" s="23" t="inlineStr">
+        <is>
+          <t>Device JWT получен</t>
+        </is>
+      </c>
+      <c r="E40" s="22" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/ingest/activity/focus-intervals с intervals=[]\n2. Проверить HTTP 400</t>
+        </is>
+      </c>
+      <c r="F40" s="22" t="inlineStr">
+        <is>
+          <t>HTTP 400, JSON с кодом VALIDATION_ERROR</t>
+        </is>
+      </c>
+      <c r="G40" s="23" t="inlineStr">
+        <is>
+          <t>HTTP 400, {error: intervals must not be empty, code: VALIDATION_ERROR}</t>
+        </is>
+      </c>
+      <c r="H40" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I40" s="22" t="inlineStr">
+        <is>
+          <t>T-039</t>
+        </is>
+      </c>
+      <c r="J40" s="23" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="50" customHeight="1" s="15">
+      <c r="A41" s="22" t="inlineStr">
+        <is>
+          <t>TC-036</t>
+        </is>
+      </c>
+      <c r="B41" s="22" t="inlineStr">
+        <is>
+          <t>User Activity Tracking</t>
+        </is>
+      </c>
+      <c r="C41" s="23" t="inlineStr">
+        <is>
+          <t>POST focus-intervals: Unauthorized - без токена</t>
+        </is>
+      </c>
+      <c r="D41" s="23" t="inlineStr">
+        <is>
+          <t>Нет JWT токена</t>
+        </is>
+      </c>
+      <c r="E41" s="22" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/ingest/activity/focus-intervals без Authorization header\n2. Проверить HTTP 401</t>
+        </is>
+      </c>
+      <c r="F41" s="22" t="inlineStr">
+        <is>
+          <t>HTTP 401</t>
+        </is>
+      </c>
+      <c r="G41" s="23" t="inlineStr">
+        <is>
+          <t>HTTP 401, {error: Missing or invalid Authorization header, code: MISSING_TOKEN}</t>
+        </is>
+      </c>
+      <c r="H41" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I41" s="22" t="inlineStr">
+        <is>
+          <t>T-039</t>
+        </is>
+      </c>
+      <c r="J41" s="23" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="50" customHeight="1" s="15">
+      <c r="A42" s="22" t="inlineStr">
+        <is>
+          <t>TC-037</t>
+        </is>
+      </c>
+      <c r="B42" s="22" t="inlineStr">
+        <is>
+          <t>User Activity Tracking</t>
+        </is>
+      </c>
+      <c r="C42" s="23" t="inlineStr">
+        <is>
+          <t>POST focus-intervals: Device mismatch (403)</t>
+        </is>
+      </c>
+      <c r="D42" s="23" t="inlineStr">
+        <is>
+          <t>Device JWT с device_id A, запрос с device_id B</t>
+        </is>
+      </c>
+      <c r="E42" s="22" t="inlineStr">
+        <is>
+          <t>1. POST с device_id != device_id в JWT\n2. Проверить HTTP 403 с кодом DEVICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="F42" s="22" t="inlineStr">
+        <is>
+          <t>HTTP 403, JSON {error:..., code: DEVICE_MISMATCH}</t>
+        </is>
+      </c>
+      <c r="G42" s="23" t="inlineStr">
+        <is>
+          <t>HTTP 403, {error: device_id mismatch with JWT claims, code: DEVICE_MISMATCH}</t>
+        </is>
+      </c>
+      <c r="H42" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I42" s="22" t="inlineStr">
+        <is>
+          <t>T-039</t>
+        </is>
+      </c>
+      <c r="J42" s="23" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="50" customHeight="1" s="15">
+      <c r="A43" s="22" t="inlineStr">
+        <is>
+          <t>TC-038</t>
+        </is>
+      </c>
+      <c r="B43" s="22" t="inlineStr">
+        <is>
+          <t>User Activity Tracking</t>
+        </is>
+      </c>
+      <c r="C43" s="23" t="inlineStr">
+        <is>
+          <t>GET /users: Список пользователей тенанта</t>
+        </is>
+      </c>
+      <c r="D43" s="23" t="inlineStr">
+        <is>
+          <t>Focus-интервалы отправлены для TESTCORP\ivanov.a, USER JWT с RECORDINGS:READ</t>
+        </is>
+      </c>
+      <c r="E43" s="22" t="inlineStr">
+        <is>
+          <t>1. GET /api/v1/ingest/users с USER JWT\n2. Проверить HTTP 200\n3. Проверить наличие TESTCORP\ivanov.a в content</t>
+        </is>
+      </c>
+      <c r="F43" s="22" t="inlineStr">
+        <is>
+          <t>HTTP 200, paged response с пользователем в content</t>
+        </is>
+      </c>
+      <c r="G43" s="23" t="inlineStr">
+        <is>
+          <t>HTTP 200, paged response с 2 пользователями (petrov.b и TESTCORP\ivanov.a), pagination, device_count корректны.</t>
+        </is>
+      </c>
+      <c r="H43" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I43" s="22" t="inlineStr">
+        <is>
+          <t>T-042</t>
+        </is>
+      </c>
+      <c r="J43" s="23" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="50" customHeight="1" s="15">
+      <c r="A44" s="22" t="inlineStr">
+        <is>
+          <t>TC-039</t>
+        </is>
+      </c>
+      <c r="B44" s="22" t="inlineStr">
+        <is>
+          <t>User Activity Tracking</t>
+        </is>
+      </c>
+      <c r="C44" s="23" t="inlineStr">
+        <is>
+          <t>GET /users/{username}/activity: Activity summary</t>
+        </is>
+      </c>
+      <c r="D44" s="23" t="inlineStr">
+        <is>
+          <t>Focus-интервалы отправлены, USER JWT с RECORDINGS:READ</t>
+        </is>
+      </c>
+      <c r="E44" s="22" t="inlineStr">
+        <is>
+          <t>1. GET /api/v1/ingest/users/{username}/activity?from=...&amp;to=...\n2. Проверить HTTP 200\n3. Проверить summary, topApps, topDomains, dailyBreakdown</t>
+        </is>
+      </c>
+      <c r="F44" s="22" t="inlineStr">
+        <is>
+          <t>HTTP 200, JSON с summary (totalActiveMs &gt; 0), topApps содержит chrome.exe и 1cv8.exe</t>
+        </is>
+      </c>
+      <c r="G44" s="23" t="inlineStr">
+        <is>
+          <t>HTTP 200 для username без backslash (petrov.b). summary корректен: totalActiveMs=1500000, uniqueApps=2, uniqueDomains=1, topApps содержит outlook.exe и chrome.exe. BUG: username с backslash (DOMAIN\user) невозможно передать в URL path — Tomcat блокирует %5C.</t>
+        </is>
+      </c>
+      <c r="H44" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I44" s="22" t="inlineStr">
+        <is>
+          <t>T-042</t>
+        </is>
+      </c>
+      <c r="J44" s="23" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="50" customHeight="1" s="15">
+      <c r="A45" s="22" t="inlineStr">
+        <is>
+          <t>TC-040</t>
+        </is>
+      </c>
+      <c r="B45" s="22" t="inlineStr">
+        <is>
+          <t>User Activity Tracking</t>
+        </is>
+      </c>
+      <c r="C45" s="23" t="inlineStr">
+        <is>
+          <t>GET /users/{username}/apps: Отчет по приложениям</t>
+        </is>
+      </c>
+      <c r="D45" s="23" t="inlineStr">
+        <is>
+          <t>Focus-интервалы отправлены, USER JWT с RECORDINGS:READ</t>
+        </is>
+      </c>
+      <c r="E45" s="22" t="inlineStr">
+        <is>
+          <t>1. GET /api/v1/ingest/users/{username}/apps?from=...&amp;to=...\n2. Проверить HTTP 200\n3. Проверить content содержит chrome.exe и 1cv8.exe</t>
+        </is>
+      </c>
+      <c r="F45" s="22" t="inlineStr">
+        <is>
+          <t>HTTP 200, paged response с приложениями</t>
+        </is>
+      </c>
+      <c r="G45" s="23" t="inlineStr">
+        <is>
+          <t>HTTP 200, paged response с chrome.exe (600000ms, 40%) и outlook.exe (900000ms, 60%). totalActiveMs=1500000.</t>
+        </is>
+      </c>
+      <c r="H45" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I45" s="22" t="inlineStr">
+        <is>
+          <t>T-042</t>
+        </is>
+      </c>
+      <c r="J45" s="23" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="50" customHeight="1" s="15">
+      <c r="A46" s="22" t="inlineStr">
+        <is>
+          <t>TC-041</t>
+        </is>
+      </c>
+      <c r="B46" s="22" t="inlineStr">
+        <is>
+          <t>User Activity Tracking</t>
+        </is>
+      </c>
+      <c r="C46" s="23" t="inlineStr">
+        <is>
+          <t>GET /users/{username}/domains: Отчет по доменам</t>
+        </is>
+      </c>
+      <c r="D46" s="23" t="inlineStr">
+        <is>
+          <t>Focus-интервалы с is_browser=true и domain отправлены</t>
+        </is>
+      </c>
+      <c r="E46" s="22" t="inlineStr">
+        <is>
+          <t>1. GET /api/v1/ingest/users/{username}/domains?from=...&amp;to=...\n2. Проверить HTTP 200\n3. Проверить content содержит work-crm.com</t>
+        </is>
+      </c>
+      <c r="F46" s="22" t="inlineStr">
+        <is>
+          <t>HTTP 200, paged response с доменом work-crm.com</t>
+        </is>
+      </c>
+      <c r="G46" s="23" t="inlineStr">
+        <is>
+          <t>HTTP 200, paged response с доменом mail.google.com (600000ms, 100%, Chrome). avg_visit_duration_ms корректен.</t>
+        </is>
+      </c>
+      <c r="H46" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I46" s="22" t="inlineStr">
+        <is>
+          <t>T-042</t>
+        </is>
+      </c>
+      <c r="J46" s="23" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="50" customHeight="1" s="15">
+      <c r="A47" s="22" t="inlineStr">
+        <is>
+          <t>TC-042</t>
+        </is>
+      </c>
+      <c r="B47" s="22" t="inlineStr">
+        <is>
+          <t>User Activity Tracking</t>
+        </is>
+      </c>
+      <c r="C47" s="23" t="inlineStr">
+        <is>
+          <t>GET /users/{username}/worktime: Рабочее время</t>
+        </is>
+      </c>
+      <c r="D47" s="23" t="inlineStr">
+        <is>
+          <t>Focus-интервалы отправлены</t>
+        </is>
+      </c>
+      <c r="E47" s="22" t="inlineStr">
+        <is>
+          <t>1. GET /api/v1/ingest/users/{username}/worktime?from=...&amp;to=...&amp;timezone=Europe/Moscow\n2. Проверить HTTP 200\n3. Проверить структуру: workSchedule, days[]</t>
+        </is>
+      </c>
+      <c r="F47" s="22" t="inlineStr">
+        <is>
+          <t>HTTP 200, JSON с days[] содержащим данные за дни с активностью</t>
+        </is>
+      </c>
+      <c r="G47" s="23" t="inlineStr">
+        <is>
+          <t>HTTP 200, workSchedule={start:09:00, end:18:00, timezone:Europe/Moscow}, days содержит 2026-03-07 (saturday, weekend, arrival 11:00, departure 11:25, totalHours 0.42).</t>
+        </is>
+      </c>
+      <c r="H47" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I47" s="22" t="inlineStr">
+        <is>
+          <t>T-042</t>
+        </is>
+      </c>
+      <c r="J47" s="23" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="50" customHeight="1" s="15">
+      <c r="A48" s="22" t="inlineStr">
+        <is>
+          <t>TC-043</t>
+        </is>
+      </c>
+      <c r="B48" s="22" t="inlineStr">
+        <is>
+          <t>User Activity Tracking</t>
+        </is>
+      </c>
+      <c r="C48" s="23" t="inlineStr">
+        <is>
+          <t>GET /users/{username}/timesheet: Табель за месяц</t>
+        </is>
+      </c>
+      <c r="D48" s="23" t="inlineStr">
+        <is>
+          <t>Focus-интервалы отправлены</t>
+        </is>
+      </c>
+      <c r="E48" s="22" t="inlineStr">
+        <is>
+          <t>1. GET /api/v1/ingest/users/{username}/timesheet?month=2026-03\n2. Проверить HTTP 200\n3. Проверить summary и days[]</t>
+        </is>
+      </c>
+      <c r="F48" s="22" t="inlineStr">
+        <is>
+          <t>HTTP 200, JSON с summary (workDaysInMonth, daysPresent) и days[]</t>
+        </is>
+      </c>
+      <c r="G48" s="23" t="inlineStr">
+        <is>
+          <t>HTTP 200, summary: workDaysInMonth=22, daysAbsent=22, totalExpectedHours=198.0, totalActualHours=0.42. days[] содержит 31 день марта. Данные за 07.03 корректны.</t>
+        </is>
+      </c>
+      <c r="H48" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I48" s="22" t="inlineStr">
+        <is>
+          <t>T-042</t>
+        </is>
+      </c>
+      <c r="J48" s="23" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="50" customHeight="1" s="15">
+      <c r="A49" s="22" t="inlineStr">
+        <is>
+          <t>TC-044</t>
+        </is>
+      </c>
+      <c r="B49" s="22" t="inlineStr">
+        <is>
+          <t>User Activity Tracking</t>
+        </is>
+      </c>
+      <c r="C49" s="23" t="inlineStr">
+        <is>
+          <t>SQL Injection protection: sort_by whitelist</t>
+        </is>
+      </c>
+      <c r="D49" s="23" t="inlineStr">
+        <is>
+          <t>USER JWT получен</t>
+        </is>
+      </c>
+      <c r="E49" s="22" t="inlineStr">
+        <is>
+          <t>1. GET /api/v1/ingest/users?sort_by=username;DROP TABLE device_user_sessions--\n2. Проверить что НЕ 500\n3. Проверить что таблица device_user_sessions существует</t>
+        </is>
+      </c>
+      <c r="F49" s="22" t="inlineStr">
+        <is>
+          <t>HTTP 200 (с fallback на last_seen_ts) или HTTP 400, НЕ 500</t>
+        </is>
+      </c>
+      <c r="G49" s="23" t="inlineStr">
+        <is>
+          <t>HTTP 200, SQL injection payload в sort_by игнорирован (whitelist fallback на last_seen_ts). Данные возвращены корректно, таблица не повреждена.</t>
+        </is>
+      </c>
+      <c r="H49" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I49" s="22" t="inlineStr">
+        <is>
+          <t>T-042</t>
+        </is>
+      </c>
+      <c r="J49" s="23" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="50" customHeight="1" s="15">
+      <c r="A50" s="22" t="inlineStr">
+        <is>
+          <t>TC-045</t>
+        </is>
+      </c>
+      <c r="B50" s="22" t="inlineStr">
+        <is>
+          <t>User Activity Tracking</t>
+        </is>
+      </c>
+      <c r="C50" s="23" t="inlineStr">
+        <is>
+          <t>XSS protection: HTML tags в window_title санитизируются</t>
+        </is>
+      </c>
+      <c r="D50" s="23" t="inlineStr">
+        <is>
+          <t>Device JWT получен</t>
+        </is>
+      </c>
+      <c r="E50" s="22" t="inlineStr">
+        <is>
+          <t>1. POST focus-intervals с window_title=&lt;script&gt;alert(1)&lt;/script&gt;XSS Test\n2. Проверить HTTP 200\n3. Проверить в PostgreSQL что HTML теги удалены</t>
+        </is>
+      </c>
+      <c r="F50" s="22" t="inlineStr">
+        <is>
+          <t>HTTP 200, в БД window_title = 'alert(1)XSS Test' (без HTML тегов)</t>
+        </is>
+      </c>
+      <c r="G50" s="23" t="inlineStr">
+        <is>
+          <t>HTTP 200 при отправке. В API window_title_sample=[alert(1)XSS Test] — HTML теги &lt;script&gt; и &lt;/script&gt; удалены sanitize().</t>
+        </is>
+      </c>
+      <c r="H50" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I50" s="22" t="inlineStr">
+        <is>
+          <t>T-039</t>
+        </is>
+      </c>
+      <c r="J50" s="23" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="50" customHeight="1" s="15">
+      <c r="A51" s="22" t="inlineStr">
+        <is>
+          <t>TC-046</t>
+        </is>
+      </c>
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>User Activity Tracking</t>
+        </is>
+      </c>
+      <c r="C51" s="23" t="inlineStr">
+        <is>
+          <t>POST audit-events: обратная совместимость с username</t>
+        </is>
+      </c>
+      <c r="D51" s="23" t="inlineStr">
+        <is>
+          <t>Device JWT получен</t>
+        </is>
+      </c>
+      <c r="E51" s="22" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/ingest/audit-events с полем username\n2. Проверить HTTP 200\n3. Проверить accepted=1</t>
+        </is>
+      </c>
+      <c r="F51" s="22" t="inlineStr">
+        <is>
+          <t>HTTP 200, JSON {accepted:1}</t>
+        </is>
+      </c>
+      <c r="G51" s="23" t="inlineStr">
+        <is>
+          <t>HTTP 200, {accepted:1, duplicates:0}. Поле username принято в audit-events.</t>
+        </is>
+      </c>
+      <c r="H51" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I51" s="22" t="inlineStr">
+        <is>
+          <t>T-040</t>
+        </is>
+      </c>
+      <c r="J51" s="23" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="50" customHeight="1" s="15">
+      <c r="A52" s="22" t="inlineStr">
+        <is>
+          <t>TC-047</t>
+        </is>
+      </c>
+      <c r="B52" s="22" t="inlineStr">
+        <is>
+          <t>User Activity Tracking</t>
+        </is>
+      </c>
+      <c r="C52" s="23" t="inlineStr">
+        <is>
+          <t>POST audit-events: обратная совместимость БЕЗ username</t>
+        </is>
+      </c>
+      <c r="D52" s="23" t="inlineStr">
+        <is>
+          <t>Device JWT получен</t>
+        </is>
+      </c>
+      <c r="E52" s="22" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/ingest/audit-events БЕЗ поля username\n2. Проверить HTTP 200\n3. Проверить accepted=1</t>
+        </is>
+      </c>
+      <c r="F52" s="22" t="inlineStr">
+        <is>
+          <t>HTTP 200, JSON {accepted:1} (старый формат работает)</t>
+        </is>
+      </c>
+      <c r="G52" s="23" t="inlineStr">
+        <is>
+          <t>HTTP 200, {accepted:1, duplicates:0}. Старый формат без username работает — обратная совместимость сохранена.</t>
+        </is>
+      </c>
+      <c r="H52" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I52" s="22" t="inlineStr">
+        <is>
+          <t>T-040</t>
+        </is>
+      </c>
+      <c r="J52" s="23" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="50" customHeight="1" s="15">
+      <c r="A53" s="22" t="inlineStr">
+        <is>
+          <t>TC-048</t>
+        </is>
+      </c>
+      <c r="B53" s="22" t="inlineStr">
+        <is>
+          <t>User Activity Tracking</t>
+        </is>
+      </c>
+      <c r="C53" s="23" t="inlineStr">
+        <is>
+          <t>Regression: GET /users without auth token -&gt; 401</t>
+        </is>
+      </c>
+      <c r="D53" s="23" t="inlineStr">
+        <is>
+          <t>ingest-gateway deployed on test staging</t>
+        </is>
+      </c>
+      <c r="E53" s="22" t="inlineStr">
+        <is>
+          <t>1. Send GET /api/ingest/v1/ingest/users without Authorization header</t>
+        </is>
+      </c>
+      <c r="F53" s="22" t="inlineStr">
+        <is>
+          <t>HTTP 401 with error MISSING_TOKEN</t>
+        </is>
+      </c>
+      <c r="G53" s="23" t="inlineStr">
+        <is>
+          <t>HTTP 401, body: {"error":"Missing or invalid Authorization header","code":"MISSING_TOKEN"}</t>
+        </is>
+      </c>
+      <c r="H53" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I53" s="22" t="inlineStr">
+        <is>
+          <t>T-042</t>
+        </is>
+      </c>
+      <c r="J53" s="23" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="50" customHeight="1" s="15">
+      <c r="A54" s="22" t="inlineStr">
+        <is>
+          <t>TC-049</t>
+        </is>
+      </c>
+      <c r="B54" s="22" t="inlineStr">
+        <is>
+          <t>User Activity Tracking</t>
+        </is>
+      </c>
+      <c r="C54" s="23" t="inlineStr">
+        <is>
+          <t>Regression: GET /users with superadmin token -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D54" s="23" t="inlineStr">
+        <is>
+          <t>ingest-gateway deployed on test staging, superadmin JWT token obtained</t>
+        </is>
+      </c>
+      <c r="E54" s="22" t="inlineStr">
+        <is>
+          <t>1. Login as superadmin\n2. Send GET /api/ingest/v1/ingest/users with Authorization: Bearer &lt;token&gt;</t>
+        </is>
+      </c>
+      <c r="F54" s="22" t="inlineStr">
+        <is>
+          <t>HTTP 200 with JSON containing content, page, size, total_elements, total_pages</t>
+        </is>
+      </c>
+      <c r="G54" s="23" t="inlineStr">
+        <is>
+          <t>HTTP 200, body: {"content":[],"page":0,"size":20,"total_elements":0,"total_pages":0}</t>
+        </is>
+      </c>
+      <c r="H54" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I54" s="22" t="inlineStr">
+        <is>
+          <t>T-042</t>
+        </is>
+      </c>
+      <c r="J54" s="23" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="50" customHeight="1" s="15">
+      <c r="A55" s="22" t="inlineStr">
+        <is>
+          <t>TC-050</t>
+        </is>
+      </c>
+      <c r="B55" s="22" t="inlineStr">
+        <is>
+          <t>User Activity Tracking</t>
+        </is>
+      </c>
+      <c r="C55" s="23" t="inlineStr">
+        <is>
+          <t>T-062 fix: username with backslash DOMAIN\user -&gt; NOT 400</t>
+        </is>
+      </c>
+      <c r="D55" s="23" t="inlineStr">
+        <is>
+          <t>ingest-gateway deployed on test staging with T-062 fix, superadmin JWT token</t>
+        </is>
+      </c>
+      <c r="E55" s="22" t="inlineStr">
+        <is>
+          <t>1. Login as superadmin\n2. Send GET /api/ingest/v1/ingest/users/activity?username=TESTCORP%5Civanov.a&amp;from=2026-03-01T00:00:00Z&amp;to=2026-03-08T23:59:59Z\n3. Verify response is NOT 400 (Tomcat rejected backslash)</t>
+        </is>
+      </c>
+      <c r="F55" s="22" t="inlineStr">
+        <is>
+          <t>HTTP 200 with valid JSON activity summary (empty data OK). Must NOT be 400 from Tomcat.</t>
+        </is>
+      </c>
+      <c r="G55" s="23" t="inlineStr">
+        <is>
+          <t>HTTP 200, username=TESTCORP\\ivanov.a correctly parsed. Response contains valid activity summary with zeroed stats. T-062 backslash fix confirmed working.</t>
+        </is>
+      </c>
+      <c r="H55" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I55" s="22" t="inlineStr">
+        <is>
+          <t>T-062</t>
+        </is>
+      </c>
+      <c r="J55" s="23" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="50" customHeight="1" s="15">
+      <c r="A56" s="22" t="inlineStr">
+        <is>
+          <t>TC-051</t>
+        </is>
+      </c>
+      <c r="B56" s="22" t="inlineStr">
+        <is>
+          <t>User Activity Tracking</t>
+        </is>
+      </c>
+      <c r="C56" s="23" t="inlineStr">
+        <is>
+          <t>Regression: POST focus-intervals with admin JWT (no device) -&gt; 400/403</t>
+        </is>
+      </c>
+      <c r="D56" s="23" t="inlineStr">
+        <is>
+          <t>ingest-gateway deployed on test staging, superadmin JWT token (no device_id claim)</t>
+        </is>
+      </c>
+      <c r="E56" s="22" t="inlineStr">
+        <is>
+          <t>1. Login as superadmin\n2. Send POST /api/ingest/v1/ingest/activity/focus-intervals with valid JSON body but admin JWT\n3. Verify response is 400 or 403, NOT 500</t>
+        </is>
+      </c>
+      <c r="F56" s="22" t="inlineStr">
+        <is>
+          <t>HTTP 400 or 403 (graceful error, not 500 internal server error)</t>
+        </is>
+      </c>
+      <c r="G56" s="23" t="inlineStr">
+        <is>
+          <t>HTTP 400, body: {"error":"Unrecognized field: 'app_name'","code":"BAD_REQUEST"}. Graceful validation error, not 500.</t>
+        </is>
+      </c>
+      <c r="H56" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I56" s="22" t="inlineStr">
+        <is>
+          <t>T-039</t>
+        </is>
+      </c>
+      <c r="J56" s="23" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="50" customHeight="1" s="15">
+      <c r="A57" s="22" t="inlineStr">
+        <is>
+          <t>TC-052</t>
+        </is>
+      </c>
+      <c r="B57" s="22" t="inlineStr">
+        <is>
+          <t>User Activity Tracking</t>
+        </is>
+      </c>
+      <c r="C57" s="23" t="inlineStr">
+        <is>
+          <t>Regression: GET /users pagination page=0 size=5 -&gt; valid response</t>
+        </is>
+      </c>
+      <c r="D57" s="23" t="inlineStr">
+        <is>
+          <t>ingest-gateway deployed on test staging, superadmin JWT token</t>
+        </is>
+      </c>
+      <c r="E57" s="22" t="inlineStr">
+        <is>
+          <t>1. Login as superadmin\n2. Send GET /api/ingest/v1/ingest/users?page=0&amp;size=5\n3. Verify response contains page=0, size=5, total_elements, total_pages</t>
+        </is>
+      </c>
+      <c r="F57" s="22" t="inlineStr">
+        <is>
+          <t>HTTP 200 with JSON: page=0, size=5, content array, total_elements, total_pages fields present</t>
+        </is>
+      </c>
+      <c r="G57" s="23" t="inlineStr">
+        <is>
+          <t>HTTP 200, body: {"content":[],"page":0,"size":5,"total_elements":0,"total_pages":0}. Pagination params correctly applied.</t>
+        </is>
+      </c>
+      <c r="H57" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I57" s="22" t="inlineStr">
+        <is>
+          <t>T-042</t>
+        </is>
+      </c>
+      <c r="J57" s="23" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="50" customHeight="1" s="15">
+      <c r="A58" s="22" t="inlineStr">
+        <is>
+          <t>TC-053</t>
+        </is>
+      </c>
+      <c r="B58" s="22" t="inlineStr">
+        <is>
+          <t>User Activity Tracking</t>
+        </is>
+      </c>
+      <c r="C58" s="23" t="inlineStr">
+        <is>
+          <t>Regression: GET /users/activity future date range -&gt; 200 empty data</t>
+        </is>
+      </c>
+      <c r="D58" s="23" t="inlineStr">
+        <is>
+          <t>ingest-gateway deployed on test staging, superadmin JWT token</t>
+        </is>
+      </c>
+      <c r="E58" s="22" t="inlineStr">
+        <is>
+          <t>1. Login as superadmin\n2. Send GET /api/ingest/v1/ingest/users/activity?username=test&amp;from=2099-01-01T00:00:00Z&amp;to=2099-12-31T23:59:59Z\n3. Verify 200 with empty summary (no error)</t>
+        </is>
+      </c>
+      <c r="F58" s="22" t="inlineStr">
+        <is>
+          <t>HTTP 200 with valid JSON: total_active_ms=0, empty top_apps/top_domains/daily_breakdown</t>
+        </is>
+      </c>
+      <c r="G58" s="23" t="inlineStr">
+        <is>
+          <t>HTTP 200, valid JSON with total_active_ms=0, empty top_apps, top_domains, daily_breakdown. Future dates handled gracefully.</t>
+        </is>
+      </c>
+      <c r="H58" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I58" s="22" t="inlineStr">
+        <is>
+          <t>T-042</t>
+        </is>
+      </c>
+      <c r="J58" s="23" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="50" customHeight="1" s="15">
+      <c r="A59" s="22" t="inlineStr">
+        <is>
+          <t>TC-054</t>
+        </is>
+      </c>
+      <c r="B59" s="22" t="inlineStr">
+        <is>
+          <t>User Activity Tracking</t>
+        </is>
+      </c>
+      <c r="C59" s="23" t="inlineStr">
+        <is>
+          <t>Regression: GET /users/activity missing username -&gt; 400</t>
+        </is>
+      </c>
+      <c r="D59" s="23" t="inlineStr">
+        <is>
+          <t>ingest-gateway deployed on test staging, superadmin JWT token</t>
+        </is>
+      </c>
+      <c r="E59" s="22" t="inlineStr">
+        <is>
+          <t>1. Login as superadmin\n2. Send GET /api/ingest/v1/ingest/users/activity?from=2026-03-01T00:00:00Z&amp;to=2026-03-08T23:59:59Z (no username)\n3. Verify response is 400 BAD_REQUEST</t>
+        </is>
+      </c>
+      <c r="F59" s="22" t="inlineStr">
+        <is>
+          <t>HTTP 400 with error message about missing required parameter 'username'</t>
+        </is>
+      </c>
+      <c r="G59" s="23" t="inlineStr">
+        <is>
+          <t>HTTP 400 с кодом MISSING_PARAMETER после фикса</t>
+        </is>
+      </c>
+      <c r="H59" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I59" s="22" t="inlineStr">
+        <is>
+          <t>T-042</t>
+        </is>
+      </c>
+      <c r="J59" s="23" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="50" customHeight="1" s="15">
+      <c r="A60" s="22" t="inlineStr">
+        <is>
+          <t>TC-055</t>
+        </is>
+      </c>
+      <c r="B60" s="22" t="inlineStr">
+        <is>
+          <t>User Activity Tracking</t>
+        </is>
+      </c>
+      <c r="C60" s="23" t="inlineStr">
+        <is>
+          <t>Regression: SQL injection in /users/apps username -&gt; parameterized, no crash</t>
+        </is>
+      </c>
+      <c r="D60" s="23" t="inlineStr">
+        <is>
+          <t>ingest-gateway deployed on test staging, superadmin JWT token</t>
+        </is>
+      </c>
+      <c r="E60" s="22" t="inlineStr">
+        <is>
+          <t>1. Login as superadmin\n2. Send GET /api/ingest/v1/ingest/users/apps?username=test'; DROP TABLE app_focus_intervals;--&amp;from=2026-03-01T00:00:00Z&amp;to=2026-03-08T23:59:59Z\n3. Verify response is 200 (parameterized query, no injection)</t>
+        </is>
+      </c>
+      <c r="F60" s="22" t="inlineStr">
+        <is>
+          <t>HTTP 200 with valid JSON (empty results OK). No 500 error. Table NOT dropped.</t>
+        </is>
+      </c>
+      <c r="G60" s="23" t="inlineStr">
+        <is>
+          <t>HTTP 200, body contains username with injection payload echoed back safely. Table not dropped. Parameterized queries work correctly.</t>
+        </is>
+      </c>
+      <c r="H60" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I60" s="22" t="inlineStr">
+        <is>
+          <t>T-042</t>
+        </is>
+      </c>
+      <c r="J60" s="23" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="50" customHeight="1" s="15">
+      <c r="A61" s="22" t="inlineStr">
+        <is>
+          <t>TC-056</t>
+        </is>
+      </c>
+      <c r="B61" s="22" t="inlineStr">
+        <is>
+          <t>Token Reveal</t>
+        </is>
+      </c>
+      <c r="C61" s="23" t="inlineStr">
+        <is>
+          <t>Reveal токена superadmin - happy path</t>
+        </is>
+      </c>
+      <c r="D61" s="23" t="inlineStr">
+        <is>
+          <t>Авторизован как superadmin. Создан новый токен устройства с encrypted_token.</t>
+        </is>
+      </c>
+      <c r="E61" s="22" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/device-tokens (создать токен)\n2. Сохранить raw token из ответа\n3. POST /api/v1/device-tokens/{id}/reveal\n4. Сравнить возвращённый token с сохранённым</t>
+        </is>
+      </c>
+      <c r="F61" s="22" t="inlineStr">
+        <is>
+          <t>200 OK, поле token совпадает с оригинальным raw token</t>
+        </is>
+      </c>
+      <c r="G61" s="23" t="inlineStr">
+        <is>
+          <t>200 OK. Revealed token 'drt_aaf4f5192673479197f7cc6306311ecc' совпал с оригинальным raw token. Response: {id, token, name}.</t>
+        </is>
+      </c>
+      <c r="H61" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I61" s="22" t="inlineStr">
+        <is>
+          <t>T-074</t>
+        </is>
+      </c>
+      <c r="J61" s="23" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="50" customHeight="1" s="15">
+      <c r="A62" s="22" t="inlineStr">
+        <is>
+          <t>TC-057</t>
+        </is>
+      </c>
+      <c r="B62" s="22" t="inlineStr">
+        <is>
+          <t>Token Reveal</t>
+        </is>
+      </c>
+      <c r="C62" s="23" t="inlineStr">
+        <is>
+          <t>Reveal токена - без авторизации -&gt; 401</t>
+        </is>
+      </c>
+      <c r="D62" s="23" t="inlineStr">
+        <is>
+          <t>Токен устройства существует. Запрос без Authorization header.</t>
+        </is>
+      </c>
+      <c r="E62" s="22" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/device-tokens/{id}/reveal без Bearer token</t>
+        </is>
+      </c>
+      <c r="F62" s="22" t="inlineStr">
+        <is>
+          <t>401 Unauthorized</t>
+        </is>
+      </c>
+      <c r="G62" s="23" t="inlineStr">
+        <is>
+          <t>401 Unauthorized. Response: {error: 'Authentication required', code: 'UNAUTHORIZED'}.</t>
+        </is>
+      </c>
+      <c r="H62" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I62" s="22" t="inlineStr">
+        <is>
+          <t>T-074</t>
+        </is>
+      </c>
+      <c r="J62" s="23" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="50" customHeight="1" s="15">
+      <c r="A63" s="22" t="inlineStr">
+        <is>
+          <t>TC-058</t>
+        </is>
+      </c>
+      <c r="B63" s="22" t="inlineStr">
+        <is>
+          <t>Token Reveal</t>
+        </is>
+      </c>
+      <c r="C63" s="23" t="inlineStr">
+        <is>
+          <t>Reveal несуществующего токена -&gt; 404</t>
+        </is>
+      </c>
+      <c r="D63" s="23" t="inlineStr">
+        <is>
+          <t>Авторизован как superadmin.</t>
+        </is>
+      </c>
+      <c r="E63" s="22" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/device-tokens/00000000-0000-0000-0000-000000000000/reveal</t>
+        </is>
+      </c>
+      <c r="F63" s="22" t="inlineStr">
+        <is>
+          <t>404 TOKEN_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="G63" s="23" t="inlineStr">
+        <is>
+          <t>404 Not Found. Response: {error: 'Device registration token not found', code: 'TOKEN_NOT_FOUND'}.</t>
+        </is>
+      </c>
+      <c r="H63" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I63" s="22" t="inlineStr">
+        <is>
+          <t>T-074</t>
+        </is>
+      </c>
+      <c r="J63" s="23" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="50" customHeight="1" s="15">
+      <c r="A64" s="22" t="inlineStr">
+        <is>
+          <t>TC-059</t>
+        </is>
+      </c>
+      <c r="B64" s="22" t="inlineStr">
+        <is>
+          <t>Token Reveal</t>
+        </is>
+      </c>
+      <c r="C64" s="23" t="inlineStr">
+        <is>
+          <t>Reveal старого токена без encrypted_token -&gt; 409</t>
+        </is>
+      </c>
+      <c r="D64" s="23" t="inlineStr">
+        <is>
+          <t>Авторизован как superadmin. Существует токен, созданный до миграции V30 (без encrypted_token).</t>
+        </is>
+      </c>
+      <c r="E64" s="22" t="inlineStr">
+        <is>
+          <t>1. Найти старый токен в списке\n2. POST /api/v1/device-tokens/{old_id}/reveal</t>
+        </is>
+      </c>
+      <c r="F64" s="22" t="inlineStr">
+        <is>
+          <t>409 Conflict - encrypted token not available</t>
+        </is>
+      </c>
+      <c r="G64" s="23" t="inlineStr">
+        <is>
+          <t>409 Conflict. Response: {error: 'Token was created before reveal support. Please create a new token.', code: 'TOKEN_REVEAL_NOT_AVAILABLE'}.</t>
+        </is>
+      </c>
+      <c r="H64" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I64" s="22" t="inlineStr">
+        <is>
+          <t>T-074</t>
+        </is>
+      </c>
+      <c r="J64" s="23" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="50" customHeight="1" s="15">
+      <c r="A65" s="22" t="inlineStr">
+        <is>
+          <t>TC-060</t>
+        </is>
+      </c>
+      <c r="B65" s="22" t="inlineStr">
+        <is>
+          <t>Token Hard Delete</t>
+        </is>
+      </c>
+      <c r="C65" s="23" t="inlineStr">
+        <is>
+          <t>Hard delete токена - happy path</t>
+        </is>
+      </c>
+      <c r="D65" s="23" t="inlineStr">
+        <is>
+          <t>Авторизован как superadmin. Создан токен для удаления.</t>
+        </is>
+      </c>
+      <c r="E65" s="22" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/device-tokens (создать токен)\n2. DELETE /api/v1/device-tokens/{id}?hard=true\n3. GET /api/v1/device-tokens/{id} - проверить что 404</t>
+        </is>
+      </c>
+      <c r="F65" s="22" t="inlineStr">
+        <is>
+          <t>204 No Content. Последующий GET возвращает 404.</t>
+        </is>
+      </c>
+      <c r="G65" s="23" t="inlineStr">
+        <is>
+          <t>204 No Content. Токен физически удален из БД. Последующий GET вернул 404 TOKEN_NOT_FOUND.</t>
+        </is>
+      </c>
+      <c r="H65" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I65" s="22" t="inlineStr">
+        <is>
+          <t>T-074</t>
+        </is>
+      </c>
+      <c r="J65" s="23" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="50" customHeight="1" s="15">
+      <c r="A66" s="22" t="inlineStr">
+        <is>
+          <t>TC-061</t>
+        </is>
+      </c>
+      <c r="B66" s="22" t="inlineStr">
+        <is>
+          <t>Token Hard Delete</t>
+        </is>
+      </c>
+      <c r="C66" s="23" t="inlineStr">
+        <is>
+          <t>Soft delete токена (без ?hard) - деактивация</t>
+        </is>
+      </c>
+      <c r="D66" s="23" t="inlineStr">
+        <is>
+          <t>Авторизован как superadmin. Создан токен для удаления.</t>
+        </is>
+      </c>
+      <c r="E66" s="22" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/device-tokens (создать токен)\n2. DELETE /api/v1/device-tokens/{id} (без ?hard)\n3. GET /api/v1/device-tokens/{id} - проверить is_active=false</t>
+        </is>
+      </c>
+      <c r="F66" s="22" t="inlineStr">
+        <is>
+          <t>204 No Content. GET возвращает токен с is_active: false.</t>
+        </is>
+      </c>
+      <c r="G66" s="23" t="inlineStr">
+        <is>
+          <t>204 No Content. GET возвращает токен с is_active: false. Токен деактивирован, но не удален из БД.</t>
+        </is>
+      </c>
+      <c r="H66" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I66" s="22" t="inlineStr">
+        <is>
+          <t>T-074</t>
+        </is>
+      </c>
+      <c r="J66" s="23" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="50" customHeight="1" s="15">
+      <c r="A67" s="22" t="inlineStr">
+        <is>
+          <t>TC-062</t>
+        </is>
+      </c>
+      <c r="B67" s="22" t="inlineStr">
+        <is>
+          <t>User Hard Delete</t>
+        </is>
+      </c>
+      <c r="C67" s="23" t="inlineStr">
+        <is>
+          <t>Hard delete пользователя - happy path</t>
+        </is>
+      </c>
+      <c r="D67" s="23" t="inlineStr">
+        <is>
+          <t>Авторизован как superadmin. Создан тестовый пользователь с ролью OPERATOR.</t>
+        </is>
+      </c>
+      <c r="E67" s="22" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/users (создать пользователя)\n2. DELETE /api/v1/users/{id}?hard=true\n3. GET /api/v1/users/{id} - проверить что 404</t>
+        </is>
+      </c>
+      <c r="F67" s="22" t="inlineStr">
+        <is>
+          <t>204 No Content. Последующий GET возвращает 404.</t>
+        </is>
+      </c>
+      <c r="G67" s="23" t="inlineStr">
+        <is>
+          <t>201 Created -&gt; 204 No Content -&gt; 404 USER_NOT_FOUND. Пользователь testdelete1772975114 создан, hard deleted, подтверждено удаление через GET.</t>
+        </is>
+      </c>
+      <c r="H67" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I67" s="22" t="inlineStr">
+        <is>
+          <t>T-074</t>
+        </is>
+      </c>
+      <c r="J67" s="23" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="50" customHeight="1" s="15">
+      <c r="A68" s="22" t="inlineStr">
+        <is>
+          <t>TC-063</t>
+        </is>
+      </c>
+      <c r="B68" s="22" t="inlineStr">
+        <is>
+          <t>User Hard Delete</t>
+        </is>
+      </c>
+      <c r="C68" s="23" t="inlineStr">
+        <is>
+          <t>Hard delete - попытка удалить себя -&gt; 409 CANNOT_DELETE_SELF</t>
+        </is>
+      </c>
+      <c r="D68" s="23" t="inlineStr">
+        <is>
+          <t>Авторизован как superadmin.</t>
+        </is>
+      </c>
+      <c r="E68" s="22" t="inlineStr">
+        <is>
+          <t>1. GET /api/v1/users/me - получить свой user_id\n2. DELETE /api/v1/users/{my_id}?hard=true</t>
+        </is>
+      </c>
+      <c r="F68" s="22" t="inlineStr">
+        <is>
+          <t>409 Conflict, code: CANNOT_DELETE_SELF</t>
+        </is>
+      </c>
+      <c r="G68" s="23" t="inlineStr">
+        <is>
+          <t>409 Conflict. Response: {error: 'Cannot delete your own account', code: 'CANNOT_DELETE_SELF'}.</t>
+        </is>
+      </c>
+      <c r="H68" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I68" s="22" t="inlineStr">
+        <is>
+          <t>T-074</t>
+        </is>
+      </c>
+      <c r="J68" s="23" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="50" customHeight="1" s="15">
+      <c r="A69" s="22" t="inlineStr">
+        <is>
+          <t>TC-064</t>
+        </is>
+      </c>
+      <c r="B69" s="22" t="inlineStr">
+        <is>
+          <t>User Hard Delete</t>
+        </is>
+      </c>
+      <c r="C69" s="23" t="inlineStr">
+        <is>
+          <t>Hard delete последнего OWNER тенанта -&gt; 409 CANNOT_DELETE_LAST_OWNER</t>
+        </is>
+      </c>
+      <c r="D69" s="23" t="inlineStr">
+        <is>
+          <t>Авторизован как superadmin. Пользователь test - единственный OWNER в tenant test-org.</t>
+        </is>
+      </c>
+      <c r="E69" s="22" t="inlineStr">
+        <is>
+          <t>1. Получить ID пользователя test через логин\n2. DELETE /api/v1/users/{test_id}?hard=true от superadmin</t>
+        </is>
+      </c>
+      <c r="F69" s="22" t="inlineStr">
+        <is>
+          <t>409 Conflict, code: CANNOT_DELETE_LAST_OWNER</t>
+        </is>
+      </c>
+      <c r="G69" s="23" t="inlineStr">
+        <is>
+          <t>409 Conflict. Response: {error: 'Cannot delete the last owner of the tenant', code: 'CANNOT_DELETE_LAST_OWNER'}. Тестировано через TENANT_ADMIN в том же тенанте.</t>
+        </is>
+      </c>
+      <c r="H69" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I69" s="22" t="inlineStr">
+        <is>
+          <t>T-074</t>
+        </is>
+      </c>
+      <c r="J69" s="23" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="50" customHeight="1" s="15">
+      <c r="A70" s="22" t="inlineStr">
+        <is>
+          <t>TC-065</t>
+        </is>
+      </c>
+      <c r="B70" s="22" t="inlineStr">
+        <is>
+          <t>Token Reveal</t>
+        </is>
+      </c>
+      <c r="C70" s="23" t="inlineStr">
+        <is>
+          <t>Reveal без permission DEVICE_TOKENS:REVEAL -&gt; 403</t>
+        </is>
+      </c>
+      <c r="D70" s="23" t="inlineStr">
+        <is>
+          <t>Создан пользователь с ролью OPERATOR (без DEVICE_TOKENS:REVEAL). Токен устройства существует.</t>
+        </is>
+      </c>
+      <c r="E70" s="22" t="inlineStr">
+        <is>
+          <t>1. Логин под OPERATOR\n2. POST /api/v1/device-tokens/{id}/reveal</t>
+        </is>
+      </c>
+      <c r="F70" s="22" t="inlineStr">
+        <is>
+          <t>403 Forbidden</t>
+        </is>
+      </c>
+      <c r="G70" s="23" t="inlineStr">
+        <is>
+          <t>403 Forbidden. Response: {error: 'You do not have permission: DEVICE_TOKENS:REVEAL', code: 'ACCESS_DENIED'}. OPERATOR не имеет permission DEVICE_TOKENS:REVEAL.</t>
+        </is>
+      </c>
+      <c r="H70" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I70" s="22" t="inlineStr">
+        <is>
+          <t>T-074</t>
+        </is>
+      </c>
+      <c r="J70" s="23" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="50" customHeight="1" s="15">
+      <c r="A71" s="22" t="inlineStr">
+        <is>
+          <t>TC-066</t>
+        </is>
+      </c>
+      <c r="B71" s="22" t="inlineStr">
+        <is>
+          <t>Audit Log</t>
+        </is>
+      </c>
+      <c r="C71" s="23" t="inlineStr">
+        <is>
+          <t>Аудит записи для reveal и hard delete операций</t>
+        </is>
+      </c>
+      <c r="D71" s="23" t="inlineStr">
+        <is>
+          <t>Выполнены операции reveal, hard delete token, hard delete user.</t>
+        </is>
+      </c>
+      <c r="E71" s="22" t="inlineStr">
+        <is>
+          <t>1. GET /api/v1/audit?size=20\n2. Проверить наличие записей DEVICE_TOKEN_REVEALED, DEVICE_TOKEN_HARD_DELETED, USER_HARD_DELETED</t>
+        </is>
+      </c>
+      <c r="F71" s="22" t="inlineStr">
+        <is>
+          <t>Audit log содержит записи всех операций с корректным action, resource, timestamp</t>
+        </is>
+      </c>
+      <c r="G71" s="23" t="inlineStr">
+        <is>
+          <t>Audit log содержит: DEVICE_TOKEN_REVEALED (resource_type=DEVICE_TOKENS, details={name}), DEVICE_TOKEN_HARD_DELETED (details={name}), USER_HARD_DELETED (details={username, roles}). Все с корректным user_id, ip_address, timestamp.</t>
+        </is>
+      </c>
+      <c r="H71" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I71" s="22" t="inlineStr">
+        <is>
+          <t>T-074</t>
+        </is>
+      </c>
+      <c r="J71" s="23" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="50" customHeight="1" s="15">
+      <c r="A72" s="22" t="inlineStr">
+        <is>
+          <t>TC-067</t>
+        </is>
+      </c>
+      <c r="B72" s="22" t="inlineStr">
+        <is>
+          <t>Token Hard Delete</t>
+        </is>
+      </c>
+      <c r="C72" s="23" t="inlineStr">
+        <is>
+          <t>Hard delete токена - проверка что токен удалён из БД (GET -&gt; 404)</t>
+        </is>
+      </c>
+      <c r="D72" s="23" t="inlineStr">
+        <is>
+          <t>Выполнен hard delete токена.</t>
+        </is>
+      </c>
+      <c r="E72" s="22" t="inlineStr">
+        <is>
+          <t>1. GET /api/v1/device-tokens/{deleted_id}</t>
+        </is>
+      </c>
+      <c r="F72" s="22" t="inlineStr">
+        <is>
+          <t>404 TOKEN_NOT_FOUND - токен физически удалён из БД</t>
+        </is>
+      </c>
+      <c r="G72" s="23" t="inlineStr">
+        <is>
+          <t>404 TOKEN_NOT_FOUND. Токен e3c30ceb физически удалён из БД после hard delete.</t>
+        </is>
+      </c>
+      <c r="H72" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I72" s="22" t="inlineStr">
+        <is>
+          <t>T-074</t>
+        </is>
+      </c>
+      <c r="J72" s="23" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="50" customHeight="1" s="15">
+      <c r="A73" s="22" t="inlineStr">
+        <is>
+          <t>TC-068</t>
+        </is>
+      </c>
+      <c r="B73" s="22" t="inlineStr">
+        <is>
+          <t>User Hard Delete</t>
+        </is>
+      </c>
+      <c r="C73" s="23" t="inlineStr">
+        <is>
+          <t>Hard delete - проверка что пользователь удалён (GET -&gt; 404)</t>
+        </is>
+      </c>
+      <c r="D73" s="23" t="inlineStr">
+        <is>
+          <t>Выполнен hard delete пользователя.</t>
+        </is>
+      </c>
+      <c r="E73" s="22" t="inlineStr">
+        <is>
+          <t>1. GET /api/v1/users/{deleted_id}</t>
+        </is>
+      </c>
+      <c r="F73" s="22" t="inlineStr">
+        <is>
+          <t>404 USER_NOT_FOUND - пользователь физически удалён из БД</t>
+        </is>
+      </c>
+      <c r="G73" s="23" t="inlineStr">
+        <is>
+          <t>404 USER_NOT_FOUND. Пользователь 5be83dd1 физически удалён из БД после hard delete.</t>
+        </is>
+      </c>
+      <c r="H73" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I73" s="22" t="inlineStr">
+        <is>
+          <t>T-074</t>
+        </is>
+      </c>
+      <c r="J73" s="23" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="50" customHeight="1" s="15">
+      <c r="A74" s="20" t="inlineStr">
+        <is>
+          <t>TC-069</t>
+        </is>
+      </c>
+      <c r="B74" s="20" t="inlineStr">
+        <is>
+          <t>Windows Agent - SessionLogon</t>
+        </is>
+      </c>
+      <c r="C74" s="21" t="inlineStr">
+        <is>
+          <t>Запись стартует автоматически после перелогина</t>
+        </is>
+      </c>
+      <c r="D74" s="21" t="inlineStr">
+        <is>
+          <t>1. Windows-машина с установленным KaderoAgent\n2. Служба KaderoAgent запущена\n3. AutoStart=true\n4. Пользователь A залогинен, запись идет</t>
+        </is>
+      </c>
+      <c r="E74" s="20" t="inlineStr">
+        <is>
+          <t>1. Выполнить Log off пользователя A\n2. Дождаться экрана входа\n3. Залогиниться под пользователем B\n4. Открыть конфигуратор агента (трей)</t>
+        </is>
+      </c>
+      <c r="F74" s="20" t="inlineStr">
+        <is>
+          <t>Запись автоматически стартует для пользователя B. В трее зеленая точка, статус 'Запись'. В логах: SESSION_LOGOFF, SESSION_LOGON, HandleSessionLogonAsync, Recording started.</t>
+        </is>
+      </c>
+      <c r="G74" s="21" t="inlineStr"/>
+      <c r="H74" s="20" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="I74" s="20" t="inlineStr">
+        <is>
+          <t>T-075</t>
+        </is>
+      </c>
+      <c r="J74" s="21" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="50" customHeight="1" s="15">
+      <c r="A75" s="20" t="inlineStr">
+        <is>
+          <t>TC-070</t>
+        </is>
+      </c>
+      <c r="B75" s="20" t="inlineStr">
+        <is>
+          <t>Windows Agent - SessionLogon</t>
+        </is>
+      </c>
+      <c r="C75" s="21" t="inlineStr">
+        <is>
+          <t>Username корректен после перелогина</t>
+        </is>
+      </c>
+      <c r="D75" s="21" t="inlineStr">
+        <is>
+          <t>1. KaderoAgent установлен и запущен\n2. Пользователь A залогинен, запись идет\n3. User Activity Tracking включен</t>
+        </is>
+      </c>
+      <c r="E75" s="20" t="inlineStr">
+        <is>
+          <t>1. Log off пользователя A\n2. Залогиниться под пользователем B\n3. Дождаться отправки audit-events и focus-intervals (30с)\n4. Проверить в серверных логах username в запросах</t>
+        </is>
+      </c>
+      <c r="F75" s="20" t="inlineStr">
+        <is>
+          <t>Audit-events и focus-intervals содержат username пользователя B (DOMAIN\UserB), а не пользователя A.</t>
+        </is>
+      </c>
+      <c r="G75" s="21" t="inlineStr"/>
+      <c r="H75" s="20" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="I75" s="20" t="inlineStr">
+        <is>
+          <t>T-076</t>
+        </is>
+      </c>
+      <c r="J75" s="21" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="50" customHeight="1" s="15">
+      <c r="A76" s="20" t="inlineStr">
+        <is>
+          <t>TC-071</t>
+        </is>
+      </c>
+      <c r="B76" s="20" t="inlineStr">
+        <is>
+          <t>Windows Agent - HTTP Error Handling</t>
+        </is>
+      </c>
+      <c r="C76" s="21" t="inlineStr">
+        <is>
+          <t>Auto-refresh JWT при 401 ответе сервера</t>
+        </is>
+      </c>
+      <c r="D76" s="21" t="inlineStr">
+        <is>
+          <t>1. KaderoAgent запущен и записывает\n2. Access token истекает через 1 минуту</t>
+        </is>
+      </c>
+      <c r="E76" s="20" t="inlineStr">
+        <is>
+          <t>1. Дождаться истечения access token\n2. Наблюдать логи агента при следующем heartbeat/upload\n3. Проверить, что агент автоматически рефрешит токен\n4. Проверить, что запрос повторяется с новым токеном</t>
+        </is>
+      </c>
+      <c r="F76" s="20" t="inlineStr">
+        <is>
+          <t>В логах: 'Got 401, attempting token refresh...', затем успешный запрос. Нет ошибок 'Response status code does not indicate success'.</t>
+        </is>
+      </c>
+      <c r="G76" s="21" t="inlineStr"/>
+      <c r="H76" s="20" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="I76" s="20" t="inlineStr">
+        <is>
+          <t>T-077</t>
+        </is>
+      </c>
+      <c r="J76" s="21" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="50" customHeight="1" s="15">
+      <c r="A77" s="20" t="inlineStr">
+        <is>
+          <t>TC-072</t>
+        </is>
+      </c>
+      <c r="B77" s="20" t="inlineStr">
+        <is>
+          <t>Windows Agent - HTTP Error Handling</t>
+        </is>
+      </c>
+      <c r="C77" s="21" t="inlineStr">
+        <is>
+          <t>Response body логируется при HTTP-ошибках</t>
+        </is>
+      </c>
+      <c r="D77" s="21" t="inlineStr">
+        <is>
+          <t>1. KaderoAgent запущен\n2. Сервер доступен</t>
+        </is>
+      </c>
+      <c r="E77" s="20" t="inlineStr">
+        <is>
+          <t>1. Сымитировать ошибку сервера (напр. удалить устройство -&gt; 404 на heartbeat)\n2. Проверить логи агента</t>
+        </is>
+      </c>
+      <c r="F77" s="20" t="inlineStr">
+        <is>
+          <t>В логах видно: HTTP PUT /api/cp/v1/devices/.../heartbeat failed: 404 - {"error":"Device not found","code":"DEVICE_NOT_FOUND"}. Тело ответа залогировано, а не только status code.</t>
+        </is>
+      </c>
+      <c r="G77" s="21" t="inlineStr"/>
+      <c r="H77" s="20" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="I77" s="20" t="inlineStr">
+        <is>
+          <t>T-078</t>
+        </is>
+      </c>
+      <c r="J77" s="21" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="50" customHeight="1" s="15">
+      <c r="A78" s="20" t="inlineStr">
+        <is>
+          <t>TC-073</t>
+        </is>
+      </c>
+      <c r="B78" s="20" t="inlineStr">
+        <is>
+          <t>Windows Agent - SessionLogon</t>
+        </is>
+      </c>
+      <c r="C78" s="21" t="inlineStr">
+        <is>
+          <t>Перелогин на того же пользователя - запись стартует</t>
+        </is>
+      </c>
+      <c r="D78" s="21" t="inlineStr">
+        <is>
+          <t>1. KaderoAgent запущен, AutoStart=true\n2. Пользователь A залогинен, запись идет</t>
+        </is>
+      </c>
+      <c r="E78" s="20" t="inlineStr">
+        <is>
+          <t>1. Log off пользователя A\n2. Снова залогиниться под пользователем A\n3. Проверить статус записи в трее</t>
+        </is>
+      </c>
+      <c r="F78" s="20" t="inlineStr">
+        <is>
+          <t>Запись стартует. Новая серверная сессия создана (новый session_id). Старая сессия корректно завершена (status=completed).</t>
+        </is>
+      </c>
+      <c r="G78" s="21" t="inlineStr"/>
+      <c r="H78" s="20" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="I78" s="20" t="inlineStr">
+        <is>
+          <t>T-075</t>
+        </is>
+      </c>
+      <c r="J78" s="21" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="50" customHeight="1" s="15">
+      <c r="A79" s="20" t="inlineStr">
+        <is>
+          <t>TC-074</t>
+        </is>
+      </c>
+      <c r="B79" s="20" t="inlineStr">
+        <is>
+          <t>Windows Agent - HTTP Error Handling</t>
+        </is>
+      </c>
+      <c r="C79" s="21" t="inlineStr">
+        <is>
+          <t>Stale segments с несуществующей session отбрасываются</t>
+        </is>
+      </c>
+      <c r="D79" s="21" t="inlineStr">
+        <is>
+          <t>1. KaderoAgent запущен\n2. В SQLite есть pending segments с session_id от закрытой сессии</t>
+        </is>
+      </c>
+      <c r="E79" s="20" t="inlineStr">
+        <is>
+          <t>1. Перезапустить службу KaderoAgent\n2. Агент пытается загрузить pending segments\n3. Presign возвращает 404 (session not found)</t>
+        </is>
+      </c>
+      <c r="F79" s="20" t="inlineStr">
+        <is>
+          <t>Сегменты помечаются как 'uploaded' (discarded), не ставятся в бесконечный retry. В логах: 'Session {id} not found (404), discarding segment'.</t>
+        </is>
+      </c>
+      <c r="G79" s="21" t="inlineStr"/>
+      <c r="H79" s="20" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="I79" s="20" t="inlineStr">
+        <is>
+          <t>T-079</t>
+        </is>
+      </c>
+      <c r="J79" s="21" t="inlineStr">
+        <is>
+          <t>08.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="50" customHeight="1" s="15">
+      <c r="A80" s="22" t="inlineStr">
+        <is>
+          <t>TC-075</t>
+        </is>
+      </c>
+      <c r="B80" s="22" t="inlineStr">
+        <is>
+          <t>Catalogs API</t>
+        </is>
+      </c>
+      <c r="C80" s="23" t="inlineStr">
+        <is>
+          <t>GET /catalogs/groups APP - lazy seed создаёт 8 групп</t>
+        </is>
+      </c>
+      <c r="D80" s="23" t="inlineStr">
+        <is>
+          <t>Superadmin авторизован, test стейджинг</t>
+        </is>
+      </c>
+      <c r="E80" s="22" t="inlineStr">
+        <is>
+          <t>1. GET /catalogs/groups?group_type=APP с Bearer токеном superadmin</t>
+        </is>
+      </c>
+      <c r="F80" s="22" t="inlineStr">
+        <is>
+          <t>200, groups[] непустой (8 APP групп), каждая группа имеет id, name, color, item_count</t>
+        </is>
+      </c>
+      <c r="G80" s="23" t="inlineStr">
+        <is>
+          <t>200, 8 APP групп: Мессенджеры(8), Офисные(9), Браузеры(8), Разработка(12), Системные(11), Мультимедиа(8), CRM/Телефония(7), Прочее(0,default). Все поля id/name/color/item_count присутствуют.</t>
+        </is>
+      </c>
+      <c r="H80" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I80" s="22" t="inlineStr">
+        <is>
+          <t>T-106</t>
+        </is>
+      </c>
+      <c r="J80" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="50" customHeight="1" s="15">
+      <c r="A81" s="22" t="inlineStr">
+        <is>
+          <t>TC-076</t>
+        </is>
+      </c>
+      <c r="B81" s="22" t="inlineStr">
+        <is>
+          <t>Catalogs API</t>
+        </is>
+      </c>
+      <c r="C81" s="23" t="inlineStr">
+        <is>
+          <t>GET /catalogs/groups SITE - lazy seed создаёт 10 групп</t>
+        </is>
+      </c>
+      <c r="D81" s="23" t="inlineStr">
+        <is>
+          <t>Superadmin авторизован, test стейджинг</t>
+        </is>
+      </c>
+      <c r="E81" s="22" t="inlineStr">
+        <is>
+          <t>1. GET /catalogs/groups?group_type=SITE с Bearer токеном superadmin</t>
+        </is>
+      </c>
+      <c r="F81" s="22" t="inlineStr">
+        <is>
+          <t>200, 10 SITE групп с id, name, color, item_count</t>
+        </is>
+      </c>
+      <c r="G81" s="23" t="inlineStr">
+        <is>
+          <t>200, 10 SITE групп: Почта(7), Поиск(5), Мессенджеры(6), Соцсети(8), Облачные(5), Разработка(7), Видео(6), Новости(6), CRM/Бизнес(7), Прочее(0,default). Все item_count корректны.</t>
+        </is>
+      </c>
+      <c r="H81" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I81" s="22" t="inlineStr">
+        <is>
+          <t>T-106</t>
+        </is>
+      </c>
+      <c r="J81" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="50" customHeight="1" s="15">
+      <c r="A82" s="22" t="inlineStr">
+        <is>
+          <t>TC-077</t>
+        </is>
+      </c>
+      <c r="B82" s="22" t="inlineStr">
+        <is>
+          <t>Catalogs API</t>
+        </is>
+      </c>
+      <c r="C82" s="23" t="inlineStr">
+        <is>
+          <t>POST /catalogs/groups - создание кастомной APP группы</t>
+        </is>
+      </c>
+      <c r="D82" s="23" t="inlineStr">
+        <is>
+          <t>Superadmin авторизован, test стейджинг</t>
+        </is>
+      </c>
+      <c r="E82" s="22" t="inlineStr">
+        <is>
+          <t>1. POST /catalogs/groups с body: name=Тестовая группа, group_type=APP, color=#FF5733, sort_order=99</t>
+        </is>
+      </c>
+      <c r="F82" s="22" t="inlineStr">
+        <is>
+          <t>201, созданная группа с id, name, color</t>
+        </is>
+      </c>
+      <c r="G82" s="23" t="inlineStr">
+        <is>
+          <t>201, группа создана: id=6ad63028..., name=Тестовая группа, color=#FF5733, sort_order=99, default=false</t>
+        </is>
+      </c>
+      <c r="H82" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I82" s="22" t="inlineStr">
+        <is>
+          <t>T-106</t>
+        </is>
+      </c>
+      <c r="J82" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="50" customHeight="1" s="15">
+      <c r="A83" s="22" t="inlineStr">
+        <is>
+          <t>TC-078</t>
+        </is>
+      </c>
+      <c r="B83" s="22" t="inlineStr">
+        <is>
+          <t>Catalogs API</t>
+        </is>
+      </c>
+      <c r="C83" s="23" t="inlineStr">
+        <is>
+          <t>PUT /catalogs/groups/{id} - обновление группы</t>
+        </is>
+      </c>
+      <c r="D83" s="23" t="inlineStr">
+        <is>
+          <t>Superadmin авторизован, кастомная группа создана (TC-077)</t>
+        </is>
+      </c>
+      <c r="E83" s="22" t="inlineStr">
+        <is>
+          <t>1. PUT /catalogs/groups/{id} с body: name=Обновлённая группа, color=#00FF00</t>
+        </is>
+      </c>
+      <c r="F83" s="22" t="inlineStr">
+        <is>
+          <t>200, обновлённое имя и цвет</t>
+        </is>
+      </c>
+      <c r="G83" s="23" t="inlineStr">
+        <is>
+          <t>200, имя обновлено на Обновлённая группа, цвет обновлён на #00FF00</t>
+        </is>
+      </c>
+      <c r="H83" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I83" s="22" t="inlineStr">
+        <is>
+          <t>T-106</t>
+        </is>
+      </c>
+      <c r="J83" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="50" customHeight="1" s="15">
+      <c r="A84" s="22" t="inlineStr">
+        <is>
+          <t>TC-079</t>
+        </is>
+      </c>
+      <c r="B84" s="22" t="inlineStr">
+        <is>
+          <t>Catalogs API</t>
+        </is>
+      </c>
+      <c r="C84" s="23" t="inlineStr">
+        <is>
+          <t>POST /catalogs/groups/{id}/items - добавление item в группу</t>
+        </is>
+      </c>
+      <c r="D84" s="23" t="inlineStr">
+        <is>
+          <t>Superadmin авторизован, кастомная группа создана</t>
+        </is>
+      </c>
+      <c r="E84" s="22" t="inlineStr">
+        <is>
+          <t>1. POST /catalogs/groups/{id}/items с body: pattern=testapp.exe, match_type=EXACT</t>
+        </is>
+      </c>
+      <c r="F84" s="22" t="inlineStr">
+        <is>
+          <t>201, item создан</t>
+        </is>
+      </c>
+      <c r="G84" s="23" t="inlineStr">
+        <is>
+          <t>201, item создан: id=980f5a93..., pattern=testapp.exe, match_type=EXACT, item_type=APP</t>
+        </is>
+      </c>
+      <c r="H84" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I84" s="22" t="inlineStr">
+        <is>
+          <t>T-106</t>
+        </is>
+      </c>
+      <c r="J84" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="50" customHeight="1" s="15">
+      <c r="A85" s="22" t="inlineStr">
+        <is>
+          <t>TC-080</t>
+        </is>
+      </c>
+      <c r="B85" s="22" t="inlineStr">
+        <is>
+          <t>Catalogs API</t>
+        </is>
+      </c>
+      <c r="C85" s="23" t="inlineStr">
+        <is>
+          <t>POST /catalogs/groups/{id}/items/batch - пакетное добавление items</t>
+        </is>
+      </c>
+      <c r="D85" s="23" t="inlineStr">
+        <is>
+          <t>Superadmin авторизован, кастомная группа создана</t>
+        </is>
+      </c>
+      <c r="E85" s="22" t="inlineStr">
+        <is>
+          <t>1. POST /catalogs/groups/{id}/items/batch с body: items=[{pattern:app1.exe}, {pattern:app2.exe}]</t>
+        </is>
+      </c>
+      <c r="F85" s="22" t="inlineStr">
+        <is>
+          <t>201, created: 2</t>
+        </is>
+      </c>
+      <c r="G85" s="23" t="inlineStr">
+        <is>
+          <t>201, создано 2 items: app1.exe и app2.exe (оба EXACT)</t>
+        </is>
+      </c>
+      <c r="H85" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I85" s="22" t="inlineStr">
+        <is>
+          <t>T-106</t>
+        </is>
+      </c>
+      <c r="J85" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="50" customHeight="1" s="15">
+      <c r="A86" s="22" t="inlineStr">
+        <is>
+          <t>TC-081</t>
+        </is>
+      </c>
+      <c r="B86" s="22" t="inlineStr">
+        <is>
+          <t>Catalogs API</t>
+        </is>
+      </c>
+      <c r="C86" s="23" t="inlineStr">
+        <is>
+          <t>GET /catalogs/groups/{id}/items - получение items группы</t>
+        </is>
+      </c>
+      <c r="D86" s="23" t="inlineStr">
+        <is>
+          <t>Superadmin авторизован, items добавлены (TC-079, TC-080)</t>
+        </is>
+      </c>
+      <c r="E86" s="22" t="inlineStr">
+        <is>
+          <t>1. GET /catalogs/groups/{id}/items</t>
+        </is>
+      </c>
+      <c r="F86" s="22" t="inlineStr">
+        <is>
+          <t>200, 3 items (testapp.exe, app1.exe, app2.exe)</t>
+        </is>
+      </c>
+      <c r="G86" s="23" t="inlineStr">
+        <is>
+          <t>200, 3 items: testapp.exe, app1.exe, app2.exe - все ожидаемые паттерны присутствуют</t>
+        </is>
+      </c>
+      <c r="H86" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I86" s="22" t="inlineStr">
+        <is>
+          <t>T-106</t>
+        </is>
+      </c>
+      <c r="J86" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="50" customHeight="1" s="15">
+      <c r="A87" s="22" t="inlineStr">
+        <is>
+          <t>TC-082</t>
+        </is>
+      </c>
+      <c r="B87" s="22" t="inlineStr">
+        <is>
+          <t>Catalogs API</t>
+        </is>
+      </c>
+      <c r="C87" s="23" t="inlineStr">
+        <is>
+          <t>DELETE /catalogs/groups/{id} - удаление кастомной группы с каскадом</t>
+        </is>
+      </c>
+      <c r="D87" s="23" t="inlineStr">
+        <is>
+          <t>Superadmin авторизован, кастомная группа с items существует</t>
+        </is>
+      </c>
+      <c r="E87" s="22" t="inlineStr">
+        <is>
+          <t>1. DELETE /catalogs/groups/{id}</t>
+        </is>
+      </c>
+      <c r="F87" s="22" t="inlineStr">
+        <is>
+          <t>204, каскадное удаление items</t>
+        </is>
+      </c>
+      <c r="G87" s="23" t="inlineStr">
+        <is>
+          <t>204, кастомная группа удалена. Каскадное удаление items подтверждено.</t>
+        </is>
+      </c>
+      <c r="H87" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I87" s="22" t="inlineStr">
+        <is>
+          <t>T-106</t>
+        </is>
+      </c>
+      <c r="J87" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="50" customHeight="1" s="15">
+      <c r="A88" s="22" t="inlineStr">
+        <is>
+          <t>TC-083</t>
+        </is>
+      </c>
+      <c r="B88" s="22" t="inlineStr">
+        <is>
+          <t>Catalogs API</t>
+        </is>
+      </c>
+      <c r="C88" s="23" t="inlineStr">
+        <is>
+          <t>DELETE default group - запрет удаления дефолтной группы (400)</t>
+        </is>
+      </c>
+      <c r="D88" s="23" t="inlineStr">
+        <is>
+          <t>Superadmin авторизован, есть группа с is_default=true</t>
+        </is>
+      </c>
+      <c r="E88" s="22" t="inlineStr">
+        <is>
+          <t>1. Найти id группы с is_default=true\n2. DELETE /catalogs/groups/{id}</t>
+        </is>
+      </c>
+      <c r="F88" s="22" t="inlineStr">
+        <is>
+          <t>400, Cannot delete default group</t>
+        </is>
+      </c>
+      <c r="G88" s="23" t="inlineStr">
+        <is>
+          <t>400, Cannot delete the default group - запрет удаления дефолтной группы работает корректно</t>
+        </is>
+      </c>
+      <c r="H88" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I88" s="22" t="inlineStr">
+        <is>
+          <t>T-106</t>
+        </is>
+      </c>
+      <c r="J88" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="50" customHeight="1" s="15">
+      <c r="A89" s="22" t="inlineStr">
+        <is>
+          <t>TC-084</t>
+        </is>
+      </c>
+      <c r="B89" s="22" t="inlineStr">
+        <is>
+          <t>Catalogs API</t>
+        </is>
+      </c>
+      <c r="C89" s="23" t="inlineStr">
+        <is>
+          <t>POST /catalogs/aliases - создание алиаса</t>
+        </is>
+      </c>
+      <c r="D89" s="23" t="inlineStr">
+        <is>
+          <t>Superadmin авторизован, test стейджинг</t>
+        </is>
+      </c>
+      <c r="E89" s="22" t="inlineStr">
+        <is>
+          <t>1. POST /catalogs/aliases с body: alias_type=APP, original=mytest.exe, display_name=Мой тест</t>
+        </is>
+      </c>
+      <c r="F89" s="22" t="inlineStr">
+        <is>
+          <t>201, алиас создан с id</t>
+        </is>
+      </c>
+      <c r="G89" s="23" t="inlineStr">
+        <is>
+          <t>201, алиас создан: id=93e5505d..., original=mytest.exe, display_name=Мой тест</t>
+        </is>
+      </c>
+      <c r="H89" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I89" s="22" t="inlineStr">
+        <is>
+          <t>T-106</t>
+        </is>
+      </c>
+      <c r="J89" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="50" customHeight="1" s="15">
+      <c r="A90" s="22" t="inlineStr">
+        <is>
+          <t>TC-085</t>
+        </is>
+      </c>
+      <c r="B90" s="22" t="inlineStr">
+        <is>
+          <t>Catalogs API</t>
+        </is>
+      </c>
+      <c r="C90" s="23" t="inlineStr">
+        <is>
+          <t>GET /catalogs/aliases - список алиасов с пагинацией</t>
+        </is>
+      </c>
+      <c r="D90" s="23" t="inlineStr">
+        <is>
+          <t>Superadmin авторизован, алиасы существуют (seed + TC-084)</t>
+        </is>
+      </c>
+      <c r="E90" s="22" t="inlineStr">
+        <is>
+          <t>1. GET /catalogs/aliases?alias_type=APP&amp;page=0&amp;size=10</t>
+        </is>
+      </c>
+      <c r="F90" s="22" t="inlineStr">
+        <is>
+          <t>200, пагинированный список с алиасами</t>
+        </is>
+      </c>
+      <c r="G90" s="23" t="inlineStr">
+        <is>
+          <t>200, total_elements=43, пагинация page=0/size=10 работает. Алиасы seed (brave.exe-&gt;Brave, calc.exe-&gt;Калькулятор и др.) присутствуют.</t>
+        </is>
+      </c>
+      <c r="H90" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I90" s="22" t="inlineStr">
+        <is>
+          <t>T-106</t>
+        </is>
+      </c>
+      <c r="J90" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="50" customHeight="1" s="15">
+      <c r="A91" s="22" t="inlineStr">
+        <is>
+          <t>TC-086</t>
+        </is>
+      </c>
+      <c r="B91" s="22" t="inlineStr">
+        <is>
+          <t>Catalogs API</t>
+        </is>
+      </c>
+      <c r="C91" s="23" t="inlineStr">
+        <is>
+          <t>Duplicate pattern - 409 PATTERN_ALREADY_ASSIGNED</t>
+        </is>
+      </c>
+      <c r="D91" s="23" t="inlineStr">
+        <is>
+          <t>Superadmin авторизован, chrome.exe уже в seed группе</t>
+        </is>
+      </c>
+      <c r="E91" s="22" t="inlineStr">
+        <is>
+          <t>1. POST /catalogs/groups/{другая_группа}/items с pattern=chrome.exe</t>
+        </is>
+      </c>
+      <c r="F91" s="22" t="inlineStr">
+        <is>
+          <t>409, PATTERN_ALREADY_ASSIGNED</t>
+        </is>
+      </c>
+      <c r="G91" s="23" t="inlineStr">
+        <is>
+          <t>400, Pattern chrome.exe already exists in another group. Примечание: HTTP 400 вместо ожидаемого 409, но функциональность работает корректно.</t>
+        </is>
+      </c>
+      <c r="H91" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I91" s="22" t="inlineStr">
+        <is>
+          <t>T-106</t>
+        </is>
+      </c>
+      <c r="J91" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="50" customHeight="1" s="15">
+      <c r="A92" s="22" t="inlineStr">
+        <is>
+          <t>TC-087</t>
+        </is>
+      </c>
+      <c r="B92" s="22" t="inlineStr">
+        <is>
+          <t>Dashboard API</t>
+        </is>
+      </c>
+      <c r="C92" s="23" t="inlineStr">
+        <is>
+          <t>GET /dashboard/metrics - метрики тенанта</t>
+        </is>
+      </c>
+      <c r="D92" s="23" t="inlineStr">
+        <is>
+          <t>Superadmin авторизован, test стейджинг</t>
+        </is>
+      </c>
+      <c r="E92" s="22" t="inlineStr">
+        <is>
+          <t>1. GET /dashboard/metrics</t>
+        </is>
+      </c>
+      <c r="F92" s="22" t="inlineStr">
+        <is>
+          <t>200, JSON с connected_devices, total_devices, active_devices, tokens_used, tokens_total, video_size_bytes</t>
+        </is>
+      </c>
+      <c r="G92" s="23" t="inlineStr">
+        <is>
+          <t>200, JSON: connected_devices=0, total_devices=2, active_users=0, tokens_used=2, tokens_total=15, video_size_bytes=0. Все ожидаемые ключи присутствуют.</t>
+        </is>
+      </c>
+      <c r="H92" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I92" s="22" t="inlineStr">
+        <is>
+          <t>T-106</t>
+        </is>
+      </c>
+      <c r="J92" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="50" customHeight="1" s="15">
+      <c r="A93" s="22" t="inlineStr">
+        <is>
+          <t>TC-088</t>
+        </is>
+      </c>
+      <c r="B93" s="22" t="inlineStr">
+        <is>
+          <t>Dashboard API</t>
+        </is>
+      </c>
+      <c r="C93" s="23" t="inlineStr">
+        <is>
+          <t>GET /dashboard/group-timeline - зональная гистограмма APP</t>
+        </is>
+      </c>
+      <c r="D93" s="23" t="inlineStr">
+        <is>
+          <t>Superadmin авторизован, test стейджинг</t>
+        </is>
+      </c>
+      <c r="E93" s="22" t="inlineStr">
+        <is>
+          <t>1. GET /dashboard/group-timeline?group_type=APP&amp;from=2026-02-01&amp;to=2026-03-08&amp;timezone=Europe/Moscow</t>
+        </is>
+      </c>
+      <c r="F93" s="22" t="inlineStr">
+        <is>
+          <t>200, JSON с groups[] и days[]</t>
+        </is>
+      </c>
+      <c r="G93" s="23" t="inlineStr">
+        <is>
+          <t>200, groups: 8 (Мессенджеры, Офисные приложения, Браузеры...), days: 0 (нет данных focus_intervals в тенанте superadmin). Структура ответа корректна.</t>
+        </is>
+      </c>
+      <c r="H93" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I93" s="22" t="inlineStr">
+        <is>
+          <t>T-106</t>
+        </is>
+      </c>
+      <c r="J93" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="50" customHeight="1" s="15">
+      <c r="A94" s="22" t="inlineStr">
+        <is>
+          <t>TC-089</t>
+        </is>
+      </c>
+      <c r="B94" s="22" t="inlineStr">
+        <is>
+          <t>Dashboard API</t>
+        </is>
+      </c>
+      <c r="C94" s="23" t="inlineStr">
+        <is>
+          <t>GET /dashboard/top-ungrouped - топ несгруппированных элементов</t>
+        </is>
+      </c>
+      <c r="D94" s="23" t="inlineStr">
+        <is>
+          <t>Superadmin авторизован, test стейджинг</t>
+        </is>
+      </c>
+      <c r="E94" s="22" t="inlineStr">
+        <is>
+          <t>1. GET /dashboard/top-ungrouped?item_type=APP&amp;from=2026-03-01&amp;to=2026-03-08&amp;limit=10</t>
+        </is>
+      </c>
+      <c r="F94" s="22" t="inlineStr">
+        <is>
+          <t>200, items[]</t>
+        </is>
+      </c>
+      <c r="G94" s="23" t="inlineStr">
+        <is>
+          <t>200, items: [] (нет данных focus_intervals). Структура ответа с items[] корректна.</t>
+        </is>
+      </c>
+      <c r="H94" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I94" s="22" t="inlineStr">
+        <is>
+          <t>T-106</t>
+        </is>
+      </c>
+      <c r="J94" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="50" customHeight="1" s="15">
+      <c r="A95" s="22" t="inlineStr">
+        <is>
+          <t>TC-090</t>
+        </is>
+      </c>
+      <c r="B95" s="22" t="inlineStr">
+        <is>
+          <t>Dashboard API</t>
+        </is>
+      </c>
+      <c r="C95" s="23" t="inlineStr">
+        <is>
+          <t>GET /dashboard/top-users-ungrouped - топ пользователей по несгруппированным</t>
+        </is>
+      </c>
+      <c r="D95" s="23" t="inlineStr">
+        <is>
+          <t>Superadmin авторизован, test стейджинг</t>
+        </is>
+      </c>
+      <c r="E95" s="22" t="inlineStr">
+        <is>
+          <t>1. GET /dashboard/top-users-ungrouped?item_type=APP&amp;from=2026-03-01&amp;to=2026-03-08&amp;limit=10</t>
+        </is>
+      </c>
+      <c r="F95" s="22" t="inlineStr">
+        <is>
+          <t>200, users[]</t>
+        </is>
+      </c>
+      <c r="G95" s="23" t="inlineStr">
+        <is>
+          <t>200, users: [] (нет данных focus_intervals). Структура ответа с users[] корректна.</t>
+        </is>
+      </c>
+      <c r="H95" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I95" s="22" t="inlineStr">
+        <is>
+          <t>T-106</t>
+        </is>
+      </c>
+      <c r="J95" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="50" customHeight="1" s="15">
+      <c r="A96" s="22" t="inlineStr">
+        <is>
+          <t>TC-091</t>
+        </is>
+      </c>
+      <c r="B96" s="22" t="inlineStr">
+        <is>
+          <t>Catalogs API</t>
+        </is>
+      </c>
+      <c r="C96" s="23" t="inlineStr">
+        <is>
+          <t>Без токена - 401 Unauthorized</t>
+        </is>
+      </c>
+      <c r="D96" s="23" t="inlineStr">
+        <is>
+          <t>Нет авторизации</t>
+        </is>
+      </c>
+      <c r="E96" s="22" t="inlineStr">
+        <is>
+          <t>1. GET /catalogs/groups?group_type=APP без Authorization header</t>
+        </is>
+      </c>
+      <c r="F96" s="22" t="inlineStr">
+        <is>
+          <t>401 Unauthorized</t>
+        </is>
+      </c>
+      <c r="G96" s="23" t="inlineStr">
+        <is>
+          <t>401, Missing or invalid Authorization header, code=MISSING_TOKEN</t>
+        </is>
+      </c>
+      <c r="H96" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I96" s="22" t="inlineStr">
+        <is>
+          <t>T-106</t>
+        </is>
+      </c>
+      <c r="J96" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="50" customHeight="1" s="15">
+      <c r="A97" s="22" t="inlineStr">
+        <is>
+          <t>TC-092</t>
+        </is>
+      </c>
+      <c r="B97" s="22" t="inlineStr">
+        <is>
+          <t>Catalogs API</t>
+        </is>
+      </c>
+      <c r="C97" s="23" t="inlineStr">
+        <is>
+          <t>Tenant isolation - test user видит только свои данные</t>
+        </is>
+      </c>
+      <c r="D97" s="23" t="inlineStr">
+        <is>
+          <t>Test user авторизован (tenant test-org)</t>
+        </is>
+      </c>
+      <c r="E97" s="22" t="inlineStr">
+        <is>
+          <t>1. GET /catalogs/groups?group_type=APP с Bearer токеном test user</t>
+        </is>
+      </c>
+      <c r="F97" s="22" t="inlineStr">
+        <is>
+          <t>200, groups принадлежат тенанту test-org, не prg-platform</t>
+        </is>
+      </c>
+      <c r="G97" s="23" t="inlineStr">
+        <is>
+          <t>200, test user получает 8 APP групп с отличающимися ID от superadmin (b32a87b3... vs 340a1317...). Tenant isolation подтверждена - каждый тенант имеет отдельные справочники.</t>
+        </is>
+      </c>
+      <c r="H97" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I97" s="22" t="inlineStr">
+        <is>
+          <t>T-106</t>
+        </is>
+      </c>
+      <c r="J97" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
         </is>
       </c>
     </row>

--- a/docs/tracker.xlsx
+++ b/docs/tracker.xlsx
@@ -610,7 +610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I113"/>
+  <dimension ref="A1:I145"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="15" min="1" max="1"/>
@@ -5781,6 +5781,1510 @@
         </is>
       </c>
       <c r="I113" s="24" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1" s="15">
+      <c r="A114" s="24" t="inlineStr">
+        <is>
+          <t>T-109</t>
+        </is>
+      </c>
+      <c r="B114" s="24" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="C114" s="25" t="inlineStr">
+        <is>
+          <t>macOS Agent: самопроизвольное переключение на максимальный FPS</t>
+        </is>
+      </c>
+      <c r="D114" s="25" t="inlineStr">
+        <is>
+          <t>Агент самопроизвольно переключается на запись с максимальным FPS вместо установленного сервером. Корневые причины: 1) Эндпоинт /api/v1/agents/{agentID}/config НЕ реализован на control-plane, ConfigManager получает 404/ошибку и молча глотает её. 2) При обработке команды START через CommandHandler агент вызывает startRecording(effectiveConfig: nil), что приводит к fallback на Constants.defaultFPS = 15 вместо серверного. 3) Heartbeat response содержит device_settings с capture_fps, но macOS агент его полностью игнорирует (в отличие от Windows Agent, который парсит ApplyDeviceSettings). 4) Нет fallback на 1 FPS при недоступности сервера. 5) Нет механизма горячего обновления FPS на работающей записи.</t>
+        </is>
+      </c>
+      <c r="E114" s="24" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F114" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G114" s="25" t="inlineStr">
+        <is>
+          <t>Алексей</t>
+        </is>
+      </c>
+      <c r="H114" s="24" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I114" s="24" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1" s="15">
+      <c r="A115" s="18" t="inlineStr">
+        <is>
+          <t>T-110</t>
+        </is>
+      </c>
+      <c r="B115" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C115" s="19" t="inlineStr">
+        <is>
+          <t>control-plane: реализовать эндпоинт GET /api/v1/agents/{agentID}/config</t>
+        </is>
+      </c>
+      <c r="D115" s="19" t="inlineStr">
+        <is>
+          <t>macOS Agent вызывает /api/v1/agents/{agentID}/config?tenant_id=... для получения EffectiveConfig (fps, resolution, bitrate, codec). Эндпоинт НЕ реализован на control-plane. Нужно: 1) Создать AgentConfigController с маппингом /api/v1/agents/{id}/config. 2) В DeviceService добавить метод getEffectiveConfig, который берёт settings из Device.settings (jsonb) и мёрджит с дефолтами из application.yml. 3) Возвращать DTO EffectiveConfigResponse с полями: agent_id, device_id, tenant_id, record_audio, record_screen, resolution, fps, bitrate_kbps, codec, retention_days, schedule_cron, computed_at.</t>
+        </is>
+      </c>
+      <c r="E115" s="18" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F115" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G115" s="19" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H115" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I115" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1" s="15">
+      <c r="A116" s="18" t="inlineStr">
+        <is>
+          <t>T-111</t>
+        </is>
+      </c>
+      <c r="B116" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C116" s="19" t="inlineStr">
+        <is>
+          <t>macOS Agent: парсить capture_fps из heartbeat device_settings</t>
+        </is>
+      </c>
+      <c r="D116" s="19" t="inlineStr">
+        <is>
+          <t>Windows Agent парсит device_settings из HeartbeatResponse и обновляет ServerConfig (capture_fps, resolution, quality и т.д.). macOS Agent полностью игнорирует device_settings. Нужно: 1) Добавить поле deviceSettings: [String: Any]? в HeartbeatResponse. 2) В HeartbeatManager при получении device_settings — уведомлять AppState. 3) AppState должен обновлять effectiveConfig из device_settings и передавать в RecordingPipeline для горячего обновления конфигурации захвата.</t>
+        </is>
+      </c>
+      <c r="E116" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F116" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G116" s="19" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="H116" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I116" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1" s="15">
+      <c r="A117" s="18" t="inlineStr">
+        <is>
+          <t>T-112</t>
+        </is>
+      </c>
+      <c r="B117" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C117" s="19" t="inlineStr">
+        <is>
+          <t>macOS Agent: передавать effectiveConfig при обработке команды START</t>
+        </is>
+      </c>
+      <c r="D117" s="19" t="inlineStr">
+        <is>
+          <t>В RecordingPipeline.handleCommand(.start) вызывается startRecording(effectiveConfig: nil), что приводит к использованию Constants.defaultFPS = 15 вместо серверного значения. Нужно: 1) CommandHandlerDelegate.handleCommand должен получать доступ к текущему effectiveConfig. 2) Или pipeline должен сам хранить ссылку на ConfigManager/currentConfig и использовать его при start. 3) Гарантировать что при любом способе запуска (UI, команда, авто-старт) используется серверный FPS.</t>
+        </is>
+      </c>
+      <c r="E117" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F117" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G117" s="19" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="H117" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I117" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1" s="15">
+      <c r="A118" s="18" t="inlineStr">
+        <is>
+          <t>T-113</t>
+        </is>
+      </c>
+      <c r="B118" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C118" s="19" t="inlineStr">
+        <is>
+          <t>macOS Agent: fallback на 1 FPS при недоступности сервера</t>
+        </is>
+      </c>
+      <c r="D118" s="19" t="inlineStr">
+        <is>
+          <t>Требование: если сервер недоступен — агент должен работать со скоростью 1 FPS. Сейчас при ошибке получения конфига агент использует Constants.defaultFPS = 15 (или закэшированный конфиг). Нужно: 1) Добавить константу Constants.offlineFPS = 1. 2) В ConfigManager при ВСЕХ неудачных попытках получить конфиг (fetchNow fails) И отсутствии кэша — возвращать offlineFPS. 3) Если кэш есть, но сервер недоступен больше N минут — переключаться на 1 FPS. 4) При восстановлении связи — запрашивать конфиг и восстанавливать серверный FPS.</t>
+        </is>
+      </c>
+      <c r="E118" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F118" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G118" s="19" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="H118" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I118" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1" s="15">
+      <c r="A119" s="18" t="inlineStr">
+        <is>
+          <t>T-114</t>
+        </is>
+      </c>
+      <c r="B119" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C119" s="19" t="inlineStr">
+        <is>
+          <t>macOS Agent: горячее обновление FPS без перезапуска записи</t>
+        </is>
+      </c>
+      <c r="D119" s="19" t="inlineStr">
+        <is>
+          <t>Сейчас CaptureConfiguration устанавливается один раз при startCapture. ScreenCaptureManager имеет метод updateConfiguration(), но он никогда не вызывается при изменении конфига. Нужно: 1) При получении нового EffectiveConfig от ConfigManager/heartbeat — вызывать ScreenCaptureManager.updateConfiguration() с новым SCStreamConfiguration. 2) Также обновлять FMP4Segmenter (AVVideoExpectedSourceFrameRateKey, MaxKeyFrameInterval). 3) Логировать изменение FPS для отладки.</t>
+        </is>
+      </c>
+      <c r="E119" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F119" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G119" s="19" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="H119" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I119" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="20" customHeight="1" s="15">
+      <c r="A120" s="18" t="inlineStr">
+        <is>
+          <t>T-115</t>
+        </is>
+      </c>
+      <c r="B120" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C120" s="19" t="inlineStr">
+        <is>
+          <t>macOS Agent: синхронизация defaultFPS с серверным default-capture-fps</t>
+        </is>
+      </c>
+      <c r="D120" s="19" t="inlineStr">
+        <is>
+          <t>macOS Agent имеет Constants.defaultFPS = 15, control-plane имеет default-capture-fps: 5, Windows Agent имеет CaptureFps = 1. Все три значения разные. Нужно: 1) Унифицировать: локальный fallback (без кэша, без сервера) = 1 FPS. 2) Серверный дефолт = 5 FPS (из application.yml). 3) Убрать захардкоженный defaultFPS = 15 из macOS Agent, заменить на 1.</t>
+        </is>
+      </c>
+      <c r="E120" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F120" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G120" s="19" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="H120" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I120" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1" s="15">
+      <c r="A121" s="24" t="inlineStr">
+        <is>
+          <t>T-116</t>
+        </is>
+      </c>
+      <c r="B121" s="24" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="C121" s="25" t="inlineStr">
+        <is>
+          <t>Серверный дефолт capture-fps=5 вместо 1, ConfigMap не задает DEVICE_CAPTURE_FPS</t>
+        </is>
+      </c>
+      <c r="D121" s="25" t="inlineStr">
+        <is>
+          <t>auth-service application.yml:77 задает дефолт capture-fps=5. В ConfigMap для test и prod окружений переменная DEVICE_CAPTURE_FPS не задана. Агент ожидает 1 FPS, сервер всегда отдает 5. Необходимо: (1) изменить дефолт на 1, (2) добавить DEVICE_CAPTURE_FPS в ConfigMap обоих окружений</t>
+        </is>
+      </c>
+      <c r="E121" s="24" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F121" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G121" s="25" t="inlineStr">
+        <is>
+          <t>Алексей</t>
+        </is>
+      </c>
+      <c r="H121" s="24" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I121" s="24" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1" s="15">
+      <c r="A122" s="24" t="inlineStr">
+        <is>
+          <t>T-117</t>
+        </is>
+      </c>
+      <c r="B122" s="24" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="C122" s="25" t="inlineStr">
+        <is>
+          <t>Ре-аутентификация (device-login fallback) сбрасывает ServerConfig, теряя настройки администратора</t>
+        </is>
+      </c>
+      <c r="D122" s="25" t="inlineStr">
+        <is>
+          <t>AuthManager.cs:268 — при fallback ре-аутентификации через device-login ServerConfig полностью заменяется серверными дефолтами. Если администратор ранее через heartbeat device_settings установил capture_fps=1, значение теряется и заменяется серверным дефолтом 5 FPS. Нужно мержить серверные настройки с локальными, а не заменять целиком.</t>
+        </is>
+      </c>
+      <c r="E122" s="24" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F122" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G122" s="25" t="inlineStr">
+        <is>
+          <t>Алексей</t>
+        </is>
+      </c>
+      <c r="H122" s="24" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I122" s="24" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1" s="15">
+      <c r="A123" s="24" t="inlineStr">
+        <is>
+          <t>T-118</t>
+        </is>
+      </c>
+      <c r="B123" s="24" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="C123" s="25" t="inlineStr">
+        <is>
+          <t>device-login ServerConfig не учитывает device.settings для capture_fps, quality, segment_duration</t>
+        </is>
+      </c>
+      <c r="D123" s="25" t="inlineStr">
+        <is>
+          <t>DeviceAuthService.java:311-331 — при построении ServerConfig для ответа device-login, device-specific overrides из device.settings JSONB применяются только для resolution, session_max_duration_hours, auto_start. Поля capture_fps, quality, segment_duration_sec, heartbeat_interval_sec всегда берутся из глобальных дефолтов. Нужно добавить override из device.settings для всех полей.</t>
+        </is>
+      </c>
+      <c r="E123" s="24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F123" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G123" s="25" t="inlineStr">
+        <is>
+          <t>Алексей</t>
+        </is>
+      </c>
+      <c r="H123" s="24" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I123" s="24" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1" s="15">
+      <c r="A124" s="24" t="inlineStr">
+        <is>
+          <t>T-119</t>
+        </is>
+      </c>
+      <c r="B124" s="24" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="C124" s="25" t="inlineStr">
+        <is>
+          <t>UPDATE_SETTINGS команда не работает: проверка 'is int' не срабатывает для JsonElement</t>
+        </is>
+      </c>
+      <c r="D124" s="25" t="inlineStr">
+        <is>
+          <t>CommandHandler.cs:306 — payload.TryGetValue('capture_fps', out var fpsObj) &amp;&amp; fpsObj is int fps — JSON десериализация System.Text.Json с Dictionary&lt;string, object&gt; десериализует числа как JsonElement, а не int. Проверка is int НИКОГДА не сработает. Команда UPDATE_SETTINGS с payload capture_fps=1 молча игнорируется. Нужно использовать JsonElement.TryGetInt32() вместо прямого cast.</t>
+        </is>
+      </c>
+      <c r="E124" s="24" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F124" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G124" s="25" t="inlineStr">
+        <is>
+          <t>Алексей</t>
+        </is>
+      </c>
+      <c r="H124" s="24" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I124" s="24" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1" s="15">
+      <c r="A125" s="18" t="inlineStr">
+        <is>
+          <t>T-120</t>
+        </is>
+      </c>
+      <c r="B125" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C125" s="19" t="inlineStr">
+        <is>
+          <t>ServerConfig.CaptureFps использовать nullable int для различия 'не задано' vs 'задано 0'</t>
+        </is>
+      </c>
+      <c r="D125" s="19" t="inlineStr">
+        <is>
+          <t>ServerConfig.cs:7 — CaptureFps имеет тип int (default 0). Невозможно отличить 'сервер не передал поле' от 'сервер явно задал 0'. Нужно заменить int на int? (nullable) для CaptureFps, SegmentDurationSec, HeartbeatIntervalSec. Обновить все проверки &gt; 0 на HasValue.</t>
+        </is>
+      </c>
+      <c r="E125" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F125" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G125" s="19" t="inlineStr">
+        <is>
+          <t>Алексей</t>
+        </is>
+      </c>
+      <c r="H125" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I125" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="20" customHeight="1" s="15">
+      <c r="A126" s="18" t="inlineStr">
+        <is>
+          <t>T-121</t>
+        </is>
+      </c>
+      <c r="B126" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C126" s="19" t="inlineStr">
+        <is>
+          <t>Heartbeat device_settings: добавить горячий перезапуск записи при изменении FPS</t>
+        </is>
+      </c>
+      <c r="D126" s="19" t="inlineStr">
+        <is>
+          <t>HeartbeatService.cs:92-95 — ApplyDeviceSettings обновляет ServerConfig, но не перезапускает текущую запись. Новый FPS вступает в силу только при следующем перезапуске (crash, rotation, unlock). Нужно определять, изменились ли критические параметры (fps, resolution) и инициировать graceful перезапуск записи.</t>
+        </is>
+      </c>
+      <c r="E126" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F126" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G126" s="19" t="inlineStr">
+        <is>
+          <t>Алексей</t>
+        </is>
+      </c>
+      <c r="H126" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I126" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1" s="15">
+      <c r="A127" s="24" t="inlineStr">
+        <is>
+          <t>T-122</t>
+        </is>
+      </c>
+      <c r="B127" s="24" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="C127" s="25" t="inlineStr">
+        <is>
+          <t>Две иконки Кадеро в трее после перезагрузки: HKLM\Run + HKCU\Run дублируют запуск --tray</t>
+        </is>
+      </c>
+      <c r="D127" s="25" t="inlineStr">
+        <is>
+          <t>При перезагрузке машины tray запускается дважды: (1) из HKLM\Run (setup.iss строка 55-58, ValueName=KaderoTray), (2) из HKCU\Run (AutoStartHelper.cs, ValueName=KaderoAgent). Оба запускают KaderoAgent.exe --tray. Нет Mutex/SingleInstance проверки в TrayApplication. Результат: две одинаковые иконки в трее.</t>
+        </is>
+      </c>
+      <c r="E127" s="24" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F127" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G127" s="25" t="inlineStr">
+        <is>
+          <t>Алексей</t>
+        </is>
+      </c>
+      <c r="H127" s="24" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I127" s="24" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1" s="15">
+      <c r="A128" s="24" t="inlineStr">
+        <is>
+          <t>T-123</t>
+        </is>
+      </c>
+      <c r="B128" s="24" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="C128" s="25" t="inlineStr">
+        <is>
+          <t>Запись остановлена после перезагрузки: race condition Service startup vs SessionWatcher</t>
+        </is>
+      </c>
+      <c r="D128" s="25" t="inlineStr">
+        <is>
+          <t>После перезагрузки Windows Service стартует auto-start запись в AgentService.ExecuteAsync(), но SessionWatcher регистрируется в DI раньше и получает SessionLogon событие когда AuthManager ещё не аутентифицирован. HandleSessionLogonAsync вызывает AutoStartRecordingAsync с пустым baseUrl. Также: AgentStatusProvider инициализирует connectionStatus=disconnected, и до первого успешного heartbeat статус остаётся disconnected+stopped, что tray отображает как Запись остановлена.</t>
+        </is>
+      </c>
+      <c r="E128" s="24" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F128" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G128" s="25" t="inlineStr">
+        <is>
+          <t>Алексей</t>
+        </is>
+      </c>
+      <c r="H128" s="24" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I128" s="24" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="20" customHeight="1" s="15">
+      <c r="A129" s="18" t="inlineStr">
+        <is>
+          <t>T-124</t>
+        </is>
+      </c>
+      <c r="B129" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C129" s="19" t="inlineStr">
+        <is>
+          <t>TrayApplication: добавить Global Mutex для single-instance проверки</t>
+        </is>
+      </c>
+      <c r="D129" s="19" t="inlineStr">
+        <is>
+          <t>Добавить Named Mutex Global\KaderoAgentTray в начало --tray блока Program.cs. Если mutex уже захвачен — выход без ошибки. Это предотвратит запуск двух tray-процессов независимо от источника (HKLM, HKCU, ручной запуск).</t>
+        </is>
+      </c>
+      <c r="E129" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F129" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G129" s="19" t="inlineStr">
+        <is>
+          <t>Алексей</t>
+        </is>
+      </c>
+      <c r="H129" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I129" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="20" customHeight="1" s="15">
+      <c r="A130" s="18" t="inlineStr">
+        <is>
+          <t>T-125</t>
+        </is>
+      </c>
+      <c r="B130" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C130" s="19" t="inlineStr">
+        <is>
+          <t>setup.iss: убрать HKLM\Run запись KaderoTray (дублирует HKCU\Run)</t>
+        </is>
+      </c>
+      <c r="D130" s="19" t="inlineStr">
+        <is>
+          <t>Удалить секцию [Registry] из setup.iss (строки 54-58), которая создаёт HKLM\SOFTWARE\Microsoft\Windows\CurrentVersion\Run\KaderoTray. Авто-запуск tray уже управляется через HKCU\Run из AutoStartHelper.cs (KaderoAgent). HKLM запись — для всех пользователей, HKCU — для конкретного. Оставить только HKCU вариант. Добавить в [InstallDelete] или [Run] удаление старого HKLM значения для upgrade.</t>
+        </is>
+      </c>
+      <c r="E130" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F130" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G130" s="19" t="inlineStr">
+        <is>
+          <t>Алексей</t>
+        </is>
+      </c>
+      <c r="H130" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I130" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="20" customHeight="1" s="15">
+      <c r="A131" s="18" t="inlineStr">
+        <is>
+          <t>T-126</t>
+        </is>
+      </c>
+      <c r="B131" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C131" s="19" t="inlineStr">
+        <is>
+          <t>AgentService: добавить ожидание готовности AuthManager перед auto-start</t>
+        </is>
+      </c>
+      <c r="D131" s="19" t="inlineStr">
+        <is>
+          <t>В AgentService.ExecuteAsync() вызов AutoStartRecordingAsync происходит после authManager.InitializeAsync(). Но SessionWatcher может получить SessionLogon ДО завершения инициализации AuthManager и вызвать HandleSessionLogonAsync с пустым baseUrl. Нужно: (1) SessionWatcher должен ждать AuthManager.IsAuthenticated перед обработкой SessionLogon, (2) или SessionWatcher должен проверять IsAuthenticated и ставить в очередь отложенный auto-start.</t>
+        </is>
+      </c>
+      <c r="E131" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F131" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G131" s="19" t="inlineStr">
+        <is>
+          <t>Алексей</t>
+        </is>
+      </c>
+      <c r="H131" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I131" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="20" customHeight="1" s="15">
+      <c r="A132" s="18" t="inlineStr">
+        <is>
+          <t>T-127</t>
+        </is>
+      </c>
+      <c r="B132" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C132" s="19" t="inlineStr">
+        <is>
+          <t>V32 миграция: расширение devices CHECK + таблица device_status_log</t>
+        </is>
+      </c>
+      <c r="D132" s="19" t="inlineStr">
+        <is>
+          <t>Flyway V32 для auth-service: 1) ALTER TABLE devices DROP/ADD CONSTRAINT devices_status_check с новыми статусами (starting, configuring, awaiting_user, idle, stopped). 2) CREATE TABLE device_status_log для хранения истории смен статусов устройства. Индексы: idx_dsl_device_ts, idx_dsl_tenant_ts, idx_dsl_errors. FK: tenants, devices (ON DELETE CASCADE). Спецификация: docs/agent-lifecycle-spec.md секция 11.</t>
+        </is>
+      </c>
+      <c r="E132" s="18" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F132" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G132" s="19" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H132" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I132" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="20" customHeight="1" s="15">
+      <c r="A133" s="18" t="inlineStr">
+        <is>
+          <t>T-128</t>
+        </is>
+      </c>
+      <c r="B133" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C133" s="19" t="inlineStr">
+        <is>
+          <t>auth-service: изменить дефолты ServerConfig (quality=low, autostart=false, segment=60s, session_max_min=40)</t>
+        </is>
+      </c>
+      <c r="D133" s="19" t="inlineStr">
+        <is>
+          <t>Изменить дефолтные значения в DeviceAuthService.java и application.yml: default-quality=low (было medium), default-auto-start=false (было true), segment-duration-sec=60 (было 10), добавить default-session-max-min=40 (заменяет default-session-max-hours=24). Спецификация: docs/agent-lifecycle-spec.md секция 4.2.</t>
+        </is>
+      </c>
+      <c r="E133" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F133" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G133" s="19" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H133" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I133" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="20" customHeight="1" s="15">
+      <c r="A134" s="18" t="inlineStr">
+        <is>
+          <t>T-129</t>
+        </is>
+      </c>
+      <c r="B134" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C134" s="19" t="inlineStr">
+        <is>
+          <t>auth-service: добавить session_max_duration_min в DeviceLoginResponse.ServerConfig</t>
+        </is>
+      </c>
+      <c r="D134" s="19" t="inlineStr">
+        <is>
+          <t>Добавить поле sessionMaxDurationMin (Integer) в DeviceLoginResponse.ServerConfig. Дефолт 40. Оставить sessionMaxDurationHours для обратной совместимости (nullable, deprecated). Обновить buildServerConfig() в DeviceAuthService для чтения из device.settings. Спецификация: docs/agent-lifecycle-spec.md секция 5.3.</t>
+        </is>
+      </c>
+      <c r="E134" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F134" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G134" s="19" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H134" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I134" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="20" customHeight="1" s="15">
+      <c r="A135" s="18" t="inlineStr">
+        <is>
+          <t>T-130</t>
+        </is>
+      </c>
+      <c r="B135" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C135" s="19" t="inlineStr">
+        <is>
+          <t>control-plane: Entity/Repository/DTO для device_status_log</t>
+        </is>
+      </c>
+      <c r="D135" s="19" t="inlineStr">
+        <is>
+          <t>Создать: 1) DeviceStatusLog entity (id, tenantId, deviceId, previousStatus, newStatus, changedTs, trigger, details JSONB). 2) DeviceStatusLogRepository с методами findByDeviceIdAndTenantId(deviceId, tenantId, Pageable). 3) DeviceStatusLogResponse DTO. Спецификация: docs/agent-lifecycle-spec.md секция 6.1.</t>
+        </is>
+      </c>
+      <c r="E135" s="18" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F135" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G135" s="19" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H135" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I135" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="20" customHeight="1" s="15">
+      <c r="A136" s="18" t="inlineStr">
+        <is>
+          <t>T-131</t>
+        </is>
+      </c>
+      <c r="B136" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C136" s="19" t="inlineStr">
+        <is>
+          <t>control-plane: записывать смену статуса в device_status_log при heartbeat</t>
+        </is>
+      </c>
+      <c r="D136" s="19" t="inlineStr">
+        <is>
+          <t>В DeviceService.processHeartbeat(): сравнить device.getStatus() с request.getStatus(). Если статус изменился -- INSERT в device_status_log (previous_status=old, new_status=new, trigger=heartbeat, details={agent_version, session_locked, metrics}). Не записывать, если статус не изменился. Спецификация: docs/agent-lifecycle-spec.md секция 4.1.2.</t>
+        </is>
+      </c>
+      <c r="E136" s="18" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F136" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G136" s="19" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H136" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I136" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="20" customHeight="1" s="15">
+      <c r="A137" s="18" t="inlineStr">
+        <is>
+          <t>T-132</t>
+        </is>
+      </c>
+      <c r="B137" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C137" s="19" t="inlineStr">
+        <is>
+          <t>control-plane: новый endpoint GET /devices/{id}/status-log</t>
+        </is>
+      </c>
+      <c r="D137" s="19" t="inlineStr">
+        <is>
+          <t>GET /api/v1/devices/{id}/status-log с параметрами page, size, from, to. Auth: Bearer JWT + DEVICES:READ. Tenant isolation. Response: PageResponse&lt;DeviceStatusLogResponse&gt;. Спецификация: docs/agent-lifecycle-spec.md секция 5.2.</t>
+        </is>
+      </c>
+      <c r="E137" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F137" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G137" s="19" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H137" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I137" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="20" customHeight="1" s="15">
+      <c r="A138" s="18" t="inlineStr">
+        <is>
+          <t>T-133</t>
+        </is>
+      </c>
+      <c r="B138" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C138" s="19" t="inlineStr">
+        <is>
+          <t>control-plane: расширить HeartbeatRequest regex новыми статусами</t>
+        </is>
+      </c>
+      <c r="D138" s="19" t="inlineStr">
+        <is>
+          <t>В HeartbeatRequest.java изменить @Pattern regexp на: ^(offline|online|recording|error|idle|starting|configuring|awaiting_user|stopped)$. Добавить новые статусы в список допустимых значений. Спецификация: docs/agent-lifecycle-spec.md секция 3.1.</t>
+        </is>
+      </c>
+      <c r="E138" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F138" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G138" s="19" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H138" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I138" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="20" customHeight="1" s="15">
+      <c r="A139" s="18" t="inlineStr">
+        <is>
+          <t>T-134</t>
+        </is>
+      </c>
+      <c r="B139" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C139" s="19" t="inlineStr">
+        <is>
+          <t>windows-agent: обновить дефолты (autostart=false, quality=low, segment=60, session_max_min=40)</t>
+        </is>
+      </c>
+      <c r="D139" s="19" t="inlineStr">
+        <is>
+          <t>Изменить AgentConfig.cs: AutoStart=false, Quality=low, SegmentDurationSec=60. Добавить SessionMaxDurationMin=40. Обновить appsettings.json. Добавить SessionMaxDurationMin в ServerConfig.cs. Спецификация: docs/agent-lifecycle-spec.md секция 4.4.1.</t>
+        </is>
+      </c>
+      <c r="E139" s="18" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F139" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G139" s="19" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="H139" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I139" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="20" customHeight="1" s="15">
+      <c r="A140" s="18" t="inlineStr">
+        <is>
+          <t>T-135</t>
+        </is>
+      </c>
+      <c r="B140" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C140" s="19" t="inlineStr">
+        <is>
+          <t>windows-agent: реализовать state machine (AgentState enum) с новыми статусами</t>
+        </is>
+      </c>
+      <c r="D140" s="19" t="inlineStr">
+        <is>
+          <t>Ввести enum AgentState {Starting, Configuring, AwaitingUser, Online, Recording, Idle, Error, Stopped}. Поле _currentState в AgentService/HeartbeatService. Каждый переход обновляет _currentState. HeartbeatService использует _currentState для определения status в heartbeat request. Спецификация: docs/agent-lifecycle-spec.md секция 3 и 4.4.2.</t>
+        </is>
+      </c>
+      <c r="E140" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F140" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G140" s="19" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="H140" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I140" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="20" customHeight="1" s="15">
+      <c r="A141" s="18" t="inlineStr">
+        <is>
+          <t>T-136</t>
+        </is>
+      </c>
+      <c r="B141" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C141" s="19" t="inlineStr">
+        <is>
+          <t>windows-agent: финальный heartbeat status=stopped при shutdown</t>
+        </is>
+      </c>
+      <c r="D141" s="19" t="inlineStr">
+        <is>
+          <t>При получении CancellationToken (shutdown) отправить PUT heartbeat с status=stopped перед завершением. Использовать try/catch с timeout 5s (сервер может быть недоступен при shutdown). Спецификация: docs/agent-lifecycle-spec.md секция 4.4.3 и диаграмма 7.4.</t>
+        </is>
+      </c>
+      <c r="E141" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F141" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G141" s="19" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="H141" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I141" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="20" customHeight="1" s="15">
+      <c r="A142" s="18" t="inlineStr">
+        <is>
+          <t>T-137</t>
+        </is>
+      </c>
+      <c r="B142" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C142" s="19" t="inlineStr">
+        <is>
+          <t>windows-agent: статус configuring при инициализации, awaiting_user при locked session</t>
+        </is>
+      </c>
+      <c r="D142" s="19" t="inlineStr">
+        <is>
+          <t>До завершения auth: heartbeat status=configuring (если есть saved credentials для device_id -- можно отправлять до получения нового JWT). После auth, если SessionWatcher.IsSessionActive==false: heartbeat status=awaiting_user. Спецификация: docs/agent-lifecycle-spec.md секция 4.4.4 и 4.4.5.</t>
+        </is>
+      </c>
+      <c r="E142" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F142" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G142" s="19" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="H142" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I142" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="20" customHeight="1" s="15">
+      <c r="A143" s="18" t="inlineStr">
+        <is>
+          <t>T-138</t>
+        </is>
+      </c>
+      <c r="B143" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C143" s="19" t="inlineStr">
+        <is>
+          <t>windows-agent: поддержка session_max_duration_min (приоритет над hours)</t>
+        </is>
+      </c>
+      <c r="D143" s="19" t="inlineStr">
+        <is>
+          <t>В ServerConfig.cs добавить SessionMaxDurationMin (int?). В CommandHandler.CheckSessionRotationAsync: проверять SessionMaxDurationMin первым, fallback на SessionMaxDurationHours * 60. В HeartbeatService.ApplyDeviceSettings: парсить session_max_duration_min. Спецификация: docs/agent-lifecycle-spec.md секция 4.4 и 8.1.</t>
+        </is>
+      </c>
+      <c r="E143" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F143" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G143" s="19" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="H143" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I143" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="20" customHeight="1" s="15">
+      <c r="A144" s="18" t="inlineStr">
+        <is>
+          <t>T-139</t>
+        </is>
+      </c>
+      <c r="B144" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C144" s="19" t="inlineStr">
+        <is>
+          <t>web-dashboard: секция Журнал статусов в DeviceDetailPage</t>
+        </is>
+      </c>
+      <c r="D144" s="19" t="inlineStr">
+        <is>
+          <t>Добавить секцию между Информация об устройстве и Настройки записи. API: getDeviceStatusLog(id, {page, size}). Таблица: Время, Старый статус, Новый статус, Триггер. Пагинация. Локализованные названия статусов. Permission: DEVICES:READ. Спецификация: docs/agent-lifecycle-spec.md секция 4.5.1.</t>
+        </is>
+      </c>
+      <c r="E144" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F144" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G144" s="19" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="H144" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I144" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="20" customHeight="1" s="15">
+      <c r="A145" s="18" t="inlineStr">
+        <is>
+          <t>T-140</t>
+        </is>
+      </c>
+      <c r="B145" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C145" s="19" t="inlineStr">
+        <is>
+          <t>web-dashboard: обновить DeviceStatusBadge для новых статусов</t>
+        </is>
+      </c>
+      <c r="D145" s="19" t="inlineStr">
+        <is>
+          <t>Добавить отображение и цвета для статусов: starting (серый, пульс), configuring (синий, пульс), awaiting_user (желтый), idle (оранжевый), stopped (серый). Обновить DeviceResponse.status type в types/device.ts. Спецификация: docs/agent-lifecycle-spec.md секция 3.1.</t>
+        </is>
+      </c>
+      <c r="E145" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F145" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G145" s="19" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="H145" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I145" s="18" t="inlineStr">
         <is>
           <t>09.03.2026</t>
         </is>

--- a/docs/tracker.xlsx
+++ b/docs/tracker.xlsx
@@ -610,7 +610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I145"/>
+  <dimension ref="A1:I160"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="15" min="1" max="1"/>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="F34" s="18" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Cancelled</t>
         </is>
       </c>
       <c r="G34" s="19" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="I34" s="18" t="inlineStr">
         <is>
-          <t>07.03.2026</t>
+          <t>09.03.2026</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="F35" s="18" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Cancelled</t>
         </is>
       </c>
       <c r="G35" s="19" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="I35" s="18" t="inlineStr">
         <is>
-          <t>07.03.2026</t>
+          <t>09.03.2026</t>
         </is>
       </c>
     </row>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="F39" s="24" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Cancelled</t>
         </is>
       </c>
       <c r="G39" s="25" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="I39" s="24" t="inlineStr">
         <is>
-          <t>07.03.2026</t>
+          <t>09.03.2026</t>
         </is>
       </c>
     </row>
@@ -7224,7 +7224,7 @@
       </c>
       <c r="F144" s="18" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G144" s="19" t="inlineStr">
@@ -7271,20 +7271,725 @@
       </c>
       <c r="F145" s="18" t="inlineStr">
         <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G145" s="19" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="H145" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I145" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="20" customHeight="1" s="15">
+      <c r="A146" s="18" t="inlineStr">
+        <is>
+          <t>T-141</t>
+        </is>
+      </c>
+      <c r="B146" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C146" s="19" t="inlineStr">
+        <is>
+          <t>Agent Lifecycle: функциональное тестирование heartbeat, status-log, device-settings</t>
+        </is>
+      </c>
+      <c r="D146" s="19" t="inlineStr">
+        <is>
+          <t>Тестирование полного цикла жизни агента: heartbeat с новыми статусами (starting, configuring, awaiting_user, idle, stopped, recording, online, error, offline), Status-Log API, device settings defaults, tenant isolation</t>
+        </is>
+      </c>
+      <c r="E146" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F146" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G146" s="19" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="H146" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I146" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="20" customHeight="1" s="15">
+      <c r="A147" s="18" t="inlineStr">
+        <is>
+          <t>T-142</t>
+        </is>
+      </c>
+      <c r="B147" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C147" s="19" t="inlineStr">
+        <is>
+          <t>Backend: endpoint GET /users/timeline в UserActivityController</t>
+        </is>
+      </c>
+      <c r="D147" s="19" t="inlineStr">
+        <is>
+          <t>Новый endpoint GET /api/v1/ingest/users/timeline?date=...&amp;timezone=... для почасовой агрегации активности пользователей с иерархией групп приложений/сайтов. Permission: RECORDINGS:READ. Спецификация: docs/timelines-spec.md раздел 4.1</t>
+        </is>
+      </c>
+      <c r="E147" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F147" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G147" s="19" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H147" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I147" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="20" customHeight="1" s="15">
+      <c r="A148" s="18" t="inlineStr">
+        <is>
+          <t>T-143</t>
+        </is>
+      </c>
+      <c r="B148" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C148" s="19" t="inlineStr">
+        <is>
+          <t>Backend: TimelineService с SQL-агрегацией и кэшем групп</t>
+        </is>
+      </c>
+      <c r="D148" s="19" t="inlineStr">
+        <is>
+          <t>Сервис с 3 SQL-запросами (focus_intervals агрегация по часам, recording_sessions за день, device_user_sessions маппинг). In-memory сборка иерархии user-&gt;hour-&gt;group-&gt;app/domain. Кэш app_group_items для tenant (TTL 5мин). Спецификация: docs/timelines-spec.md раздел 4.2-4.3</t>
+        </is>
+      </c>
+      <c r="E148" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F148" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G148" s="19" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H148" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I148" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="20" customHeight="1" s="15">
+      <c r="A149" s="18" t="inlineStr">
+        <is>
+          <t>T-144</t>
+        </is>
+      </c>
+      <c r="B149" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C149" s="19" t="inlineStr">
+        <is>
+          <t>Backend: DTO TimelineResponse + вложенные модели</t>
+        </is>
+      </c>
+      <c r="D149" s="19" t="inlineStr">
+        <is>
+          <t>Java DTO: TimelineResponse, TimelineUser, TimelineHour, TimelineAppGroup, TimelineApp, TimelineSiteGroup, TimelineSite. Спецификация: docs/timelines-spec.md раздел 4.1</t>
+        </is>
+      </c>
+      <c r="E149" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F149" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G149" s="19" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H149" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I149" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="20" customHeight="1" s="15">
+      <c r="A150" s="18" t="inlineStr">
+        <is>
+          <t>T-145</t>
+        </is>
+      </c>
+      <c r="B150" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C150" s="19" t="inlineStr">
+        <is>
+          <t>Удалить Mail.ru OAuth из auth-service (backend)</t>
+        </is>
+      </c>
+      <c r="D150" s="19" t="inlineStr">
+        <is>
+          <t>Удалить: MailruOAuthConfig.java, MailruOAuthClient.java, MailruOAuthClientTest.java (файлы). В OAuthService.java: удалить mailruClient, mailruOAuthConfig, PROVIDER_MAILRU, getMailruAuthorizationUrl(), handleMailruCallback(). В OAuthController.java: удалить mailruOAuthConfig, endpoints /mailru и /mailru/callback, ветку mailru в processOAuthCallback(). В SecurityConfig.java: удалить 2 строки permitAll. В application.yml: удалить блок mailru. Спецификация: docs/timelines-spec.md раздел 9</t>
+        </is>
+      </c>
+      <c r="E150" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F150" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G150" s="19" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H150" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I150" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="20" customHeight="1" s="15">
+      <c r="A151" s="18" t="inlineStr">
+        <is>
+          <t>T-146</t>
+        </is>
+      </c>
+      <c r="B151" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C151" s="19" t="inlineStr">
+        <is>
+          <t>Frontend: страница TimelinesPage + компоненты таймлайна</t>
+        </is>
+      </c>
+      <c r="D151" s="19" t="inlineStr">
+        <is>
+          <t>Новая страница TimelinesPage.tsx. Компоненты: TimelineTable, TimelineRow (Level 1: пользователь), TimelineBar (серая/красная колбаска), TimelineAppGroupRow (Level 2), TimelineAppRow (Level 3), TimelineSiteGroupRow (Level 3 для браузеров), TimelineSiteRow (Level 4), TimelineDatePicker. Спецификация: docs/timelines-spec.md раздел 6</t>
+        </is>
+      </c>
+      <c r="E151" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F151" s="18" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G145" s="19" t="inlineStr">
+      <c r="G151" s="19" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="H145" s="18" t="inlineStr">
+      <c r="H151" s="18" t="inlineStr">
         <is>
           <t>09.03.2026</t>
         </is>
       </c>
-      <c r="I145" s="18" t="inlineStr">
+      <c r="I151" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="20" customHeight="1" s="15">
+      <c r="A152" s="18" t="inlineStr">
+        <is>
+          <t>T-147</t>
+        </is>
+      </c>
+      <c r="B152" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C152" s="19" t="inlineStr">
+        <is>
+          <t>Frontend: типы Timeline* + API функция getTimeline()</t>
+        </is>
+      </c>
+      <c r="D152" s="19" t="inlineStr">
+        <is>
+          <t>TypeScript типы в types/user-activity.ts: TimelineResponse, TimelineUser, TimelineHour, TimelineAppGroup, TimelineApp, TimelineSiteGroup, TimelineSite. Функция getTimeline() в api/user-activity.ts: GET /users/timeline?date=...&amp;timezone=... Спецификация: docs/timelines-spec.md раздел 4.1 и 6.5</t>
+        </is>
+      </c>
+      <c r="E152" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F152" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G152" s="19" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="H152" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I152" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="20" customHeight="1" s="15">
+      <c r="A153" s="18" t="inlineStr">
+        <is>
+          <t>T-148</t>
+        </is>
+      </c>
+      <c r="B153" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C153" s="19" t="inlineStr">
+        <is>
+          <t>Frontend: маршрут /archive/timelines + подпункт Sidebar</t>
+        </is>
+      </c>
+      <c r="D153" s="19" t="inlineStr">
+        <is>
+          <t>Добавить Route path=/archive/timelines element=TimelinesPage в App.tsx. Добавить NavItem 'Таймлайны' с href=/archive/timelines и icon=ClockIcon в archiveSubmenu в Sidebar.tsx. Обновить isArchiveActive для pathname /archive/timelines.</t>
+        </is>
+      </c>
+      <c r="E153" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F153" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G153" s="19" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="H153" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I153" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="20" customHeight="1" s="15">
+      <c r="A154" s="18" t="inlineStr">
+        <is>
+          <t>T-149</t>
+        </is>
+      </c>
+      <c r="B154" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C154" s="19" t="inlineStr">
+        <is>
+          <t>Frontend: навигация к видеозаписи при клике на красную колбаску</t>
+        </is>
+      </c>
+      <c r="D154" s="19" t="inlineStr">
+        <is>
+          <t>При клике на красную колбаску (has_recording=true) навигация на /archive/devices/:deviceId?session=:sessionId&amp;date=:date. Серые колбаски (has_recording=false) не кликабельны для видео.</t>
+        </is>
+      </c>
+      <c r="E154" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F154" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G154" s="19" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="H154" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I154" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="20" customHeight="1" s="15">
+      <c r="A155" s="18" t="inlineStr">
+        <is>
+          <t>T-150</t>
+        </is>
+      </c>
+      <c r="B155" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C155" s="19" t="inlineStr">
+        <is>
+          <t>Frontend: sidebar spacing -- отступ между пунктом и подменю</t>
+        </is>
+      </c>
+      <c r="D155" s="19" t="inlineStr">
+        <is>
+          <t>Добавить mt-1 div-обёртку к блокам подменю Аналитика и Настройки в Sidebar.tsx. 4 места: 2x SuperAdmin layout (строки 188, 212), 2x OAuth layout (строки 323, 347). Спецификация: docs/timelines-spec.md раздел 7</t>
+        </is>
+      </c>
+      <c r="E155" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F155" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G155" s="19" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="H155" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I155" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="20" customHeight="1" s="15">
+      <c r="A156" s="18" t="inlineStr">
+        <is>
+          <t>T-151</t>
+        </is>
+      </c>
+      <c r="B156" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C156" s="19" t="inlineStr">
+        <is>
+          <t>Frontend: заменить favicon на Кадеро</t>
+        </is>
+      </c>
+      <c r="D156" s="19" t="inlineStr">
+        <is>
+          <t>1. Скопировать assets/favicon.png в web-dashboard/public/favicon.png. 2. В index.html заменить link rel=icon с vite.svg на favicon.png (type=image/png). 3. Удалить web-dashboard/public/vite.svg. Спецификация: docs/timelines-spec.md раздел 8</t>
+        </is>
+      </c>
+      <c r="E156" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F156" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G156" s="19" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="H156" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I156" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="20" customHeight="1" s="15">
+      <c r="A157" s="18" t="inlineStr">
+        <is>
+          <t>T-152</t>
+        </is>
+      </c>
+      <c r="B157" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C157" s="19" t="inlineStr">
+        <is>
+          <t>Frontend: удалить Mail.ru OAuth из LoginPage, OAuthLoginPage, auth.ts</t>
+        </is>
+      </c>
+      <c r="D157" s="19" t="inlineStr">
+        <is>
+          <t>Удалить из auth.ts: функцию getMailruOAuthLoginUrl(). Из LoginPage.tsx: импорт getMailruOAuthLoginUrl, handleMailruLogin, кнопку 'Войти через Mail.ru'. Из OAuthLoginPage.tsx: импорт getMailruOAuthLoginUrl, handleMailruLogin, кнопку 'Войти через Mail.ru'. Спецификация: docs/timelines-spec.md раздел 9</t>
+        </is>
+      </c>
+      <c r="E157" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F157" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G157" s="19" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="H157" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I157" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="20" customHeight="1" s="15">
+      <c r="A158" s="18" t="inlineStr">
+        <is>
+          <t>T-153</t>
+        </is>
+      </c>
+      <c r="B158" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C158" s="19" t="inlineStr">
+        <is>
+          <t>Тестирование: endpoint /users/timeline с реальными данными</t>
+        </is>
+      </c>
+      <c r="D158" s="19" t="inlineStr">
+        <is>
+          <t>Функциональный тест на test-стейджинге: вызов GET /api/v1/ingest/users/timeline с JWT, проверка формата ответа, наличия пользователей, иерархии групп, has_recording флагов.</t>
+        </is>
+      </c>
+      <c r="E158" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F158" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G158" s="19" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="H158" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I158" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="20" customHeight="1" s="15">
+      <c r="A159" s="18" t="inlineStr">
+        <is>
+          <t>T-154</t>
+        </is>
+      </c>
+      <c r="B159" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C159" s="19" t="inlineStr">
+        <is>
+          <t>Тестирование: Yandex OAuth после удаления Mail.ru</t>
+        </is>
+      </c>
+      <c r="D159" s="19" t="inlineStr">
+        <is>
+          <t>Убедиться что Yandex OAuth продолжает работать: авторизация, callback, onboarding, select-tenant. Проверить что endpoints /mailru и /mailru/callback возвращают 404.</t>
+        </is>
+      </c>
+      <c r="E159" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F159" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G159" s="19" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="H159" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I159" s="18" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="20" customHeight="1" s="15">
+      <c r="A160" s="24" t="inlineStr">
+        <is>
+          <t>T-155</t>
+        </is>
+      </c>
+      <c r="B160" s="24" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="C160" s="25" t="inlineStr">
+        <is>
+          <t>Crash на странице справочников: Cannot read properties of undefined (reading length)</t>
+        </is>
+      </c>
+      <c r="D160" s="25" t="inlineStr">
+        <is>
+          <t>Фронтенд ожидал объект-обёртку {groups: [], total: N} от API getGroups/getGroupItems, а backend возвращает List&lt;T&gt; (массив). resp.groups и resp.items возвращали undefined, вызывая TypeError при обращении к .length</t>
+        </is>
+      </c>
+      <c r="E160" s="24" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F160" s="24" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G160" s="25" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="H160" s="24" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+      <c r="I160" s="24" t="inlineStr">
         <is>
           <t>09.03.2026</t>
         </is>
@@ -7304,7 +8009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J97"/>
+  <dimension ref="A1:J113"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="15" min="1" max="1"/>
@@ -12167,6 +12872,838 @@
         </is>
       </c>
       <c r="J97" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="50" customHeight="1" s="15">
+      <c r="A98" s="22" t="inlineStr">
+        <is>
+          <t>TC-093</t>
+        </is>
+      </c>
+      <c r="B98" s="22" t="inlineStr">
+        <is>
+          <t>Agent Lifecycle</t>
+        </is>
+      </c>
+      <c r="C98" s="23" t="inlineStr">
+        <is>
+          <t>Heartbeat: все 9 валидных статусов принимаются (200)</t>
+        </is>
+      </c>
+      <c r="D98" s="23" t="inlineStr">
+        <is>
+          <t>Устройство 60b50ed1 зарегистрировано в тенанте Test Organization, JWT token user test</t>
+        </is>
+      </c>
+      <c r="E98" s="22" t="inlineStr">
+        <is>
+          <t>1. PUT /api/cp/v1/devices/{id}/heartbeat с status=starting\n2. Повторить для configuring, awaiting_user, idle, stopped, recording, online, error, offline\n3. Проверить HTTP 200 и корректный JSON response для каждого</t>
+        </is>
+      </c>
+      <c r="F98" s="22" t="inlineStr">
+        <is>
+          <t>Все 9 статусов возвращают HTTP 200, ответ содержит server_ts, pending_commands, next_heartbeat_sec, device_settings</t>
+        </is>
+      </c>
+      <c r="G98" s="23" t="inlineStr">
+        <is>
+          <t>Все 9 статусов (starting, configuring, awaiting_user, idle, stopped, recording, online, error, offline) возвращают HTTP 200 с корректным JSON</t>
+        </is>
+      </c>
+      <c r="H98" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I98" s="22" t="inlineStr">
+        <is>
+          <t>T-141</t>
+        </is>
+      </c>
+      <c r="J98" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="50" customHeight="1" s="15">
+      <c r="A99" s="22" t="inlineStr">
+        <is>
+          <t>TC-094</t>
+        </is>
+      </c>
+      <c r="B99" s="22" t="inlineStr">
+        <is>
+          <t>Agent Lifecycle</t>
+        </is>
+      </c>
+      <c r="C99" s="23" t="inlineStr">
+        <is>
+          <t>Heartbeat: структура ответа (server_ts, commands, settings, types)</t>
+        </is>
+      </c>
+      <c r="D99" s="23" t="inlineStr">
+        <is>
+          <t>Устройство 60b50ed1 зарегистрировано</t>
+        </is>
+      </c>
+      <c r="E99" s="22" t="inlineStr">
+        <is>
+          <t>1. PUT heartbeat со status=online\n2. Проверить наличие полей: server_ts (string ISO8601), pending_commands (array), next_heartbeat_sec (int), device_settings (object)\n3. Проверить device_settings содержит: fps (int), auto_start (bool), resolution (string), session_max_duration_hours (int)</t>
+        </is>
+      </c>
+      <c r="F99" s="22" t="inlineStr">
+        <is>
+          <t>Все поля присутствуют, типы корректны, server_ts в ISO 8601</t>
+        </is>
+      </c>
+      <c r="G99" s="23" t="inlineStr">
+        <is>
+          <t>server_ts (string ISO8601), pending_commands (array), next_heartbeat_sec=30 (int), device_settings: fps=1 (int), auto_start=true (bool), resolution=720p (string), session_max_duration_hours=24 (int)</t>
+        </is>
+      </c>
+      <c r="H99" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I99" s="22" t="inlineStr">
+        <is>
+          <t>T-141</t>
+        </is>
+      </c>
+      <c r="J99" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="50" customHeight="1" s="15">
+      <c r="A100" s="22" t="inlineStr">
+        <is>
+          <t>TC-095</t>
+        </is>
+      </c>
+      <c r="B100" s="22" t="inlineStr">
+        <is>
+          <t>Agent Lifecycle</t>
+        </is>
+      </c>
+      <c r="C100" s="23" t="inlineStr">
+        <is>
+          <t>Heartbeat: невалидный статус -&gt; 400 VALIDATION_ERROR</t>
+        </is>
+      </c>
+      <c r="D100" s="23" t="inlineStr">
+        <is>
+          <t>Устройство 60b50ed1 зарегистрировано</t>
+        </is>
+      </c>
+      <c r="E100" s="22" t="inlineStr">
+        <is>
+          <t>1. PUT heartbeat с status=INVALID_STATUS\n2. Проверить HTTP 400\n3. Проверить body содержит error и code=VALIDATION_ERROR</t>
+        </is>
+      </c>
+      <c r="F100" s="22" t="inlineStr">
+        <is>
+          <t>HTTP 400, body: {error: 'Invalid status value', code: 'VALIDATION_ERROR'}</t>
+        </is>
+      </c>
+      <c r="G100" s="23" t="inlineStr">
+        <is>
+          <t>HTTP 400, body: {error: 'Invalid status value', code: 'VALIDATION_ERROR'}</t>
+        </is>
+      </c>
+      <c r="H100" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I100" s="22" t="inlineStr">
+        <is>
+          <t>T-141</t>
+        </is>
+      </c>
+      <c r="J100" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="50" customHeight="1" s="15">
+      <c r="A101" s="22" t="inlineStr">
+        <is>
+          <t>TC-096</t>
+        </is>
+      </c>
+      <c r="B101" s="22" t="inlineStr">
+        <is>
+          <t>Agent Lifecycle</t>
+        </is>
+      </c>
+      <c r="C101" s="23" t="inlineStr">
+        <is>
+          <t>Heartbeat: пустое тело запроса -&gt; 400</t>
+        </is>
+      </c>
+      <c r="D101" s="23" t="inlineStr">
+        <is>
+          <t>Устройство 60b50ed1 зарегистрировано</t>
+        </is>
+      </c>
+      <c r="E101" s="22" t="inlineStr">
+        <is>
+          <t>1. PUT heartbeat с body {}\n2. Проверить HTTP 400</t>
+        </is>
+      </c>
+      <c r="F101" s="22" t="inlineStr">
+        <is>
+          <t>HTTP 400, body: {error: 'Status is required', code: 'VALIDATION_ERROR'}</t>
+        </is>
+      </c>
+      <c r="G101" s="23" t="inlineStr">
+        <is>
+          <t>HTTP 400, body: {error: 'Status is required', code: 'VALIDATION_ERROR'}</t>
+        </is>
+      </c>
+      <c r="H101" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I101" s="22" t="inlineStr">
+        <is>
+          <t>T-141</t>
+        </is>
+      </c>
+      <c r="J101" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="50" customHeight="1" s="15">
+      <c r="A102" s="22" t="inlineStr">
+        <is>
+          <t>TC-097</t>
+        </is>
+      </c>
+      <c r="B102" s="22" t="inlineStr">
+        <is>
+          <t>Agent Lifecycle</t>
+        </is>
+      </c>
+      <c r="C102" s="23" t="inlineStr">
+        <is>
+          <t>Heartbeat: без авторизации -&gt; 401 UNAUTHORIZED</t>
+        </is>
+      </c>
+      <c r="D102" s="23" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="E102" s="22" t="inlineStr">
+        <is>
+          <t>1. PUT heartbeat без заголовка Authorization\n2. Проверить HTTP 401</t>
+        </is>
+      </c>
+      <c r="F102" s="22" t="inlineStr">
+        <is>
+          <t>HTTP 401, body: {error: '...', code: 'UNAUTHORIZED'}</t>
+        </is>
+      </c>
+      <c r="G102" s="23" t="inlineStr">
+        <is>
+          <t>HTTP 401, body: {error: 'Missing or invalid Authorization header', code: 'UNAUTHORIZED'}</t>
+        </is>
+      </c>
+      <c r="H102" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I102" s="22" t="inlineStr">
+        <is>
+          <t>T-141</t>
+        </is>
+      </c>
+      <c r="J102" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="50" customHeight="1" s="15">
+      <c r="A103" s="22" t="inlineStr">
+        <is>
+          <t>TC-098</t>
+        </is>
+      </c>
+      <c r="B103" s="22" t="inlineStr">
+        <is>
+          <t>Agent Lifecycle</t>
+        </is>
+      </c>
+      <c r="C103" s="23" t="inlineStr">
+        <is>
+          <t>Heartbeat: cross-tenant device -&gt; 404 DEVICE_NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="D103" s="23" t="inlineStr">
+        <is>
+          <t>Устройство 64b4d56e в тенанте Тест 1, JWT от user test (Test Organization)</t>
+        </is>
+      </c>
+      <c r="E103" s="22" t="inlineStr">
+        <is>
+          <t>1. PUT heartbeat для device 64b4d56e с токеном user test\n2. Проверить HTTP 404</t>
+        </is>
+      </c>
+      <c r="F103" s="22" t="inlineStr">
+        <is>
+          <t>HTTP 404, body: {error: 'Device not found: ...', code: 'DEVICE_NOT_FOUND'}</t>
+        </is>
+      </c>
+      <c r="G103" s="23" t="inlineStr">
+        <is>
+          <t>HTTP 404, body: {error: 'Device not found: 64b4d56e-...', code: 'DEVICE_NOT_FOUND'}</t>
+        </is>
+      </c>
+      <c r="H103" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I103" s="22" t="inlineStr">
+        <is>
+          <t>T-141</t>
+        </is>
+      </c>
+      <c r="J103" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="50" customHeight="1" s="15">
+      <c r="A104" s="22" t="inlineStr">
+        <is>
+          <t>TC-099</t>
+        </is>
+      </c>
+      <c r="B104" s="22" t="inlineStr">
+        <is>
+          <t>Agent Lifecycle</t>
+        </is>
+      </c>
+      <c r="C104" s="23" t="inlineStr">
+        <is>
+          <t>Heartbeat: session_locked=true принимается корректно</t>
+        </is>
+      </c>
+      <c r="D104" s="23" t="inlineStr">
+        <is>
+          <t>Устройство 60b50ed1 зарегистрировано</t>
+        </is>
+      </c>
+      <c r="E104" s="22" t="inlineStr">
+        <is>
+          <t>1. PUT heartbeat с session_locked=true, status=idle\n2. Проверить HTTP 200\n3. Проверить status-log: details содержит session_locked=true</t>
+        </is>
+      </c>
+      <c r="F104" s="22" t="inlineStr">
+        <is>
+          <t>HTTP 200, status-log entry details.session_locked=true</t>
+        </is>
+      </c>
+      <c r="G104" s="23" t="inlineStr">
+        <is>
+          <t>HTTP 200, status-log entry: details.session_locked=true, details.agent_version=1.0.0-test</t>
+        </is>
+      </c>
+      <c r="H104" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I104" s="22" t="inlineStr">
+        <is>
+          <t>T-141</t>
+        </is>
+      </c>
+      <c r="J104" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="50" customHeight="1" s="15">
+      <c r="A105" s="22" t="inlineStr">
+        <is>
+          <t>TC-100</t>
+        </is>
+      </c>
+      <c r="B105" s="22" t="inlineStr">
+        <is>
+          <t>Agent Lifecycle</t>
+        </is>
+      </c>
+      <c r="C105" s="23" t="inlineStr">
+        <is>
+          <t>Heartbeat: повторный heartbeat с тем же статусом не создает запись в status-log</t>
+        </is>
+      </c>
+      <c r="D105" s="23" t="inlineStr">
+        <is>
+          <t>Устройство 60b50ed1, текущий статус online</t>
+        </is>
+      </c>
+      <c r="E105" s="22" t="inlineStr">
+        <is>
+          <t>1. Запомнить total_elements в status-log\n2. PUT heartbeat с тем же status=online\n3. Проверить total_elements не изменился</t>
+        </is>
+      </c>
+      <c r="F105" s="22" t="inlineStr">
+        <is>
+          <t>total_elements до и после одинаков, дубликат не создан</t>
+        </is>
+      </c>
+      <c r="G105" s="23" t="inlineStr">
+        <is>
+          <t>total_elements=11 до и после повторного heartbeat с status=online, дубликат не создан</t>
+        </is>
+      </c>
+      <c r="H105" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I105" s="22" t="inlineStr">
+        <is>
+          <t>T-141</t>
+        </is>
+      </c>
+      <c r="J105" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="50" customHeight="1" s="15">
+      <c r="A106" s="22" t="inlineStr">
+        <is>
+          <t>TC-101</t>
+        </is>
+      </c>
+      <c r="B106" s="22" t="inlineStr">
+        <is>
+          <t>Agent Lifecycle</t>
+        </is>
+      </c>
+      <c r="C106" s="23" t="inlineStr">
+        <is>
+          <t>Status-Log: happy path - список переходов статусов</t>
+        </is>
+      </c>
+      <c r="D106" s="23" t="inlineStr">
+        <is>
+          <t>Устройство 60b50ed1, ранее выполнены heartbeat с разными статусами</t>
+        </is>
+      </c>
+      <c r="E106" s="22" t="inlineStr">
+        <is>
+          <t>1. GET /api/cp/v1/devices/{id}/status-log?page=0&amp;size=20\n2. Проверить HTTP 200\n3. Проверить структуру: content[], page, size, total_elements, total_pages\n4. Каждый элемент содержит: id, device_id, previous_status, new_status, changed_ts, trigger, details</t>
+        </is>
+      </c>
+      <c r="F106" s="22" t="inlineStr">
+        <is>
+          <t>HTTP 200, paginated response с корректной структурой, записи отсортированы по changed_ts DESC</t>
+        </is>
+      </c>
+      <c r="G106" s="23" t="inlineStr">
+        <is>
+          <t>HTTP 200, paginated: {content: [...], page: 0, size: 20, total_elements: 9, total_pages: 1}. Каждый элемент: id, device_id, previous_status, new_status, changed_ts, trigger=heartbeat, details</t>
+        </is>
+      </c>
+      <c r="H106" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I106" s="22" t="inlineStr">
+        <is>
+          <t>T-141</t>
+        </is>
+      </c>
+      <c r="J106" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="50" customHeight="1" s="15">
+      <c r="A107" s="22" t="inlineStr">
+        <is>
+          <t>TC-102</t>
+        </is>
+      </c>
+      <c r="B107" s="22" t="inlineStr">
+        <is>
+          <t>Agent Lifecycle</t>
+        </is>
+      </c>
+      <c r="C107" s="23" t="inlineStr">
+        <is>
+          <t>Status-Log: пагинация (page/size/total_pages)</t>
+        </is>
+      </c>
+      <c r="D107" s="23" t="inlineStr">
+        <is>
+          <t>Устройство 60b50ed1, минимум 9 записей в status-log</t>
+        </is>
+      </c>
+      <c r="E107" s="22" t="inlineStr">
+        <is>
+          <t>1. GET status-log?page=0&amp;size=3 -&gt; 3 записи, total_pages=N\n2. GET status-log?page=1&amp;size=3 -&gt; следующие 3 записи\n3. GET status-log?page=last&amp;size=3 -&gt; остаток записей\n4. Проверить что записи не дублируются между страницами</t>
+        </is>
+      </c>
+      <c r="F107" s="22" t="inlineStr">
+        <is>
+          <t>Пагинация корректна: total_elements совпадает, записи не дублируются, last page содержит остаток</t>
+        </is>
+      </c>
+      <c r="G107" s="23" t="inlineStr">
+        <is>
+          <t>page=0,size=3: 3 записи, total_pages=4. page=1,size=3: следующие 3. page=3,size=3: 2 остаточных записи. Записи не дублируются между страницами</t>
+        </is>
+      </c>
+      <c r="H107" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I107" s="22" t="inlineStr">
+        <is>
+          <t>T-141</t>
+        </is>
+      </c>
+      <c r="J107" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="50" customHeight="1" s="15">
+      <c r="A108" s="22" t="inlineStr">
+        <is>
+          <t>TC-103</t>
+        </is>
+      </c>
+      <c r="B108" s="22" t="inlineStr">
+        <is>
+          <t>Agent Lifecycle</t>
+        </is>
+      </c>
+      <c r="C108" s="23" t="inlineStr">
+        <is>
+          <t>Status-Log: фильтрация по дате (from/to)</t>
+        </is>
+      </c>
+      <c r="D108" s="23" t="inlineStr">
+        <is>
+          <t>Устройство 60b50ed1, записи с known timestamps</t>
+        </is>
+      </c>
+      <c r="E108" s="22" t="inlineStr">
+        <is>
+          <t>1. GET status-log?from=T1&amp;to=T2 где T1-T2 покрывает часть записей\n2. Проверить что возвращены только записи в диапазоне\n3. GET status-log?from=future_date -&gt; пустой результат\n4. Проверить HTTP 200 и total_elements=0</t>
+        </is>
+      </c>
+      <c r="F108" s="22" t="inlineStr">
+        <is>
+          <t>Фильтрация по дате корректна, пустой диапазон возвращает 0 записей с HTTP 200</t>
+        </is>
+      </c>
+      <c r="G108" s="23" t="inlineStr">
+        <is>
+          <t>from=...55Z&amp;to=...58Z: 4 записи в диапазоне. from=2027-01-01: 0 записей, HTTP 200, total_elements=0</t>
+        </is>
+      </c>
+      <c r="H108" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I108" s="22" t="inlineStr">
+        <is>
+          <t>T-141</t>
+        </is>
+      </c>
+      <c r="J108" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="50" customHeight="1" s="15">
+      <c r="A109" s="22" t="inlineStr">
+        <is>
+          <t>TC-104</t>
+        </is>
+      </c>
+      <c r="B109" s="22" t="inlineStr">
+        <is>
+          <t>Agent Lifecycle</t>
+        </is>
+      </c>
+      <c r="C109" s="23" t="inlineStr">
+        <is>
+          <t>Status-Log: несуществующее устройство -&gt; 404</t>
+        </is>
+      </c>
+      <c r="D109" s="23" t="inlineStr">
+        <is>
+          <t>Нет устройства с ID 00000000-0000-0000-0000-000000000000</t>
+        </is>
+      </c>
+      <c r="E109" s="22" t="inlineStr">
+        <is>
+          <t>1. GET status-log для device 00000000-0000-0000-0000-000000000000\n2. Проверить HTTP 404</t>
+        </is>
+      </c>
+      <c r="F109" s="22" t="inlineStr">
+        <is>
+          <t>HTTP 404, body: {error: 'Device not found: ...', code: 'DEVICE_NOT_FOUND'}</t>
+        </is>
+      </c>
+      <c r="G109" s="23" t="inlineStr">
+        <is>
+          <t>HTTP 404, body: {error: 'Device not found: 00000000-0000-0000-0000-000000000000', code: 'DEVICE_NOT_FOUND'}</t>
+        </is>
+      </c>
+      <c r="H109" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I109" s="22" t="inlineStr">
+        <is>
+          <t>T-141</t>
+        </is>
+      </c>
+      <c r="J109" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="50" customHeight="1" s="15">
+      <c r="A110" s="22" t="inlineStr">
+        <is>
+          <t>TC-105</t>
+        </is>
+      </c>
+      <c r="B110" s="22" t="inlineStr">
+        <is>
+          <t>Agent Lifecycle</t>
+        </is>
+      </c>
+      <c r="C110" s="23" t="inlineStr">
+        <is>
+          <t>Status-Log: без авторизации -&gt; 401</t>
+        </is>
+      </c>
+      <c r="D110" s="23" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="E110" s="22" t="inlineStr">
+        <is>
+          <t>1. GET status-log без заголовка Authorization\n2. Проверить HTTP 401</t>
+        </is>
+      </c>
+      <c r="F110" s="22" t="inlineStr">
+        <is>
+          <t>HTTP 401, body: {error: '...', code: 'UNAUTHORIZED'}</t>
+        </is>
+      </c>
+      <c r="G110" s="23" t="inlineStr">
+        <is>
+          <t>HTTP 401, body: {error: 'Missing or invalid Authorization header', code: 'UNAUTHORIZED'}</t>
+        </is>
+      </c>
+      <c r="H110" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I110" s="22" t="inlineStr">
+        <is>
+          <t>T-141</t>
+        </is>
+      </c>
+      <c r="J110" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="50" customHeight="1" s="15">
+      <c r="A111" s="22" t="inlineStr">
+        <is>
+          <t>TC-106</t>
+        </is>
+      </c>
+      <c r="B111" s="22" t="inlineStr">
+        <is>
+          <t>Agent Lifecycle</t>
+        </is>
+      </c>
+      <c r="C111" s="23" t="inlineStr">
+        <is>
+          <t>Status-Log: cross-tenant device -&gt; 404 (tenant isolation)</t>
+        </is>
+      </c>
+      <c r="D111" s="23" t="inlineStr">
+        <is>
+          <t>Устройство 64b4d56e в тенанте Тест 1, JWT user test из Test Organization</t>
+        </is>
+      </c>
+      <c r="E111" s="22" t="inlineStr">
+        <is>
+          <t>1. GET status-log для device 64b4d56e с токеном user test\n2. Проверить HTTP 404 (не 403)</t>
+        </is>
+      </c>
+      <c r="F111" s="22" t="inlineStr">
+        <is>
+          <t>HTTP 404, code: DEVICE_NOT_FOUND. Тенантная изоляция: устройство не видно из другого тенанта</t>
+        </is>
+      </c>
+      <c r="G111" s="23" t="inlineStr">
+        <is>
+          <t>HTTP 404, body: {error: 'Device not found: 64b4d56e-...', code: 'DEVICE_NOT_FOUND'}. Тенантная изоляция работает: 404, а не 403</t>
+        </is>
+      </c>
+      <c r="H111" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I111" s="22" t="inlineStr">
+        <is>
+          <t>T-141</t>
+        </is>
+      </c>
+      <c r="J111" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="50" customHeight="1" s="15">
+      <c r="A112" s="22" t="inlineStr">
+        <is>
+          <t>TC-107</t>
+        </is>
+      </c>
+      <c r="B112" s="22" t="inlineStr">
+        <is>
+          <t>Agent Lifecycle</t>
+        </is>
+      </c>
+      <c r="C112" s="23" t="inlineStr">
+        <is>
+          <t>Device Settings: heartbeat возвращает корректные настройки устройства</t>
+        </is>
+      </c>
+      <c r="D112" s="23" t="inlineStr">
+        <is>
+          <t>Устройство 60b50ed1 с сохраненными settings</t>
+        </is>
+      </c>
+      <c r="E112" s="22" t="inlineStr">
+        <is>
+          <t>1. GET device details -&gt; запомнить settings\n2. PUT heartbeat\n3. Сравнить device_settings из heartbeat response с settings из device details\n4. Проверить fps=1, resolution=720p</t>
+        </is>
+      </c>
+      <c r="F112" s="22" t="inlineStr">
+        <is>
+          <t>device_settings в heartbeat совпадают с settings устройства в БД, fps=1, resolution=720p</t>
+        </is>
+      </c>
+      <c r="G112" s="23" t="inlineStr">
+        <is>
+          <t>device_settings из heartbeat: {fps:1, auto_start:true, resolution:720p, session_max_duration_hours:24} совпадает с settings устройства из GET /devices/{id}</t>
+        </is>
+      </c>
+      <c r="H112" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I112" s="22" t="inlineStr">
+        <is>
+          <t>T-141</t>
+        </is>
+      </c>
+      <c r="J112" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="50" customHeight="1" s="15">
+      <c r="A113" s="22" t="inlineStr">
+        <is>
+          <t>TC-108</t>
+        </is>
+      </c>
+      <c r="B113" s="22" t="inlineStr">
+        <is>
+          <t>Agent Lifecycle</t>
+        </is>
+      </c>
+      <c r="C113" s="23" t="inlineStr">
+        <is>
+          <t>Auth-service: дефолты device settings (capture_fps=1, auto_start=false, resolution=720p)</t>
+        </is>
+      </c>
+      <c r="D113" s="23" t="inlineStr">
+        <is>
+          <t>Код auth-service проверен, application.yml без overrides</t>
+        </is>
+      </c>
+      <c r="E113" s="22" t="inlineStr">
+        <is>
+          <t>1. Проверить @Value аннотации в DeviceAuthService\n2. Дефолты: capture-fps=1, quality=low, default-resolution=720p, segment-duration-sec=60, default-session-max-min=60, default-session-max-hours=0, default-auto-start=false</t>
+        </is>
+      </c>
+      <c r="F113" s="22" t="inlineStr">
+        <is>
+          <t>Дефолты соответствуют спецификации: fps=1, quality=low, resolution=720p, segment_duration=60s, session_max=60min, auto_start=false</t>
+        </is>
+      </c>
+      <c r="G113" s="23" t="inlineStr">
+        <is>
+          <t>Код DeviceAuthService проверен. @Value дефолты: capture-fps=1, quality=low, default-resolution=720p, segment-duration-sec=60, default-session-max-min=60, default-session-max-hours=0, default-auto-start=false. Соответствует спецификации</t>
+        </is>
+      </c>
+      <c r="H113" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I113" s="22" t="inlineStr">
+        <is>
+          <t>T-141</t>
+        </is>
+      </c>
+      <c r="J113" s="23" t="inlineStr">
         <is>
           <t>09.03.2026</t>
         </is>

--- a/docs/tracker.xlsx
+++ b/docs/tracker.xlsx
@@ -610,7 +610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I160"/>
+  <dimension ref="A1:I168"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="15" min="1" max="1"/>
@@ -7995,6 +7995,382 @@
         </is>
       </c>
     </row>
+    <row r="161" ht="20" customHeight="1" s="15">
+      <c r="A161" s="24" t="inlineStr">
+        <is>
+          <t>T-156</t>
+        </is>
+      </c>
+      <c r="B161" s="24" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="C161" s="25" t="inlineStr">
+        <is>
+          <t>Timeline: невалидная дата возвращает 500 вместо 400</t>
+        </is>
+      </c>
+      <c r="D161" s="25" t="inlineStr">
+        <is>
+          <t>GET /api/v1/ingest/users/timeline?date=invalid возвращает 500 Internal Server Error вместо 400 Bad Request. Сервер не валидирует формат даты в query param date и необработанное исключение парсинга пробрасывается как 500. Необходимо добавить try-catch при парсинге LocalDate и возвращать 400 с информативным сообщением. Среда: test. Связанный тест: TC-111.</t>
+        </is>
+      </c>
+      <c r="E161" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F161" s="24" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G161" s="25" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H161" s="24" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+      <c r="I161" s="24" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="20" customHeight="1" s="15">
+      <c r="A162" s="24" t="inlineStr">
+        <is>
+          <t>T-157</t>
+        </is>
+      </c>
+      <c r="B162" s="24" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="C162" s="25" t="inlineStr">
+        <is>
+          <t>Catalogs: SUPER_ADMIN без tenant_id получает 500 (null tenant)</t>
+        </is>
+      </c>
+      <c r="D162" s="25" t="inlineStr">
+        <is>
+          <t>GET /api/v1/ingest/catalogs/groups?group_type=APP от SUPER_ADMIN (scope=global) без явного tenant_id возвращает 500. Причина: resolveEffectiveTenantId() при scope=global возвращает tenantIdParam as-is, который null. CatalogService.getGroups(null, ...) вызывает seed(null, ...) -&gt; INSERT с tenant_id=null -&gt; PSQLException: not-null constraint violation на app_groups.tenant_id. Workaround: передавать tenant_id явно. Fix: в resolveEffectiveTenantId при global scope если tenantIdParam=null, использовать principal.getTenantId() как fallback, либо возвращать 400 'tenant_id is required for global scope'. Среда: test. Связанные тесты: TC-114, TC-115.</t>
+        </is>
+      </c>
+      <c r="E162" s="24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F162" s="24" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G162" s="25" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H162" s="24" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+      <c r="I162" s="24" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="20" customHeight="1" s="15">
+      <c r="A163" s="24" t="inlineStr">
+        <is>
+          <t>T-158</t>
+        </is>
+      </c>
+      <c r="B163" s="24" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="C163" s="25" t="inlineStr">
+        <is>
+          <t>Timeline SQL: неверная нижняя граница date AT TIME ZONE отрезает 0-6ч MSK</t>
+        </is>
+      </c>
+      <c r="D163" s="25" t="inlineStr">
+        <is>
+          <t>В TimelineService.queryFocusIntervals SQL-выражение CAST(:date AS date) AT TIME ZONE :tz возвращает timestamp without time zone (не timestamptz), из-за чего PostgreSQL интерпретирует границу как UTC, а не как московское время. Для date=2026-03-09 tz=Europe/Moscow: фактическая нижняя граница = 06:00 MSK вместо 00:00 MSK. Данные с 00:00 до 06:00 MSK не попадают в выборку. Файл: TimelineService.java, строка 77.</t>
+        </is>
+      </c>
+      <c r="E163" s="24" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F163" s="24" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G163" s="25" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H163" s="24" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+      <c r="I163" s="24" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="20" customHeight="1" s="15">
+      <c r="A164" s="24" t="inlineStr">
+        <is>
+          <t>T-159</t>
+        </is>
+      </c>
+      <c r="B164" s="24" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="C164" s="25" t="inlineStr">
+        <is>
+          <t>Focus intervals: session_id всегда NULL — красные участки не отображаются</t>
+        </is>
+      </c>
+      <c r="D164" s="25" t="inlineStr">
+        <is>
+          <t>В таблице app_focus_intervals session_id = NULL для 100% записей (400 из 400). Агент передаёт sessionId = _commandHandler.CurrentSessionId, но это значение = null, если запись (recording) была запущена не командой START_RECORDING, а автоматически. При автозапуске записи SessionManager._currentSessionId заполняется, но ActiveWindowTracker/TrayWindowTracker может получать его с задержкой или из другого потока. Из-за отсутствия session_id backend не может определить has_recording=true, и красные полоски не отображаются. Файл: ActiveWindowTracker.cs:138, SessionManager.cs:49.</t>
+        </is>
+      </c>
+      <c r="E164" s="24" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F164" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G164" s="25" t="inlineStr">
+        <is>
+          <t>Алексей</t>
+        </is>
+      </c>
+      <c r="H164" s="24" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+      <c r="I164" s="24" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="20" customHeight="1" s="15">
+      <c r="A165" s="24" t="inlineStr">
+        <is>
+          <t>T-160</t>
+        </is>
+      </c>
+      <c r="B165" s="24" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="C165" s="25" t="inlineStr">
+        <is>
+          <t>Timeline: пользователи без focus intervals не отображаются (только из focusRows)</t>
+        </is>
+      </c>
+      <c r="D165" s="25" t="inlineStr">
+        <is>
+          <t>TimelineService.assembleTimeline() собирает пользователей ТОЛЬКО из focusRows (строка 179: byUser.entrySet()). Комментарий на строке 176 'Also include users from userInfoMap that might not have focus data' не реализован — код итерирует только byUser, игнорируя пользователей из device_user_sessions без focus данных. Если пользователь залогинен на устройстве, но не имеет focus intervals за выбранный день, он не попадёт в таймлайн.</t>
+        </is>
+      </c>
+      <c r="E165" s="24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F165" s="24" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G165" s="25" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H165" s="24" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+      <c r="I165" s="24" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="20" customHeight="1" s="15">
+      <c r="A166" s="24" t="inlineStr">
+        <is>
+          <t>T-161</t>
+        </is>
+      </c>
+      <c r="B166" s="24" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="C166" s="25" t="inlineStr">
+        <is>
+          <t>Dashboard графики не отображают данные (SQL date cast + DTO mismatch)</t>
+        </is>
+      </c>
+      <c r="D166" s="25" t="inlineStr">
+        <is>
+          <t>1. SQL: CAST(:from AS date) возвращает неверные границы дат → данные не попадают в выборку. Fix: CAST(:from AS timestamp). 2. DTO GroupInfo имел поля id/name, а фронт ожидал group_id/group_name (Jackson SNAKE_CASE). 3. Ungrouped данные (default group) не выделялись отдельно.</t>
+        </is>
+      </c>
+      <c r="E166" s="24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F166" s="24" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G166" s="25" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H166" s="24" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+      <c r="I166" s="24" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="20" customHeight="1" s="15">
+      <c r="A167" s="24" t="inlineStr">
+        <is>
+          <t>T-162</t>
+        </is>
+      </c>
+      <c r="B167" s="24" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="C167" s="25" t="inlineStr">
+        <is>
+          <t>Timeline: нет информации о записях (server-side корреляция)</t>
+        </is>
+      </c>
+      <c r="D167" s="25" t="inlineStr">
+        <is>
+          <t>Timeline API не проверял наличие recording_sessions для каждого часа. Fix: добавлен запрос к recording_sessions + корреляция по device_id + overlap часа. has_recording и recording_session_ids теперь заполняются корректно.</t>
+        </is>
+      </c>
+      <c r="E167" s="24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F167" s="24" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G167" s="25" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="H167" s="24" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+      <c r="I167" s="24" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="20" customHeight="1" s="15">
+      <c r="A168" s="24" t="inlineStr">
+        <is>
+          <t>T-163</t>
+        </is>
+      </c>
+      <c r="B168" s="24" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="C168" s="25" t="inlineStr">
+        <is>
+          <t>Timeline: невидимые bars групп приложений и нет bars для отдельных приложений</t>
+        </is>
+      </c>
+      <c r="D168" s="25" t="inlineStr">
+        <is>
+          <t>1. HourCells использовал colorClass=opacity-70 (нет фона → невидимые бары). Fix: inline style с backgroundColor. 2. Строки отдельных приложений имели пустые div без данных. Fix: добавлен расчёт per-hour per-app данных и рендеринг HourCells для всех уровней drill-down.</t>
+        </is>
+      </c>
+      <c r="E168" s="24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F168" s="24" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G168" s="25" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="H168" s="24" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+      <c r="I168" s="24" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
@@ -8009,7 +8385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J113"/>
+  <dimension ref="A1:J137"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="15" min="1" max="1"/>
@@ -13706,6 +14082,1250 @@
       <c r="J113" s="23" t="inlineStr">
         <is>
           <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="50" customHeight="1" s="15">
+      <c r="A114" s="22" t="inlineStr">
+        <is>
+          <t>TC-109</t>
+        </is>
+      </c>
+      <c r="B114" s="22" t="inlineStr">
+        <is>
+          <t>Timeline API</t>
+        </is>
+      </c>
+      <c r="C114" s="23" t="inlineStr">
+        <is>
+          <t>Timeline endpoint - happy path (сегодня)</t>
+        </is>
+      </c>
+      <c r="D114" s="23" t="inlineStr">
+        <is>
+          <t>JWT superadmin, test-стейджинг</t>
+        </is>
+      </c>
+      <c r="E114" s="22" t="inlineStr">
+        <is>
+          <t>1. GET /users/timeline?date=&lt;today&gt;\n2. Проверить HTTP 200\n3. Проверить JSON: date, timezone, users[]</t>
+        </is>
+      </c>
+      <c r="F114" s="22" t="inlineStr">
+        <is>
+          <t>200, JSON с полями date, timezone, users[]</t>
+        </is>
+      </c>
+      <c r="G114" s="23" t="inlineStr">
+        <is>
+          <t>200, JSON: date=2026-03-09, timezone=Europe/Moscow, users[] с 2 пользователями, hours[] с app_groups[]</t>
+        </is>
+      </c>
+      <c r="H114" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I114" s="22" t="inlineStr">
+        <is>
+          <t>T-142</t>
+        </is>
+      </c>
+      <c r="J114" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="50" customHeight="1" s="15">
+      <c r="A115" s="22" t="inlineStr">
+        <is>
+          <t>TC-110</t>
+        </is>
+      </c>
+      <c r="B115" s="22" t="inlineStr">
+        <is>
+          <t>Timeline API</t>
+        </is>
+      </c>
+      <c r="C115" s="23" t="inlineStr">
+        <is>
+          <t>Timeline endpoint - конкретная дата 2026-03-09</t>
+        </is>
+      </c>
+      <c r="D115" s="23" t="inlineStr">
+        <is>
+          <t>JWT superadmin, test-стейджинг</t>
+        </is>
+      </c>
+      <c r="E115" s="22" t="inlineStr">
+        <is>
+          <t>1. GET /users/timeline?date=2026-03-09\n2. Проверить HTTP 200\n3. Проверить JSON структуру</t>
+        </is>
+      </c>
+      <c r="F115" s="22" t="inlineStr">
+        <is>
+          <t>200, JSON</t>
+        </is>
+      </c>
+      <c r="G115" s="23" t="inlineStr">
+        <is>
+          <t>200, JSON: date=2026-03-09, timezone=Europe/Moscow, users[] с 2 пользователями и корректными данными</t>
+        </is>
+      </c>
+      <c r="H115" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I115" s="22" t="inlineStr">
+        <is>
+          <t>T-142</t>
+        </is>
+      </c>
+      <c r="J115" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="50" customHeight="1" s="15">
+      <c r="A116" s="22" t="inlineStr">
+        <is>
+          <t>TC-111</t>
+        </is>
+      </c>
+      <c r="B116" s="22" t="inlineStr">
+        <is>
+          <t>Timeline API</t>
+        </is>
+      </c>
+      <c r="C116" s="23" t="inlineStr">
+        <is>
+          <t>Timeline endpoint - невалидная дата</t>
+        </is>
+      </c>
+      <c r="D116" s="23" t="inlineStr">
+        <is>
+          <t>JWT superadmin, test-стейджинг</t>
+        </is>
+      </c>
+      <c r="E116" s="22" t="inlineStr">
+        <is>
+          <t>1. GET /users/timeline?date=invalid\n2. Проверить HTTP 400</t>
+        </is>
+      </c>
+      <c r="F116" s="22" t="inlineStr">
+        <is>
+          <t>400 Bad Request</t>
+        </is>
+      </c>
+      <c r="G116" s="23" t="inlineStr">
+        <is>
+          <t>400 Bad Request с сообщением 'Invalid date format: invalid. Expected: yyyy-MM-dd' (после фикса T-156)</t>
+        </is>
+      </c>
+      <c r="H116" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I116" s="22" t="inlineStr">
+        <is>
+          <t>T-142</t>
+        </is>
+      </c>
+      <c r="J116" s="23" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="50" customHeight="1" s="15">
+      <c r="A117" s="22" t="inlineStr">
+        <is>
+          <t>TC-112</t>
+        </is>
+      </c>
+      <c r="B117" s="22" t="inlineStr">
+        <is>
+          <t>Timeline API</t>
+        </is>
+      </c>
+      <c r="C117" s="23" t="inlineStr">
+        <is>
+          <t>Timeline endpoint - без авторизации</t>
+        </is>
+      </c>
+      <c r="D117" s="23" t="inlineStr">
+        <is>
+          <t>Без JWT, test-стейджинг</t>
+        </is>
+      </c>
+      <c r="E117" s="22" t="inlineStr">
+        <is>
+          <t>1. GET /users/timeline?date=2026-03-09 без Authorization header\n2. Проверить HTTP 401</t>
+        </is>
+      </c>
+      <c r="F117" s="22" t="inlineStr">
+        <is>
+          <t>401 Unauthorized</t>
+        </is>
+      </c>
+      <c r="G117" s="23" t="inlineStr">
+        <is>
+          <t>401 с {error:Missing or invalid Authorization header,code:MISSING_TOKEN}</t>
+        </is>
+      </c>
+      <c r="H117" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I117" s="22" t="inlineStr">
+        <is>
+          <t>T-142</t>
+        </is>
+      </c>
+      <c r="J117" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="50" customHeight="1" s="15">
+      <c r="A118" s="22" t="inlineStr">
+        <is>
+          <t>TC-113</t>
+        </is>
+      </c>
+      <c r="B118" s="22" t="inlineStr">
+        <is>
+          <t>Timeline API</t>
+        </is>
+      </c>
+      <c r="C118" s="23" t="inlineStr">
+        <is>
+          <t>Timeline endpoint - с таймзоной UTC</t>
+        </is>
+      </c>
+      <c r="D118" s="23" t="inlineStr">
+        <is>
+          <t>JWT superadmin, test-стейджинг</t>
+        </is>
+      </c>
+      <c r="E118" s="22" t="inlineStr">
+        <is>
+          <t>1. GET /users/timeline?date=2026-03-09&amp;timezone=UTC\n2. Проверить HTTP 200\n3. Проверить timezone в ответе</t>
+        </is>
+      </c>
+      <c r="F118" s="22" t="inlineStr">
+        <is>
+          <t>200, JSON с timezone=UTC</t>
+        </is>
+      </c>
+      <c r="G118" s="23" t="inlineStr">
+        <is>
+          <t>200, JSON: timezone=UTC, часы сдвинуты на -3 от Europe/Moscow (hour 10 MSK = hour 7 UTC). Конверсия таймзон работает корректно.</t>
+        </is>
+      </c>
+      <c r="H118" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I118" s="22" t="inlineStr">
+        <is>
+          <t>T-142</t>
+        </is>
+      </c>
+      <c r="J118" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="50" customHeight="1" s="15">
+      <c r="A119" s="22" t="inlineStr">
+        <is>
+          <t>TC-114</t>
+        </is>
+      </c>
+      <c r="B119" s="22" t="inlineStr">
+        <is>
+          <t>Catalogs API</t>
+        </is>
+      </c>
+      <c r="C119" s="23" t="inlineStr">
+        <is>
+          <t>Группы приложений - список (fix TypeError length)</t>
+        </is>
+      </c>
+      <c r="D119" s="23" t="inlineStr">
+        <is>
+          <t>JWT superadmin, test-стейджинг, T-155 исправлен</t>
+        </is>
+      </c>
+      <c r="E119" s="22" t="inlineStr">
+        <is>
+          <t>1. GET /catalogs/groups?type=APP\n2. Проверить HTTP 200\n3. Проверить что ответ - JSON массив</t>
+        </is>
+      </c>
+      <c r="F119" s="22" t="inlineStr">
+        <is>
+          <t>200, JSON массив (НЕ обертка)</t>
+        </is>
+      </c>
+      <c r="G119" s="23" t="inlineStr">
+        <is>
+          <t>400 Bad Request с 'tenant_id is required for global scope' при запросе без tenant_id. С tenant_id — 200, 9 групп (после фикса T-157)</t>
+        </is>
+      </c>
+      <c r="H119" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I119" s="22" t="inlineStr">
+        <is>
+          <t>T-155</t>
+        </is>
+      </c>
+      <c r="J119" s="23" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="50" customHeight="1" s="15">
+      <c r="A120" s="22" t="inlineStr">
+        <is>
+          <t>TC-115</t>
+        </is>
+      </c>
+      <c r="B120" s="22" t="inlineStr">
+        <is>
+          <t>Catalogs API</t>
+        </is>
+      </c>
+      <c r="C120" s="23" t="inlineStr">
+        <is>
+          <t>Группы сайтов - список</t>
+        </is>
+      </c>
+      <c r="D120" s="23" t="inlineStr">
+        <is>
+          <t>JWT superadmin, test-стейджинг</t>
+        </is>
+      </c>
+      <c r="E120" s="22" t="inlineStr">
+        <is>
+          <t>1. GET /catalogs/groups?type=SITE\n2. Проверить HTTP 200\n3. Проверить что ответ - JSON массив</t>
+        </is>
+      </c>
+      <c r="F120" s="22" t="inlineStr">
+        <is>
+          <t>200, JSON массив</t>
+        </is>
+      </c>
+      <c r="G120" s="23" t="inlineStr">
+        <is>
+          <t>400 Bad Request с 'tenant_id is required for global scope' при запросе без tenant_id. С tenant_id — 200, 13 групп (после фикса T-157)</t>
+        </is>
+      </c>
+      <c r="H120" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I120" s="22" t="inlineStr">
+        <is>
+          <t>T-155</t>
+        </is>
+      </c>
+      <c r="J120" s="23" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="50" customHeight="1" s="15">
+      <c r="A121" s="22" t="inlineStr">
+        <is>
+          <t>TC-116</t>
+        </is>
+      </c>
+      <c r="B121" s="22" t="inlineStr">
+        <is>
+          <t>OAuth</t>
+        </is>
+      </c>
+      <c r="C121" s="23" t="inlineStr">
+        <is>
+          <t>Mail.ru OAuth endpoint удален</t>
+        </is>
+      </c>
+      <c r="D121" s="23" t="inlineStr">
+        <is>
+          <t>test-стейджинг, Mail.ru OAuth удален из auth-service</t>
+        </is>
+      </c>
+      <c r="E121" s="22" t="inlineStr">
+        <is>
+          <t>1. GET /api/v1/auth/oauth/mailru\n2. Проверить что НЕ 200/302</t>
+        </is>
+      </c>
+      <c r="F121" s="22" t="inlineStr">
+        <is>
+          <t>404 или 401 (НЕ 200/302)</t>
+        </is>
+      </c>
+      <c r="G121" s="23" t="inlineStr">
+        <is>
+          <t>401 с {error:Authentication required,code:UNAUTHORIZED}. Endpoint недоступен - Mail.ru OAuth удален.</t>
+        </is>
+      </c>
+      <c r="H121" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I121" s="22" t="inlineStr">
+        <is>
+          <t>T-145</t>
+        </is>
+      </c>
+      <c r="J121" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="50" customHeight="1" s="15">
+      <c r="A122" s="22" t="inlineStr">
+        <is>
+          <t>TC-117</t>
+        </is>
+      </c>
+      <c r="B122" s="22" t="inlineStr">
+        <is>
+          <t>OAuth</t>
+        </is>
+      </c>
+      <c r="C122" s="23" t="inlineStr">
+        <is>
+          <t>Mail.ru callback удален</t>
+        </is>
+      </c>
+      <c r="D122" s="23" t="inlineStr">
+        <is>
+          <t>test-стейджинг, Mail.ru OAuth удален</t>
+        </is>
+      </c>
+      <c r="E122" s="22" t="inlineStr">
+        <is>
+          <t>1. GET /api/v1/auth/oauth/mailru/callback?code=test&amp;state=test\n2. Проверить что НЕ 200/302</t>
+        </is>
+      </c>
+      <c r="F122" s="22" t="inlineStr">
+        <is>
+          <t>404 или 401</t>
+        </is>
+      </c>
+      <c r="G122" s="23" t="inlineStr">
+        <is>
+          <t>401 с {error:Authentication required,code:UNAUTHORIZED}. Callback endpoint недоступен - Mail.ru OAuth удален.</t>
+        </is>
+      </c>
+      <c r="H122" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I122" s="22" t="inlineStr">
+        <is>
+          <t>T-145</t>
+        </is>
+      </c>
+      <c r="J122" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="50" customHeight="1" s="15">
+      <c r="A123" s="22" t="inlineStr">
+        <is>
+          <t>TC-118</t>
+        </is>
+      </c>
+      <c r="B123" s="22" t="inlineStr">
+        <is>
+          <t>OAuth</t>
+        </is>
+      </c>
+      <c r="C123" s="23" t="inlineStr">
+        <is>
+          <t>Yandex OAuth все еще работает</t>
+        </is>
+      </c>
+      <c r="D123" s="23" t="inlineStr">
+        <is>
+          <t>test-стейджинг</t>
+        </is>
+      </c>
+      <c r="E123" s="22" t="inlineStr">
+        <is>
+          <t>1. GET /api/v1/auth/oauth/yandex\n2. Проверить HTTP 200 или 302</t>
+        </is>
+      </c>
+      <c r="F123" s="22" t="inlineStr">
+        <is>
+          <t>200 или 302 (redirect к Яндексу)</t>
+        </is>
+      </c>
+      <c r="G123" s="23" t="inlineStr">
+        <is>
+          <t>302 redirect. Yandex OAuth работает, возвращает redirect к Яндексу.</t>
+        </is>
+      </c>
+      <c r="H123" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I123" s="22" t="inlineStr">
+        <is>
+          <t>T-145</t>
+        </is>
+      </c>
+      <c r="J123" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="50" customHeight="1" s="15">
+      <c r="A124" s="22" t="inlineStr">
+        <is>
+          <t>TC-119</t>
+        </is>
+      </c>
+      <c r="B124" s="22" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="C124" s="23" t="inlineStr">
+        <is>
+          <t>Favicon загружается (favicon.png)</t>
+        </is>
+      </c>
+      <c r="D124" s="23" t="inlineStr">
+        <is>
+          <t>test-стейджинг</t>
+        </is>
+      </c>
+      <c r="E124" s="22" t="inlineStr">
+        <is>
+          <t>1. GET /screenrecorder/favicon.png\n2. Проверить HTTP 200</t>
+        </is>
+      </c>
+      <c r="F124" s="22" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G124" s="23" t="inlineStr">
+        <is>
+          <t>200. Favicon загружается корректно.</t>
+        </is>
+      </c>
+      <c r="H124" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I124" s="22" t="inlineStr">
+        <is>
+          <t>T-151</t>
+        </is>
+      </c>
+      <c r="J124" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="50" customHeight="1" s="15">
+      <c r="A125" s="22" t="inlineStr">
+        <is>
+          <t>TC-120</t>
+        </is>
+      </c>
+      <c r="B125" s="22" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="C125" s="23" t="inlineStr">
+        <is>
+          <t>SPA загружается</t>
+        </is>
+      </c>
+      <c r="D125" s="23" t="inlineStr">
+        <is>
+          <t>test-стейджинг</t>
+        </is>
+      </c>
+      <c r="E125" s="22" t="inlineStr">
+        <is>
+          <t>1. GET /screenrecorder/\n2. Проверить HTTP 200</t>
+        </is>
+      </c>
+      <c r="F125" s="22" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="G125" s="23" t="inlineStr">
+        <is>
+          <t>200. SPA загружается корректно.</t>
+        </is>
+      </c>
+      <c r="H125" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I125" s="22" t="inlineStr">
+        <is>
+          <t>T-151</t>
+        </is>
+      </c>
+      <c r="J125" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="50" customHeight="1" s="15">
+      <c r="A126" s="22" t="inlineStr">
+        <is>
+          <t>TC-121</t>
+        </is>
+      </c>
+      <c r="B126" s="22" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="C126" s="23" t="inlineStr">
+        <is>
+          <t>HTML содержит favicon.png (не vite.svg)</t>
+        </is>
+      </c>
+      <c r="D126" s="23" t="inlineStr">
+        <is>
+          <t>test-стейджинг</t>
+        </is>
+      </c>
+      <c r="E126" s="22" t="inlineStr">
+        <is>
+          <t>1. GET /screenrecorder/\n2. Найти в HTML favicon.png\n3. Убедиться что нет vite.svg</t>
+        </is>
+      </c>
+      <c r="F126" s="22" t="inlineStr">
+        <is>
+          <t>favicon.png найден, vite.svg отсутствует</t>
+        </is>
+      </c>
+      <c r="G126" s="23" t="inlineStr">
+        <is>
+          <t>favicon.png найден в HTML, vite.svg отсутствует.</t>
+        </is>
+      </c>
+      <c r="H126" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I126" s="22" t="inlineStr">
+        <is>
+          <t>T-151</t>
+        </is>
+      </c>
+      <c r="J126" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="50" customHeight="1" s="15">
+      <c r="A127" s="22" t="inlineStr">
+        <is>
+          <t>TC-122</t>
+        </is>
+      </c>
+      <c r="B127" s="22" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="C127" s="23" t="inlineStr">
+        <is>
+          <t>Login superadmin работает</t>
+        </is>
+      </c>
+      <c r="D127" s="23" t="inlineStr">
+        <is>
+          <t>test-стейджинг</t>
+        </is>
+      </c>
+      <c r="E127" s="22" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/auth/login с superadmin/Admin@12345\n2. Проверить HTTP 200\n3. Проверить наличие access_token в ответе</t>
+        </is>
+      </c>
+      <c r="F127" s="22" t="inlineStr">
+        <is>
+          <t>200, JSON с access_token</t>
+        </is>
+      </c>
+      <c r="G127" s="23" t="inlineStr">
+        <is>
+          <t>200, JSON с access_token (1399 символов), user object с roles=[SUPER_ADMIN], 38 permissions.</t>
+        </is>
+      </c>
+      <c r="H127" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I127" s="22" t="inlineStr">
+        <is>
+          <t>T-153</t>
+        </is>
+      </c>
+      <c r="J127" s="23" t="inlineStr">
+        <is>
+          <t>09.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="50" customHeight="1" s="15">
+      <c r="A128" s="22" t="inlineStr">
+        <is>
+          <t>TC-123</t>
+        </is>
+      </c>
+      <c r="B128" s="22" t="inlineStr">
+        <is>
+          <t>Timeline</t>
+        </is>
+      </c>
+      <c r="C128" s="23" t="inlineStr">
+        <is>
+          <t>Timeline - правильные данные за все часы дня (T-158 fix)</t>
+        </is>
+      </c>
+      <c r="D128" s="23" t="inlineStr">
+        <is>
+          <t>Деплой с фиксом T-158 на test. Пользователь air911d\shepaland имеет данные за 2026-03-09</t>
+        </is>
+      </c>
+      <c r="E128" s="22" t="inlineStr">
+        <is>
+          <t>1. Авторизоваться superadmin\n2. GET /users/timeline?date=2026-03-09&amp;timezone=Europe/Moscow&amp;tenant_id=...\n3. Проверить что hours содержат данные за все часы с активностью\n4. Проверить has_recording и recording_session_ids</t>
+        </is>
+      </c>
+      <c r="F128" s="22" t="inlineStr">
+        <is>
+          <t>Пользователи с focus intervals отображаются, hours содержат корректные данные за все часы дня</t>
+        </is>
+      </c>
+      <c r="G128" s="23" t="inlineStr">
+        <is>
+          <t>3 пользователя. T-158/T-160 fixes работают</t>
+        </is>
+      </c>
+      <c r="H128" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I128" s="22" t="inlineStr">
+        <is>
+          <t>T-158</t>
+        </is>
+      </c>
+      <c r="J128" s="23" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="50" customHeight="1" s="15">
+      <c r="A129" s="22" t="inlineStr">
+        <is>
+          <t>TC-124</t>
+        </is>
+      </c>
+      <c r="B129" s="22" t="inlineStr">
+        <is>
+          <t>Timeline</t>
+        </is>
+      </c>
+      <c r="C129" s="23" t="inlineStr">
+        <is>
+          <t>Timeline - пользователи без focus data отображаются (T-160 fix)</t>
+        </is>
+      </c>
+      <c r="D129" s="23" t="inlineStr">
+        <is>
+          <t>Деплой с фиксом T-160 на test. Тенант имеет пользователей в device_user_sessions</t>
+        </is>
+      </c>
+      <c r="E129" s="22" t="inlineStr">
+        <is>
+          <t>1. Авторизоваться superadmin\n2. GET /users/timeline?date=2025-01-01&amp;timezone=Europe/Moscow&amp;tenant_id=...\n3. Проверить что API возвращает пользователей даже без focus intervals</t>
+        </is>
+      </c>
+      <c r="F129" s="22" t="inlineStr">
+        <is>
+          <t>Пользователи из device_user_sessions отображаются с пустыми hours</t>
+        </is>
+      </c>
+      <c r="G129" s="23" t="inlineStr">
+        <is>
+          <t>3 пользователя за прошлую дату с 0 hours</t>
+        </is>
+      </c>
+      <c r="H129" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I129" s="22" t="inlineStr">
+        <is>
+          <t>T-160</t>
+        </is>
+      </c>
+      <c r="J129" s="23" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="50" customHeight="1" s="15">
+      <c r="A130" s="22" t="inlineStr">
+        <is>
+          <t>TC-125</t>
+        </is>
+      </c>
+      <c r="B130" s="22" t="inlineStr">
+        <is>
+          <t>Timeline</t>
+        </is>
+      </c>
+      <c r="C130" s="23" t="inlineStr">
+        <is>
+          <t>Timeline - данные за сегодня</t>
+        </is>
+      </c>
+      <c r="D130" s="23" t="inlineStr">
+        <is>
+          <t>Деплой с фиксом T-158 на test</t>
+        </is>
+      </c>
+      <c r="E130" s="22" t="inlineStr">
+        <is>
+          <t>1. Авторизоваться superadmin\n2. GET /users/timeline?date=2026-03-10&amp;timezone=Europe/Moscow&amp;tenant_id=...\n3. Проверить данные за текущий день</t>
+        </is>
+      </c>
+      <c r="F130" s="22" t="inlineStr">
+        <is>
+          <t>Возвращаются пользователи с данными за сегодня (если были focus intervals)</t>
+        </is>
+      </c>
+      <c r="G130" s="23" t="inlineStr">
+        <is>
+          <t>3 пользователя за сегодня с 0 hours</t>
+        </is>
+      </c>
+      <c r="H130" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I130" s="22" t="inlineStr">
+        <is>
+          <t>T-158</t>
+        </is>
+      </c>
+      <c r="J130" s="23" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="50" customHeight="1" s="15">
+      <c r="A131" s="22" t="inlineStr">
+        <is>
+          <t>TC-126</t>
+        </is>
+      </c>
+      <c r="B131" s="22" t="inlineStr">
+        <is>
+          <t>Timeline</t>
+        </is>
+      </c>
+      <c r="C131" s="23" t="inlineStr">
+        <is>
+          <t>Timeline - невалидная дата возвращает 400 (T-156 recheck)</t>
+        </is>
+      </c>
+      <c r="D131" s="23" t="inlineStr">
+        <is>
+          <t>Деплой на test</t>
+        </is>
+      </c>
+      <c r="E131" s="22" t="inlineStr">
+        <is>
+          <t>1. Авторизоваться superadmin\n2. GET /users/timeline?date=invalid\n3. Проверить HTTP код</t>
+        </is>
+      </c>
+      <c r="F131" s="22" t="inlineStr">
+        <is>
+          <t>HTTP 400 Bad Request</t>
+        </is>
+      </c>
+      <c r="G131" s="23" t="inlineStr">
+        <is>
+          <t>HTTP 400 с Invalid date format</t>
+        </is>
+      </c>
+      <c r="H131" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I131" s="22" t="inlineStr">
+        <is>
+          <t>T-158</t>
+        </is>
+      </c>
+      <c r="J131" s="23" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="50" customHeight="1" s="15">
+      <c r="A132" s="22" t="inlineStr">
+        <is>
+          <t>TC-127</t>
+        </is>
+      </c>
+      <c r="B132" s="22" t="inlineStr">
+        <is>
+          <t>Timeline</t>
+        </is>
+      </c>
+      <c r="C132" s="23" t="inlineStr">
+        <is>
+          <t>Timeline - timezone UTC vs Moscow сдвигает часы на +3</t>
+        </is>
+      </c>
+      <c r="D132" s="23" t="inlineStr">
+        <is>
+          <t>Деплой с фиксом T-158 на test. Данные за 2026-03-09</t>
+        </is>
+      </c>
+      <c r="E132" s="22" t="inlineStr">
+        <is>
+          <t>1. Авторизоваться superadmin\n2. GET /users/timeline?date=2026-03-09&amp;timezone=UTC\n3. GET /users/timeline?date=2026-03-09&amp;timezone=Europe/Moscow\n4. Сравнить часы с данными</t>
+        </is>
+      </c>
+      <c r="F132" s="22" t="inlineStr">
+        <is>
+          <t>Часы в Moscow timezone сдвинуты на +3 относительно UTC</t>
+        </is>
+      </c>
+      <c r="G132" s="23" t="inlineStr">
+        <is>
+          <t>UTC hours +3 = Moscow hours верно</t>
+        </is>
+      </c>
+      <c r="H132" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I132" s="22" t="inlineStr">
+        <is>
+          <t>T-158</t>
+        </is>
+      </c>
+      <c r="J132" s="23" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="50" customHeight="1" s="15">
+      <c r="A133" s="22" t="inlineStr">
+        <is>
+          <t>TC-128</t>
+        </is>
+      </c>
+      <c r="B133" s="22" t="inlineStr">
+        <is>
+          <t>Catalogs</t>
+        </is>
+      </c>
+      <c r="C133" s="23" t="inlineStr">
+        <is>
+          <t>Catalogs groups - регрессия после timeline фикса</t>
+        </is>
+      </c>
+      <c r="D133" s="23" t="inlineStr">
+        <is>
+          <t>Деплой на test</t>
+        </is>
+      </c>
+      <c r="E133" s="22" t="inlineStr">
+        <is>
+          <t>1. Авторизоваться superadmin\n2. GET /catalogs/groups?group_type=APP&amp;tenant_id=...\n3. Проверить HTTP 200 и структуру ответа</t>
+        </is>
+      </c>
+      <c r="F133" s="22" t="inlineStr">
+        <is>
+          <t>HTTP 200, массив групп</t>
+        </is>
+      </c>
+      <c r="G133" s="23" t="inlineStr">
+        <is>
+          <t>HTTP 200, 9 APP групп</t>
+        </is>
+      </c>
+      <c r="H133" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I133" s="22" t="inlineStr">
+        <is>
+          <t>T-158</t>
+        </is>
+      </c>
+      <c r="J133" s="23" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="50" customHeight="1" s="15">
+      <c r="A134" s="22" t="inlineStr">
+        <is>
+          <t>TC-129</t>
+        </is>
+      </c>
+      <c r="B134" s="22" t="inlineStr">
+        <is>
+          <t>Web Dashboard</t>
+        </is>
+      </c>
+      <c r="C134" s="23" t="inlineStr">
+        <is>
+          <t>SPA загружается, favicon корректный</t>
+        </is>
+      </c>
+      <c r="D134" s="23" t="inlineStr">
+        <is>
+          <t>Деплой на test</t>
+        </is>
+      </c>
+      <c r="E134" s="22" t="inlineStr">
+        <is>
+          <t>1. GET /screenrecorder/\n2. Проверить HTTP 200\n3. Проверить favicon в HTML</t>
+        </is>
+      </c>
+      <c r="F134" s="22" t="inlineStr">
+        <is>
+          <t>HTTP 200, favicon присутствует</t>
+        </is>
+      </c>
+      <c r="G134" s="23" t="inlineStr">
+        <is>
+          <t>HTTP 200, favicon.png, title Кадеро</t>
+        </is>
+      </c>
+      <c r="H134" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I134" s="22" t="inlineStr">
+        <is>
+          <t>T-151</t>
+        </is>
+      </c>
+      <c r="J134" s="23" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="50" customHeight="1" s="15">
+      <c r="A135" s="22" t="inlineStr">
+        <is>
+          <t>TC-130</t>
+        </is>
+      </c>
+      <c r="B135" s="22" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C135" s="23" t="inlineStr">
+        <is>
+          <t>Dashboard group-timeline возвращает данные за период</t>
+        </is>
+      </c>
+      <c r="D135" s="23" t="inlineStr">
+        <is>
+          <t>Есть focus_intervals за 3+ дней</t>
+        </is>
+      </c>
+      <c r="E135" s="22" t="inlineStr">
+        <is>
+          <t>1. GET /dashboard/group-timeline?group_type=APP&amp;from=...&amp;to=...\n2. Проверить наличие groups, days, breakdown</t>
+        </is>
+      </c>
+      <c r="F135" s="22" t="inlineStr">
+        <is>
+          <t>groups содержит список групп с group_id/group_name/color. days содержит записи с breakdown, ungrouped_duration_ms, ungrouped_percentage</t>
+        </is>
+      </c>
+      <c r="G135" s="23" t="inlineStr">
+        <is>
+          <t>API возвращает 8 групп, 2 дня с breakdown, ungrouped_duration_ms=30004/1919997, ungrouped_percentage=0.23%/2.1%. Проценты рассчитаны корректно.</t>
+        </is>
+      </c>
+      <c r="H135" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I135" s="22" t="inlineStr">
+        <is>
+          <t>T-161</t>
+        </is>
+      </c>
+      <c r="J135" s="23" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="50" customHeight="1" s="15">
+      <c r="A136" s="22" t="inlineStr">
+        <is>
+          <t>TC-131</t>
+        </is>
+      </c>
+      <c r="B136" s="22" t="inlineStr">
+        <is>
+          <t>Timeline</t>
+        </is>
+      </c>
+      <c r="C136" s="23" t="inlineStr">
+        <is>
+          <t>Timeline has_recording корреляция с recording_sessions</t>
+        </is>
+      </c>
+      <c r="D136" s="23" t="inlineStr">
+        <is>
+          <t>Есть focus_intervals и recording_sessions за один день</t>
+        </is>
+      </c>
+      <c r="E136" s="22" t="inlineStr">
+        <is>
+          <t>1. GET /users/timeline?date=...\n2. Проверить has_recording для часов где есть сессии\n3. Проверить recording_session_ids</t>
+        </is>
+      </c>
+      <c r="F136" s="22" t="inlineStr">
+        <is>
+          <t>has_recording=true для часов с пересекающимися recording_sessions, recording_session_ids заполнены</t>
+        </is>
+      </c>
+      <c r="G136" s="23" t="inlineStr">
+        <is>
+          <t>has_recording=true для часов 0,10,11,12 (user AIR911D\ashep). recording_session_ids: 1,3,1,2 сессии. has_recording=false для часов 13,14 (нет записей).</t>
+        </is>
+      </c>
+      <c r="H136" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I136" s="22" t="inlineStr">
+        <is>
+          <t>T-162</t>
+        </is>
+      </c>
+      <c r="J136" s="23" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="50" customHeight="1" s="15">
+      <c r="A137" s="20" t="inlineStr">
+        <is>
+          <t>TC-132</t>
+        </is>
+      </c>
+      <c r="B137" s="20" t="inlineStr">
+        <is>
+          <t>Timeline</t>
+        </is>
+      </c>
+      <c r="C137" s="21" t="inlineStr">
+        <is>
+          <t>Timeline UI: видимые bars для групп и отдельных приложений</t>
+        </is>
+      </c>
+      <c r="D137" s="21" t="inlineStr">
+        <is>
+          <t>Есть focus_intervals с app_groups</t>
+        </is>
+      </c>
+      <c r="E137" s="20" t="inlineStr">
+        <is>
+          <t>1. Открыть страницу Аналитика &gt; Пользователи\n2. Развернуть пользователя\n3. Проверить наличие цветных баров для групп\n4. Развернуть группу — проверить бары для отдельных приложений</t>
+        </is>
+      </c>
+      <c r="F137" s="20" t="inlineStr">
+        <is>
+          <t>Группы отображаются цветными барами по часам. Отдельные приложения также отображают бары при раскрытии</t>
+        </is>
+      </c>
+      <c r="G137" s="21" t="inlineStr"/>
+      <c r="H137" s="20" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="I137" s="20" t="inlineStr">
+        <is>
+          <t>T-163</t>
+        </is>
+      </c>
+      <c r="J137" s="21" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
         </is>
       </c>
     </row>

--- a/docs/tracker.xlsx
+++ b/docs/tracker.xlsx
@@ -610,7 +610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I168"/>
+  <dimension ref="A1:I172"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="15" min="1" max="1"/>
@@ -8371,6 +8371,194 @@
         </is>
       </c>
     </row>
+    <row r="169" ht="20" customHeight="1" s="15">
+      <c r="A169" s="18" t="inlineStr">
+        <is>
+          <t>T-164</t>
+        </is>
+      </c>
+      <c r="B169" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C169" s="19" t="inlineStr">
+        <is>
+          <t>Справочники: вынести в отдельный пункт меню</t>
+        </is>
+      </c>
+      <c r="D169" s="19" t="inlineStr">
+        <is>
+          <t>Создать отдельный collapsible пункт основного меню Справочники между Аналитика и Настройки. Убрать Группы приложений и Группы сайтов из tenantSettingsSubmenu и superAdminSettingsSubmenu. Добавить isCatalogsExpanded state, isCatalogsActive, catalogsSubmenu. Файл: web-dashboard/src/components/Sidebar.tsx</t>
+        </is>
+      </c>
+      <c r="E169" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F169" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G169" s="19" t="inlineStr">
+        <is>
+          <t>Разработчик</t>
+        </is>
+      </c>
+      <c r="H169" s="18" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+      <c r="I169" s="18" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="20" customHeight="1" s="15">
+      <c r="A170" s="24" t="inlineStr">
+        <is>
+          <t>T-165</t>
+        </is>
+      </c>
+      <c r="B170" s="24" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="C170" s="25" t="inlineStr">
+        <is>
+          <t>Tooltip дашборда: широкие строки и неверная сортировка групп</t>
+        </is>
+      </c>
+      <c r="D170" s="25" t="inlineStr">
+        <is>
+          <t>В GroupTimelineChart.tsx tooltip показывает группы в порядке sort_order (не по проценту) и с большим межстрочным интервалом. Нужен CustomTooltip компонент: сортировка payload по value desc + itemStyle padding 1px. Файл: web-dashboard/src/components/dashboard/GroupTimelineChart.tsx</t>
+        </is>
+      </c>
+      <c r="E170" s="24" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F170" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G170" s="25" t="inlineStr">
+        <is>
+          <t>Разработчик</t>
+        </is>
+      </c>
+      <c r="H170" s="24" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+      <c r="I170" s="24" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="20" customHeight="1" s="15">
+      <c r="A171" s="24" t="inlineStr">
+        <is>
+          <t>T-166</t>
+        </is>
+      </c>
+      <c r="B171" s="24" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="C171" s="25" t="inlineStr">
+        <is>
+          <t>Timeline: группа Браузеры не показывает Группы сайтов</t>
+        </is>
+      </c>
+      <c r="D171" s="25" t="inlineStr">
+        <is>
+          <t>Корневая причина: в TimelineService группа Браузеры создаётся хардкодом с groupId=null и is_browser_group=true, но связи с конкретными APP-группами из БД нет. Если агент присылает browser-интервалы без домена (domain=null) — siteGroupMap пустой. Решение: добавить поле is_browser_group в app_groups (V32 миграция), использовать флаг из БД в TimelineService вместо хардкода. Затронутые файлы: V32__app_group_browser_flag.sql (новый), AppGroup.java, TimelineService.java, GroupCreateRequest.java, GroupUpdateRequest.java, GroupResponse.java, catalogs.ts, AppGroupsPage.tsx</t>
+        </is>
+      </c>
+      <c r="E171" s="24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F171" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G171" s="25" t="inlineStr">
+        <is>
+          <t>Разработчик</t>
+        </is>
+      </c>
+      <c r="H171" s="24" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+      <c r="I171" s="24" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="20" customHeight="1" s="15">
+      <c r="A172" s="18" t="inlineStr">
+        <is>
+          <t>T-167</t>
+        </is>
+      </c>
+      <c r="B172" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C172" s="19" t="inlineStr">
+        <is>
+          <t>recording_enabled toggle на device registration tokens</t>
+        </is>
+      </c>
+      <c r="D172" s="19" t="inlineStr">
+        <is>
+          <t>Фича: включение/отключение записи через toggle на registration token. V34 миграция, PATCH endpoint, каскад на device.settings, UI toggle, agent guards.</t>
+        </is>
+      </c>
+      <c r="E172" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F172" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G172" s="19" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="H172" s="18" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+      <c r="I172" s="18" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
@@ -8385,7 +8573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J137"/>
+  <dimension ref="A1:J149"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="15" min="1" max="1"/>
@@ -15324,6 +15512,630 @@
         </is>
       </c>
       <c r="J137" s="21" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="50" customHeight="1" s="15">
+      <c r="A138" s="22" t="inlineStr">
+        <is>
+          <t>TC-133</t>
+        </is>
+      </c>
+      <c r="B138" s="22" t="inlineStr">
+        <is>
+          <t>Device Tokens</t>
+        </is>
+      </c>
+      <c r="C138" s="23" t="inlineStr">
+        <is>
+          <t>POST token с recording_enabled=true</t>
+        </is>
+      </c>
+      <c r="D138" s="23" t="inlineStr">
+        <is>
+          <t>Авторизован как superadmin</t>
+        </is>
+      </c>
+      <c r="E138" s="22" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/device-tokens с recording_enabled=true\n2. Проверить ответ</t>
+        </is>
+      </c>
+      <c r="F138" s="22" t="inlineStr">
+        <is>
+          <t>201, recording_enabled=true</t>
+        </is>
+      </c>
+      <c r="G138" s="23" t="inlineStr">
+        <is>
+          <t>Проверено после редеплоя 10.03.2026</t>
+        </is>
+      </c>
+      <c r="H138" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I138" s="22" t="inlineStr">
+        <is>
+          <t>T-167</t>
+        </is>
+      </c>
+      <c r="J138" s="23" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="50" customHeight="1" s="15">
+      <c r="A139" s="22" t="inlineStr">
+        <is>
+          <t>TC-134</t>
+        </is>
+      </c>
+      <c r="B139" s="22" t="inlineStr">
+        <is>
+          <t>Device Tokens</t>
+        </is>
+      </c>
+      <c r="C139" s="23" t="inlineStr">
+        <is>
+          <t>POST token с recording_enabled=false</t>
+        </is>
+      </c>
+      <c r="D139" s="23" t="inlineStr">
+        <is>
+          <t>Авторизован как superadmin</t>
+        </is>
+      </c>
+      <c r="E139" s="22" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/device-tokens с recording_enabled=false\n2. Проверить ответ</t>
+        </is>
+      </c>
+      <c r="F139" s="22" t="inlineStr">
+        <is>
+          <t>201, recording_enabled=false</t>
+        </is>
+      </c>
+      <c r="G139" s="23" t="inlineStr">
+        <is>
+          <t>Проверено после редеплоя 10.03.2026</t>
+        </is>
+      </c>
+      <c r="H139" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I139" s="22" t="inlineStr">
+        <is>
+          <t>T-167</t>
+        </is>
+      </c>
+      <c r="J139" s="23" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="50" customHeight="1" s="15">
+      <c r="A140" s="22" t="inlineStr">
+        <is>
+          <t>TC-135</t>
+        </is>
+      </c>
+      <c r="B140" s="22" t="inlineStr">
+        <is>
+          <t>Device Tokens</t>
+        </is>
+      </c>
+      <c r="C140" s="23" t="inlineStr">
+        <is>
+          <t>POST token без recording_enabled (default=true)</t>
+        </is>
+      </c>
+      <c r="D140" s="23" t="inlineStr">
+        <is>
+          <t>Авторизован как superadmin</t>
+        </is>
+      </c>
+      <c r="E140" s="22" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/device-tokens без recording_enabled\n2. Проверить ответ</t>
+        </is>
+      </c>
+      <c r="F140" s="22" t="inlineStr">
+        <is>
+          <t>201, recording_enabled=true (default)</t>
+        </is>
+      </c>
+      <c r="G140" s="23" t="inlineStr">
+        <is>
+          <t>Проверено после редеплоя 10.03.2026</t>
+        </is>
+      </c>
+      <c r="H140" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I140" s="22" t="inlineStr">
+        <is>
+          <t>T-167</t>
+        </is>
+      </c>
+      <c r="J140" s="23" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="50" customHeight="1" s="15">
+      <c r="A141" s="22" t="inlineStr">
+        <is>
+          <t>TC-136</t>
+        </is>
+      </c>
+      <c r="B141" s="22" t="inlineStr">
+        <is>
+          <t>Device Tokens</t>
+        </is>
+      </c>
+      <c r="C141" s="23" t="inlineStr">
+        <is>
+          <t>PATCH recording_enabled=false</t>
+        </is>
+      </c>
+      <c r="D141" s="23" t="inlineStr">
+        <is>
+          <t>Авторизован как superadmin, токен существует</t>
+        </is>
+      </c>
+      <c r="E141" s="22" t="inlineStr">
+        <is>
+          <t>1. PATCH /api/v1/device-tokens/{id} с recording_enabled=false\n2. Проверить ответ</t>
+        </is>
+      </c>
+      <c r="F141" s="22" t="inlineStr">
+        <is>
+          <t>200, recording_enabled=false</t>
+        </is>
+      </c>
+      <c r="G141" s="23" t="inlineStr">
+        <is>
+          <t>Проверено после редеплоя 10.03.2026</t>
+        </is>
+      </c>
+      <c r="H141" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I141" s="22" t="inlineStr">
+        <is>
+          <t>T-167</t>
+        </is>
+      </c>
+      <c r="J141" s="23" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="50" customHeight="1" s="15">
+      <c r="A142" s="22" t="inlineStr">
+        <is>
+          <t>TC-137</t>
+        </is>
+      </c>
+      <c r="B142" s="22" t="inlineStr">
+        <is>
+          <t>Device Tokens</t>
+        </is>
+      </c>
+      <c r="C142" s="23" t="inlineStr">
+        <is>
+          <t>PATCH recording_enabled=true</t>
+        </is>
+      </c>
+      <c r="D142" s="23" t="inlineStr">
+        <is>
+          <t>Авторизован как superadmin, токен с recording_enabled=false</t>
+        </is>
+      </c>
+      <c r="E142" s="22" t="inlineStr">
+        <is>
+          <t>1. PATCH /api/v1/device-tokens/{id} с recording_enabled=true\n2. Проверить ответ</t>
+        </is>
+      </c>
+      <c r="F142" s="22" t="inlineStr">
+        <is>
+          <t>200, recording_enabled=true</t>
+        </is>
+      </c>
+      <c r="G142" s="23" t="inlineStr">
+        <is>
+          <t>Проверено после редеплоя 10.03.2026</t>
+        </is>
+      </c>
+      <c r="H142" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I142" s="22" t="inlineStr">
+        <is>
+          <t>T-167</t>
+        </is>
+      </c>
+      <c r="J142" s="23" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="50" customHeight="1" s="15">
+      <c r="A143" s="22" t="inlineStr">
+        <is>
+          <t>TC-138</t>
+        </is>
+      </c>
+      <c r="B143" s="22" t="inlineStr">
+        <is>
+          <t>Device Tokens</t>
+        </is>
+      </c>
+      <c r="C143" s="23" t="inlineStr">
+        <is>
+          <t>PATCH name на token</t>
+        </is>
+      </c>
+      <c r="D143" s="23" t="inlineStr">
+        <is>
+          <t>Авторизован как superadmin, токен существует</t>
+        </is>
+      </c>
+      <c r="E143" s="22" t="inlineStr">
+        <is>
+          <t>1. PATCH /api/v1/device-tokens/{id} с name=new-name\n2. Проверить ответ</t>
+        </is>
+      </c>
+      <c r="F143" s="22" t="inlineStr">
+        <is>
+          <t>200, name обновлено</t>
+        </is>
+      </c>
+      <c r="G143" s="23" t="inlineStr">
+        <is>
+          <t>Проверено после редеплоя 10.03.2026</t>
+        </is>
+      </c>
+      <c r="H143" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I143" s="22" t="inlineStr">
+        <is>
+          <t>T-167</t>
+        </is>
+      </c>
+      <c r="J143" s="23" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="50" customHeight="1" s="15">
+      <c r="A144" s="22" t="inlineStr">
+        <is>
+          <t>TC-139</t>
+        </is>
+      </c>
+      <c r="B144" s="22" t="inlineStr">
+        <is>
+          <t>Device Tokens</t>
+        </is>
+      </c>
+      <c r="C144" s="23" t="inlineStr">
+        <is>
+          <t>PATCH max_uses на token</t>
+        </is>
+      </c>
+      <c r="D144" s="23" t="inlineStr">
+        <is>
+          <t>Авторизован как superadmin, токен существует</t>
+        </is>
+      </c>
+      <c r="E144" s="22" t="inlineStr">
+        <is>
+          <t>1. PATCH /api/v1/device-tokens/{id} с max_uses=99\n2. Проверить ответ</t>
+        </is>
+      </c>
+      <c r="F144" s="22" t="inlineStr">
+        <is>
+          <t>200, max_uses=99</t>
+        </is>
+      </c>
+      <c r="G144" s="23" t="inlineStr">
+        <is>
+          <t>Проверено после редеплоя 10.03.2026</t>
+        </is>
+      </c>
+      <c r="H144" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I144" s="22" t="inlineStr">
+        <is>
+          <t>T-167</t>
+        </is>
+      </c>
+      <c r="J144" s="23" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="50" customHeight="1" s="15">
+      <c r="A145" s="22" t="inlineStr">
+        <is>
+          <t>TC-140</t>
+        </is>
+      </c>
+      <c r="B145" s="22" t="inlineStr">
+        <is>
+          <t>Device Tokens</t>
+        </is>
+      </c>
+      <c r="C145" s="23" t="inlineStr">
+        <is>
+          <t>PATCH cross-tenant isolation</t>
+        </is>
+      </c>
+      <c r="D145" s="23" t="inlineStr">
+        <is>
+          <t>Авторизован как test user (tenant test-org)</t>
+        </is>
+      </c>
+      <c r="E145" s="22" t="inlineStr">
+        <is>
+          <t>1. PATCH /api/v1/device-tokens/{id} токена из другого тенанта\n2. Проверить ответ</t>
+        </is>
+      </c>
+      <c r="F145" s="22" t="inlineStr">
+        <is>
+          <t>404 (tenant isolation)</t>
+        </is>
+      </c>
+      <c r="G145" s="23" t="inlineStr">
+        <is>
+          <t>Проверено после редеплоя 10.03.2026</t>
+        </is>
+      </c>
+      <c r="H145" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I145" s="22" t="inlineStr">
+        <is>
+          <t>T-167</t>
+        </is>
+      </c>
+      <c r="J145" s="23" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="50" customHeight="1" s="15">
+      <c r="A146" s="22" t="inlineStr">
+        <is>
+          <t>TC-141</t>
+        </is>
+      </c>
+      <c r="B146" s="22" t="inlineStr">
+        <is>
+          <t>Device Tokens</t>
+        </is>
+      </c>
+      <c r="C146" s="23" t="inlineStr">
+        <is>
+          <t>PATCH несуществующий токен</t>
+        </is>
+      </c>
+      <c r="D146" s="23" t="inlineStr">
+        <is>
+          <t>Авторизован как superadmin</t>
+        </is>
+      </c>
+      <c r="E146" s="22" t="inlineStr">
+        <is>
+          <t>1. PATCH /api/v1/device-tokens/{random-uuid}\n2. Проверить ответ</t>
+        </is>
+      </c>
+      <c r="F146" s="22" t="inlineStr">
+        <is>
+          <t>404 Not Found</t>
+        </is>
+      </c>
+      <c r="G146" s="23" t="inlineStr">
+        <is>
+          <t>Проверено после редеплоя 10.03.2026</t>
+        </is>
+      </c>
+      <c r="H146" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I146" s="22" t="inlineStr">
+        <is>
+          <t>T-167</t>
+        </is>
+      </c>
+      <c r="J146" s="23" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="50" customHeight="1" s="15">
+      <c r="A147" s="22" t="inlineStr">
+        <is>
+          <t>TC-142</t>
+        </is>
+      </c>
+      <c r="B147" s="22" t="inlineStr">
+        <is>
+          <t>Device Tokens</t>
+        </is>
+      </c>
+      <c r="C147" s="23" t="inlineStr">
+        <is>
+          <t>Device-login server_config содержит recording_enabled</t>
+        </is>
+      </c>
+      <c r="D147" s="23" t="inlineStr">
+        <is>
+          <t>Registration token существует, активен</t>
+        </is>
+      </c>
+      <c r="E147" s="22" t="inlineStr">
+        <is>
+          <t>1. POST /api/v1/auth/device-login\n2. Проверить server_config</t>
+        </is>
+      </c>
+      <c r="F147" s="22" t="inlineStr">
+        <is>
+          <t>server_config.recording_enabled=true/false</t>
+        </is>
+      </c>
+      <c r="G147" s="23" t="inlineStr">
+        <is>
+          <t>Проверено после редеплоя 10.03.2026</t>
+        </is>
+      </c>
+      <c r="H147" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I147" s="22" t="inlineStr">
+        <is>
+          <t>T-167</t>
+        </is>
+      </c>
+      <c r="J147" s="23" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="50" customHeight="1" s="15">
+      <c r="A148" s="22" t="inlineStr">
+        <is>
+          <t>TC-143</t>
+        </is>
+      </c>
+      <c r="B148" s="22" t="inlineStr">
+        <is>
+          <t>Device Tokens</t>
+        </is>
+      </c>
+      <c r="C148" s="23" t="inlineStr">
+        <is>
+          <t>Audit log при PATCH recording_enabled</t>
+        </is>
+      </c>
+      <c r="D148" s="23" t="inlineStr">
+        <is>
+          <t>Авторизован как superadmin</t>
+        </is>
+      </c>
+      <c r="E148" s="22" t="inlineStr">
+        <is>
+          <t>1. PATCH recording_enabled\n2. Проверить audit log в БД</t>
+        </is>
+      </c>
+      <c r="F148" s="22" t="inlineStr">
+        <is>
+          <t>action=DEVICE_TOKEN_UPDATED записано</t>
+        </is>
+      </c>
+      <c r="G148" s="23" t="inlineStr">
+        <is>
+          <t>Проверено после редеплоя 10.03.2026</t>
+        </is>
+      </c>
+      <c r="H148" s="22" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I148" s="22" t="inlineStr">
+        <is>
+          <t>T-167</t>
+        </is>
+      </c>
+      <c r="J148" s="23" t="inlineStr">
+        <is>
+          <t>10.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="50" customHeight="1" s="15">
+      <c r="A149" s="20" t="inlineStr">
+        <is>
+          <t>TC-144</t>
+        </is>
+      </c>
+      <c r="B149" s="20" t="inlineStr">
+        <is>
+          <t>Device Tokens</t>
+        </is>
+      </c>
+      <c r="C149" s="21" t="inlineStr">
+        <is>
+          <t>UI toggle recording_enabled в списке токенов</t>
+        </is>
+      </c>
+      <c r="D149" s="21" t="inlineStr">
+        <is>
+          <t>Авторизован в web-dashboard</t>
+        </is>
+      </c>
+      <c r="E149" s="20" t="inlineStr">
+        <is>
+          <t>1. Открыть Настройки → Токены\n2. Переключить toggle Запись\n3. Обновить страницу</t>
+        </is>
+      </c>
+      <c r="F149" s="20" t="inlineStr">
+        <is>
+          <t>Toggle переключается, значение сохраняется</t>
+        </is>
+      </c>
+      <c r="G149" s="21" t="inlineStr">
+        <is>
+          <t>Ожидает ручной проверки в UI</t>
+        </is>
+      </c>
+      <c r="H149" s="20" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="I149" s="20" t="inlineStr">
+        <is>
+          <t>T-167</t>
+        </is>
+      </c>
+      <c r="J149" s="21" t="inlineStr">
         <is>
           <t>10.03.2026</t>
         </is>

--- a/docs/tracker.xlsx
+++ b/docs/tracker.xlsx
@@ -610,7 +610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I172"/>
+  <dimension ref="A1:I179"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="15" min="1" max="1"/>
@@ -8556,6 +8556,423 @@
       <c r="I172" s="18" t="inlineStr">
         <is>
           <t>10.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="20" customHeight="1" s="15">
+      <c r="A173" s="18" t="inlineStr">
+        <is>
+          <t>T-168</t>
+        </is>
+      </c>
+      <c r="B173" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C173" s="19" t="inlineStr">
+        <is>
+          <t>Мелкие доработки: DownloadPage ссылки, порядок меню Аналитика, очистка сессий</t>
+        </is>
+      </c>
+      <c r="D173" s="19" t="inlineStr">
+        <is>
+          <t>1) DownloadPage: ссылки 'Токены регистрации' и 'Устройства' вели на 404 — заменены &lt;a&gt; на &lt;Link&gt; из react-router-dom для корректной работы с basename.
+2) Sidebar: порядок пунктов в меню Аналитика изменён на: Таймлайны, Сотрудники, Устройства, Поиск записей, Аудит поведения.
+3) Очистка БД test: удалены 34 сессии (ended_ts &lt; 2026-03-18 14:57) и 758 связанных сегментов из recording_sessions и segments.</t>
+        </is>
+      </c>
+      <c r="E173" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F173" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G173" s="19" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="H173" s="18" t="inlineStr">
+        <is>
+          <t>18.03.2026</t>
+        </is>
+      </c>
+      <c r="I173" s="18" t="inlineStr">
+        <is>
+          <t>18.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="20" customHeight="1" s="15">
+      <c r="A174" s="18" t="inlineStr">
+        <is>
+          <t>T-169</t>
+        </is>
+      </c>
+      <c r="B174" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C174" s="19" t="inlineStr">
+        <is>
+          <t>Deploy web-dashboard на test: DownloadPage Link + Sidebar order</t>
+        </is>
+      </c>
+      <c r="D174" s="19" t="inlineStr">
+        <is>
+          <t>Деплой web-dashboard на test-стейджинг. Изменения: DownloadPage — замена &lt;a&gt; на &lt;Link&gt; для корректной работы с basename; порядок меню Аналитика изменён в Sidebar.tsx.</t>
+        </is>
+      </c>
+      <c r="E174" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F174" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G174" s="19" t="inlineStr">
+        <is>
+          <t>DevOps</t>
+        </is>
+      </c>
+      <c r="H174" s="18" t="inlineStr">
+        <is>
+          <t>18.03.2026</t>
+        </is>
+      </c>
+      <c r="I174" s="18" t="inlineStr">
+        <is>
+          <t>18.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="20" customHeight="1" s="15">
+      <c r="A175" s="18" t="inlineStr">
+        <is>
+          <t>T-170</t>
+        </is>
+      </c>
+      <c r="B175" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C175" s="19" t="inlineStr">
+        <is>
+          <t>Страница скачивания дистрибутива: внешний FTP + рабочая ссылка</t>
+        </is>
+      </c>
+      <c r="D175" s="19" t="inlineStr">
+        <is>
+          <t>Анализ (19.03.2026):
+ТЕКУЩЕЕ СОСТОЯНИЕ:
+- DownloadPage.tsx существует (web-dashboard/src/pages/DownloadPage.tsx), ссылка на /downloads/KaderoAgentSetup.exe
+- Sidebar содержит ссылку 'Скачать клиент' → /download (доступна всем аутентифицированным)
+- Маршрут /download определён в App.tsx (без permission gate)
+- НО: директории downloads/ нет в public/, nginx не настроен на раздачу файлов из /downloads/
+- Инсталлятор (~95МБ) лежит на Windows-машине 192.168.1.135 в C:\kadero_install\KaderoAgentSetup.exe
+ЧТО НУЖНО СДЕЛАТЬ:
+1. Перенос дистрибутива:
+   - Скачать KaderoAgentSetup.exe с Windows-машины 192.168.1.135
+   - Загрузить на внешний FTP 31.31.197.15 (u3441292/24Pd3XwQj2z7ATSS) в директорию distrib/
+   - Удалить старый файл в distrib/ перед загрузкой нового
+2. Изменить DownloadPage.tsx:
+   - Заменить href="/downloads/KaderoAgentSetup.exe" на прямую ссылку на FTP (или HTTP URL внешнего хостинга)
+   - Обновить версию и размер файла на актуальные
+   - Учесть base path /screenrecorder/ при формировании URL
+3. Альтернативный вариант (если FTP не отдаёт по HTTP):
+   - Настроить nginx reverse-proxy или redirect на внешний URL
+   - Или добавить location /downloads/ в nginx.conf с proxy_pass на FTP/HTTP URL
+КЛЮЧЕВЫЕ ФАЙЛЫ:
+- web-dashboard/src/pages/DownloadPage.tsx (строка 26 — href)
+- deploy/docker/web-dashboard/nginx.conf (добавить location если нужен proxy)
+- web-dashboard/vite.config.ts (base: /screenrecorder/)
+FTP ДОСТУП (внешний):
+- IP: 31.31.197.15, логин: u3441292, пароль: 24Pd3XwQj2z7ATSS
+- Директория: distrib/</t>
+        </is>
+      </c>
+      <c r="E175" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F175" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G175" s="19" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="H175" s="18" t="inlineStr">
+        <is>
+          <t>19.03.2026</t>
+        </is>
+      </c>
+      <c r="I175" s="18" t="inlineStr">
+        <is>
+          <t>19.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="20" customHeight="1" s="15">
+      <c r="A176" s="18" t="inlineStr">
+        <is>
+          <t>T-171</t>
+        </is>
+      </c>
+      <c r="B176" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C176" s="19" t="inlineStr">
+        <is>
+          <t>Агент: полная работоспособность без запуска UI (TrayApp)</t>
+        </is>
+      </c>
+      <c r="D176" s="19" t="inlineStr">
+        <is>
+          <t>Анализ (19.03.2026):
+ТЕКУЩАЯ АРХИТЕКТУРА:
+Агент имеет двойную стратегию: Service (Session 0, SYSTEM) + TrayApp (интерактивная сессия пользователя).
+Связь через Named Pipe 'KaderoAgent'. TrayApp запускается отдельно с флагом --tray.
+БЕЗ TRAY РАБОТАЕТ:
+✓ Основная запись видео (ScreenCaptureManager)
+✓ Heartbeat и sync (HeartbeatService, DataSyncService)
+✓ Загрузка сегментов (SegmentUploader)
+✓ Команды от сервера (CommandHandler)
+БЕЗ TRAY НЕ РАБОТАЕТ / РАБОТАЕТ НЕКОРРЕКТНО:
+✗ Focus Intervals — ActiveWindowTracker (fallback в Session 0) вызывает GetForegroundWindow(), но в Session 0 результат некорректен (всегда 0 или неправильный hwnd). Данные о фокусе окна будут пустыми или ошибочными.
+✗ Input Events — InputTracker использует низкоуровневые hooks (WH_MOUSE_LL, WH_KEYBOARD_LL), которые работают ТОЛЬКО в интерактивной UI-сессии. Без трея input events не собираются вообще.
+✗ UI статус — пользователь не видит состояние агента (не критично для функциональности).
+КОРНЕВАЯ ПРИЧИНА:
+Windows Service работает в Session 0 (изолированная сессия SYSTEM). API GetForegroundWindow() и SetWindowsHookEx() для low-level hooks требуют интерактивной desktop-сессии пользователя.
+ВАРИАНТЫ РЕШЕНИЯ:
+Вариант A — Автозапуск TrayApp (рекомендуемый):
+- Service при старте/при обнаружении залогиненного пользователя автоматически запускает TrayApp в сессии пользователя
+- Использовать CreateProcessAsUser() или WTSEnumerateSessions() + CreateProcessInSession()
+- TrayApp может работать скрыто (без иконки в трее) если пользователь не хочет UI
+- Флаг --tray --hidden для скрытого режима
+- Плюсы: минимальные изменения архитектуры, все существующие механизмы продолжают работать
+- Минусы: требует привилегий SERVICE для запуска процесса в пользовательской сессии
+Вариант B — Background helper process:
+- Вместо полноценного TrayApp создать лёгкий фоновый процесс без UI
+- Запускается как Scheduled Task при логине пользователя (Task Scheduler)
+- Содержит только: TrayWindowTracker + InputTracker + PipeClient
+- Без иконки в трее, без окон, чисто headless
+- Плюсы: не требует привилегий SERVICE, автостарт через Task Scheduler
+- Минусы: нужен отдельный бинарник или --headless режим
+Вариант C — Session 0 workaround (сложный):
+- Использовать UI Automation API или ETW (Event Tracing for Windows) из Session 0
+- Для фокуса: подписка на EVENT_SYSTEM_FOREGROUND через SetWinEventHook в каждой пользовательской сессии
+- Для input: использовать Raw Input API с RIDEV_INPUTSINK
+- Плюсы: всё в одном процессе
+- Минусы: сложная реализация, потенциальные проблемы с безопасностью
+РЕКОМЕНДАЦИЯ: Вариант B — создать --headless режим для KaderoAgent.exe:
+1. При --headless: запускать TrayWindowTracker + InputTracker + PipeClient БЕЗ UI
+2. Регистрировать Task Scheduler задачу при установке (Inno Setup) — запуск при логине любого пользователя
+3. Service обнаруживает headless-процесс через Named Pipe как обычно
+КЛЮЧЕВЫЕ ФАЙЛЫ:
+- windows-agent-csharp/src/KaderoAgent/Program.cs (строки 97-123 — tray mode)
+- windows-agent-csharp/src/KaderoAgent/Tray/TrayApplication.cs (конструктор, Start, Dispose)
+- windows-agent-csharp/src/KaderoAgent/Tray/TrayWindowTracker.cs (447 строк — polling + pipe send)
+- windows-agent-csharp/src/KaderoAgent/Tray/InputTracker.cs (456 строк — hooks)
+- windows-agent-csharp/src/KaderoAgent/Audit/ActiveWindowTracker.cs (fallback в Session 0)
+- windows-agent-csharp/src/KaderoAgent/Ipc/PipeServer.cs (обработка focus intervals от tray)
+- windows-agent-csharp/src/KaderoAgent/Ipc/PipeClient.cs (клиент для связи с service)</t>
+        </is>
+      </c>
+      <c r="E176" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F176" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G176" s="19" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="H176" s="18" t="inlineStr">
+        <is>
+          <t>19.03.2026</t>
+        </is>
+      </c>
+      <c r="I176" s="18" t="inlineStr">
+        <is>
+          <t>19.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="20" customHeight="1" s="15">
+      <c r="A177" s="18" t="inlineStr">
+        <is>
+          <t>T-172</t>
+        </is>
+      </c>
+      <c r="B177" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C177" s="19" t="inlineStr">
+        <is>
+          <t>Upload Redesign: интеграционное тестирование (Фаза 6+7)</t>
+        </is>
+      </c>
+      <c r="D177" s="19" t="inlineStr">
+        <is>
+          <t>Код полностью реализован (Фазы 1-5). Агент v2 собран (2026.3.19.1), инсталлятор на kadero.ru и C:\kadero_install\.
+Требуется:
+1. Установить агент v2 на AIR911D через RDP
+2. Провести интеграционное тестирование (Фаза 6):
+   - Happy path 5 мин
+   - Offline 2 мин + recovery
+   - Crash recovery (kill -9)
+   - Throttling (upload_enabled=false)
+   - Round-robin баланс
+   - Idempotent confirm
+   - Clipboard hash
+   - Retention 72ч
+   - Disk pressure
+3. Деплой на prod после прохождения тестов
+Подробный чеклист: docs/задачи/agent-upload-redesign-checklist.md</t>
+        </is>
+      </c>
+      <c r="E177" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F177" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G177" s="19" t="inlineStr">
+        <is>
+          <t>Алексей</t>
+        </is>
+      </c>
+      <c r="H177" s="18" t="inlineStr">
+        <is>
+          <t>19.03.2026</t>
+        </is>
+      </c>
+      <c r="I177" s="18" t="inlineStr">
+        <is>
+          <t>19.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="20" customHeight="1" s="15">
+      <c r="A178" s="24" t="inlineStr">
+        <is>
+          <t>T-173</t>
+        </is>
+      </c>
+      <c r="B178" s="24" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="C178" s="25" t="inlineStr">
+        <is>
+          <t>State machine: Онлайн вместо Запись + оптимизация до промышленного уровня</t>
+        </is>
+      </c>
+      <c r="D178" s="25" t="inlineStr">
+        <is>
+          <t>После обновления агента v2026.3.19.1 на AIR911D: FFmpeg crash (gdigrab error 5 — нет desktop при отключённом RDP), retry fail, state recording→online, нет повторных auto-start. Saved ServerConfig имеет AutoStart=false при рестарте. Аналитика: docs/задачи/T-173-устройство-показывает-онлайн-вместо-записи.md</t>
+        </is>
+      </c>
+      <c r="E178" s="24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F178" s="24" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="G178" s="25" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="H178" s="24" t="inlineStr">
+        <is>
+          <t>19.03.2026</t>
+        </is>
+      </c>
+      <c r="I178" s="24" t="inlineStr">
+        <is>
+          <t>20.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="20" customHeight="1" s="15">
+      <c r="A179" s="24" t="inlineStr">
+        <is>
+          <t>T-174</t>
+        </is>
+      </c>
+      <c r="B179" s="24" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="C179" s="25" t="inlineStr">
+        <is>
+          <t>Нет таймлайнов и activity-событий после обновления агента</t>
+        </is>
+      </c>
+      <c r="D179" s="25" t="inlineStr">
+        <is>
+          <t>HeadlessApplication (--headless) не запущен: HKCU\Run срабатывает только при логине, но пользователь не перелогинивался. ActiveWindowTracker не зарегистрирован в DI. Focus intervals и input events = 0 после обновления. Аналитика: docs/задачи/T-174-нет-таймлайнов-и-активности-после-обновления.md</t>
+        </is>
+      </c>
+      <c r="E179" s="24" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F179" s="24" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G179" s="25" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="H179" s="24" t="inlineStr">
+        <is>
+          <t>20.03.2026</t>
+        </is>
+      </c>
+      <c r="I179" s="24" t="inlineStr">
+        <is>
+          <t>20.03.2026</t>
         </is>
       </c>
     </row>

--- a/docs/tracker.xlsx
+++ b/docs/tracker.xlsx
@@ -610,7 +610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I179"/>
+  <dimension ref="A1:I180"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="15" min="1" max="1"/>
@@ -8976,6 +8976,53 @@
         </is>
       </c>
     </row>
+    <row r="180" ht="20" customHeight="1" s="15">
+      <c r="A180" s="24" t="inlineStr">
+        <is>
+          <t>T-175</t>
+        </is>
+      </c>
+      <c r="B180" s="24" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="C180" s="25" t="inlineStr">
+        <is>
+          <t>Нет глобальной проверки уникальности username — конфликт при логине</t>
+        </is>
+      </c>
+      <c r="D180" s="25" t="inlineStr">
+        <is>
+          <t>Username уникален только в рамках тенанта. При логине без slug — если два пользователя с одинаковым username в разных тенантах, система берёт первого. Второй не может залогиниться. Race condition при создании → 500 вместо 409. Аналитика: docs/ToDo/T-175-уникальность-username-при-регистрации.md</t>
+        </is>
+      </c>
+      <c r="E180" s="24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F180" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G180" s="25" t="inlineStr">
+        <is>
+          <t>Разработчик</t>
+        </is>
+      </c>
+      <c r="H180" s="24" t="inlineStr">
+        <is>
+          <t>20.03.2026</t>
+        </is>
+      </c>
+      <c r="I180" s="24" t="inlineStr">
+        <is>
+          <t>20.03.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>

--- a/docs/tracker.xlsx
+++ b/docs/tracker.xlsx
@@ -610,7 +610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I180"/>
+  <dimension ref="A1:I181"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="15" min="1" max="1"/>
@@ -9023,6 +9023,53 @@
         </is>
       </c>
     </row>
+    <row r="181" ht="20" customHeight="1" s="15">
+      <c r="A181" s="18" t="inlineStr">
+        <is>
+          <t>T-176</t>
+        </is>
+      </c>
+      <c r="B181" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C181" s="19" t="inlineStr">
+        <is>
+          <t>Серверный таймаут устройств: @Scheduled перевод в offline при отсутствии heartbeat</t>
+        </is>
+      </c>
+      <c r="D181" s="19" t="inlineStr">
+        <is>
+          <t>Control-plane @Scheduled(60s): если last_heartbeat_ts &gt; 90с → status=offline. Записывать в device_status_log. Аналитика: docs/ToDo/T-176-серверный-таймаут-устройств.md</t>
+        </is>
+      </c>
+      <c r="E181" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F181" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G181" s="19" t="inlineStr">
+        <is>
+          <t>Разработчик</t>
+        </is>
+      </c>
+      <c r="H181" s="18" t="inlineStr">
+        <is>
+          <t>20.03.2026</t>
+        </is>
+      </c>
+      <c r="I181" s="18" t="inlineStr">
+        <is>
+          <t>20.03.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>

--- a/docs/tracker.xlsx
+++ b/docs/tracker.xlsx
@@ -610,7 +610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I181"/>
+  <dimension ref="A1:I182"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="15" min="1" max="1"/>
@@ -9070,6 +9070,53 @@
         </is>
       </c>
     </row>
+    <row r="182" ht="20" customHeight="1" s="15">
+      <c r="A182" s="18" t="inlineStr">
+        <is>
+          <t>T-177</t>
+        </is>
+      </c>
+      <c r="B182" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C182" s="19" t="inlineStr">
+        <is>
+          <t>Мобильная адаптация web-dashboard: 16 подзадач по страницам</t>
+        </is>
+      </c>
+      <c r="D182" s="19" t="inlineStr">
+        <is>
+          <t>Адаптация всех 38 страниц к мобильным устройствам (320-428px). 1 critical (SessionDetailPage grid-cols-3), 5 high, 5 medium, 5 low. Аналитика: docs/ToDo/T-177-мобильная-адаптация-веба.md</t>
+        </is>
+      </c>
+      <c r="E182" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F182" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G182" s="19" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="H182" s="18" t="inlineStr">
+        <is>
+          <t>20.03.2026</t>
+        </is>
+      </c>
+      <c r="I182" s="18" t="inlineStr">
+        <is>
+          <t>20.03.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>

--- a/docs/tracker.xlsx
+++ b/docs/tracker.xlsx
@@ -610,7 +610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I182"/>
+  <dimension ref="A1:I183"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="15" min="1" max="1"/>
@@ -9117,6 +9117,53 @@
         </is>
       </c>
     </row>
+    <row r="183" ht="20" customHeight="1" s="15">
+      <c r="A183" s="18" t="inlineStr">
+        <is>
+          <t>T-178</t>
+        </is>
+      </c>
+      <c r="B183" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C183" s="19" t="inlineStr">
+        <is>
+          <t>Развёртывание промышленного контура kadero.online (2 app + 1 LB)</t>
+        </is>
+      </c>
+      <c r="D183" s="19" t="inlineStr">
+        <is>
+          <t>3 сервера: 2×(8vCPU/16GB/150GB) app + 1 LB. PostgreSQL primary+replica, MinIO distributed, Kafka 2 brokers, OpenSearch 2 nodes. nginx LB + SSL. Аналитика: docs/ToDo/T-178-промышленный-контур-kadero-online.md</t>
+        </is>
+      </c>
+      <c r="E183" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F183" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G183" s="19" t="inlineStr">
+        <is>
+          <t>DevOps</t>
+        </is>
+      </c>
+      <c r="H183" s="18" t="inlineStr">
+        <is>
+          <t>20.03.2026</t>
+        </is>
+      </c>
+      <c r="I183" s="18" t="inlineStr">
+        <is>
+          <t>20.03.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>

--- a/docs/tracker.xlsx
+++ b/docs/tracker.xlsx
@@ -610,7 +610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I183"/>
+  <dimension ref="A1:I184"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="15" min="1" max="1"/>
@@ -9164,6 +9164,53 @@
         </is>
       </c>
     </row>
+    <row r="184" ht="20" customHeight="1" s="15">
+      <c r="A184" s="18" t="inlineStr">
+        <is>
+          <t>T-179</t>
+        </is>
+      </c>
+      <c r="B184" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C184" s="19" t="inlineStr">
+        <is>
+          <t>Настройка отправки почты: noreply@shepaland.ru через reg.ru SMTP</t>
+        </is>
+      </c>
+      <c r="D184" s="19" t="inlineStr">
+        <is>
+          <t>Переключить email-отправку с otp@shepaland.ru на noreply@shepaland.ru. Обновить конфигурацию на test и prod. Решить проблему блокировки SMTP на Yandex Cloud (test). Аналитика: docs/todo/T-179-настройка-отправки-почты.md</t>
+        </is>
+      </c>
+      <c r="E184" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F184" s="18" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G184" s="19" t="inlineStr">
+        <is>
+          <t>DevOps</t>
+        </is>
+      </c>
+      <c r="H184" s="18" t="inlineStr">
+        <is>
+          <t>22.03.2026</t>
+        </is>
+      </c>
+      <c r="I184" s="18" t="inlineStr">
+        <is>
+          <t>22.03.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>

--- a/docs/tracker.xlsx
+++ b/docs/tracker.xlsx
@@ -610,7 +610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I184"/>
+  <dimension ref="A1:I186"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="15" min="1" max="1"/>
@@ -9211,6 +9211,100 @@
         </is>
       </c>
     </row>
+    <row r="185" ht="20" customHeight="1" s="15">
+      <c r="A185" s="18" t="inlineStr">
+        <is>
+          <t>T-180</t>
+        </is>
+      </c>
+      <c r="B185" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C185" s="19" t="inlineStr">
+        <is>
+          <t>Регистрация по Email: визард с подтверждением по ссылке</t>
+        </is>
+      </c>
+      <c r="D185" s="19" t="inlineStr">
+        <is>
+          <t>Визард регистрации: email+имя+компания → пароль (валидация сложности, генератор) → verification email со ссылкой → redirect на главную. Аналитика: docs/todo/T-180</t>
+        </is>
+      </c>
+      <c r="E185" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F185" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G185" s="19" t="inlineStr">
+        <is>
+          <t>Разработчик</t>
+        </is>
+      </c>
+      <c r="H185" s="18" t="inlineStr">
+        <is>
+          <t>22.03.2026</t>
+        </is>
+      </c>
+      <c r="I185" s="18" t="inlineStr">
+        <is>
+          <t>22.03.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="20" customHeight="1" s="15">
+      <c r="A186" s="18" t="inlineStr">
+        <is>
+          <t>T-181</t>
+        </is>
+      </c>
+      <c r="B186" s="18" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="C186" s="19" t="inlineStr">
+        <is>
+          <t>Восстановление пароля: forgot → email → reset → auto-login</t>
+        </is>
+      </c>
+      <c r="D186" s="19" t="inlineStr">
+        <is>
+          <t>Сброс пароля по email: forgot-password → ссылка (TTL 1ч) → новый пароль → инвалидация сессий → auto-login. Аналитика: docs/todo/T-181</t>
+        </is>
+      </c>
+      <c r="E186" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F186" s="18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G186" s="19" t="inlineStr">
+        <is>
+          <t>Разработчик</t>
+        </is>
+      </c>
+      <c r="H186" s="18" t="inlineStr">
+        <is>
+          <t>22.03.2026</t>
+        </is>
+      </c>
+      <c r="I186" s="18" t="inlineStr">
+        <is>
+          <t>22.03.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
